--- a/research/traditional_assets/database/data/italy/italy_retail_rei_ts.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_retail_rei_ts.xlsx
@@ -644,10 +644,10 @@
         <v>-0.07514867543701569</v>
       </c>
       <c r="X2">
-        <v>0.1959910726946192</v>
+        <v>0.1959629422719611</v>
       </c>
       <c r="Y2">
-        <v>-0.2711397481316348</v>
+        <v>-0.2711116177089768</v>
       </c>
       <c r="Z2">
         <v>0.07684003004130681</v>
@@ -656,10 +656,10 @@
         <v>0.05318250093879084</v>
       </c>
       <c r="AB2">
-        <v>0.09620845481097232</v>
+        <v>0.09620179528783643</v>
       </c>
       <c r="AC2">
-        <v>-0.04302595387218147</v>
+        <v>-0.04301929434904558</v>
       </c>
       <c r="AD2">
         <v>920.8</v>
@@ -775,10 +775,10 @@
         <v>-0.07514867543701569</v>
       </c>
       <c r="X3">
-        <v>0.1959910726946192</v>
+        <v>0.1959629422719611</v>
       </c>
       <c r="Y3">
-        <v>-0.2711397481316348</v>
+        <v>-0.2711116177089768</v>
       </c>
       <c r="Z3">
         <v>0.07684003004130681</v>
@@ -787,10 +787,10 @@
         <v>0.05318250093879084</v>
       </c>
       <c r="AB3">
-        <v>0.09620845481097232</v>
+        <v>0.09620179528783643</v>
       </c>
       <c r="AC3">
-        <v>-0.04302595387218147</v>
+        <v>-0.04301929434904558</v>
       </c>
       <c r="AD3">
         <v>920.8</v>
@@ -1127,7 +1127,7 @@
         <v>1.4256050955414</v>
       </c>
       <c r="F2">
-        <v>13.2649235820564</v>
+        <v>13.5226107320431</v>
       </c>
       <c r="G2">
         <v>8.05599300087489</v>
@@ -1145,13 +1145,13 @@
         <v>285.6</v>
       </c>
       <c r="L2">
-        <v>1181.14178371796</v>
+        <v>1185.87947813013</v>
       </c>
       <c r="M2">
         <v>1199.88</v>
       </c>
       <c r="N2">
-        <v>1367.64578371796</v>
+        <v>1372.38347813013</v>
       </c>
       <c r="O2">
         <v>920.8</v>
@@ -1160,16 +1160,16 @@
         <v>193.024</v>
       </c>
       <c r="Q2">
-        <v>0.0962084548109723</v>
+        <v>0.0962017952878364</v>
       </c>
       <c r="R2">
-        <v>0.0892638733997798</v>
+        <v>0.0890857934581103</v>
       </c>
       <c r="S2">
         <v>0.0652593717662617</v>
       </c>
       <c r="T2">
-        <v>0.0558353717662617</v>
+        <v>0.0547713717662617</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.195991072694619</v>
+        <v>0.195962942271961</v>
       </c>
       <c r="X2">
-        <v>0.0956312070442594</v>
+        <v>0.0956218737803672</v>
       </c>
       <c r="Y2">
         <v>2.06704942245325</v>
@@ -1224,7 +1224,7 @@
         <v>285.6</v>
       </c>
       <c r="AK2">
-        <v>0.07265964280446037</v>
+        <v>0.07264603383006794</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +1412,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08932975656944457</v>
+        <v>0.08932160355190144</v>
       </c>
       <c r="C2">
-        <v>1372.354060183942</v>
+        <v>1372.396224610062</v>
       </c>
       <c r="D2">
-        <v>1365.834060183942</v>
+        <v>1365.876224610062</v>
       </c>
       <c r="E2">
         <v>-920.8</v>
@@ -1463,19 +1463,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08932975656944457</v>
+        <v>0.08932160355190144</v>
       </c>
       <c r="T2">
         <v>0.5990912546403601</v>
       </c>
       <c r="U2">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V2">
         <v>0.24</v>
       </c>
       <c r="W2">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +1494,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08932563887134051</v>
+        <v>0.08930686542103949</v>
       </c>
       <c r="C3">
-        <v>1360.403152268505</v>
+        <v>1360.737119532206</v>
       </c>
       <c r="D3">
-        <v>1365.947152268505</v>
+        <v>1366.281119532206</v>
       </c>
       <c r="E3">
         <v>-908.736</v>
@@ -1527,37 +1527,37 @@
         <v>188.11</v>
       </c>
       <c r="M3">
-        <v>0.8863130591949751</v>
+        <v>0.869423459194975</v>
       </c>
       <c r="N3">
-        <v>187.223686940805</v>
+        <v>187.2405765408051</v>
       </c>
       <c r="O3">
-        <v>44.93368486579321</v>
+        <v>44.93773836979321</v>
       </c>
       <c r="P3">
-        <v>142.2900020750118</v>
+        <v>142.3028381710118</v>
       </c>
       <c r="Q3">
-        <v>144.6800020750118</v>
+        <v>144.6928381710118</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08966392439765444</v>
+        <v>0.08965570879128978</v>
       </c>
       <c r="T3">
         <v>0.6036903390194174</v>
       </c>
       <c r="U3">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V3">
         <v>0.24</v>
       </c>
       <c r="W3">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>212.2387773129029</v>
+        <v>216.3617717126895</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +1576,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08932152117323645</v>
+        <v>0.08929212729017755</v>
       </c>
       <c r="C4">
-        <v>1348.452263082837</v>
+        <v>1349.078254576416</v>
       </c>
       <c r="D4">
-        <v>1366.060263082837</v>
+        <v>1366.686254576416</v>
       </c>
       <c r="E4">
         <v>-896.6719999999999</v>
@@ -1609,37 +1609,37 @@
         <v>188.11</v>
       </c>
       <c r="M4">
-        <v>1.77262611838995</v>
+        <v>1.73884691838995</v>
       </c>
       <c r="N4">
-        <v>186.3373738816101</v>
+        <v>186.3711530816101</v>
       </c>
       <c r="O4">
-        <v>44.72096973158641</v>
+        <v>44.72907673958641</v>
       </c>
       <c r="P4">
-        <v>141.6164041500236</v>
+        <v>141.6420763420236</v>
       </c>
       <c r="Q4">
-        <v>144.0064041500236</v>
+        <v>144.0320763420236</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09000491197746044</v>
+        <v>0.08999663250495135</v>
       </c>
       <c r="T4">
         <v>0.6083832822633534</v>
       </c>
       <c r="U4">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V4">
         <v>0.24</v>
       </c>
       <c r="W4">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>106.1193886564514</v>
+        <v>108.1808858563448</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +1658,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08931740347513242</v>
+        <v>0.08927738915931561</v>
       </c>
       <c r="C5">
-        <v>1336.501392631592</v>
+        <v>1337.41962995636</v>
       </c>
       <c r="D5">
-        <v>1366.173392631592</v>
+        <v>1367.09162995636</v>
       </c>
       <c r="E5">
         <v>-884.6079999999999</v>
@@ -1691,37 +1691,37 @@
         <v>188.11</v>
       </c>
       <c r="M5">
-        <v>2.658939177584925</v>
+        <v>2.608270377584925</v>
       </c>
       <c r="N5">
-        <v>185.4510608224151</v>
+        <v>185.5017296224151</v>
       </c>
       <c r="O5">
-        <v>44.50825459737962</v>
+        <v>44.52041510937962</v>
       </c>
       <c r="P5">
-        <v>140.9428062250355</v>
+        <v>140.9813145130355</v>
       </c>
       <c r="Q5">
-        <v>143.3328062250355</v>
+        <v>143.3713145130355</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09035293022901503</v>
+        <v>0.09034458557353378</v>
       </c>
       <c r="T5">
         <v>0.6131729872236593</v>
       </c>
       <c r="U5">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V5">
         <v>0.24</v>
       </c>
       <c r="W5">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>70.74625910430098</v>
+        <v>72.12059057089651</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +1740,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08931328577702838</v>
+        <v>0.08926265102845365</v>
       </c>
       <c r="C6">
-        <v>1324.550540919425</v>
+        <v>1325.761245885962</v>
       </c>
       <c r="D6">
-        <v>1366.286540919425</v>
+        <v>1367.497245885962</v>
       </c>
       <c r="E6">
         <v>-872.544</v>
@@ -1773,37 +1773,37 @@
         <v>188.11</v>
       </c>
       <c r="M6">
-        <v>3.5452522367799</v>
+        <v>3.4776938367799</v>
       </c>
       <c r="N6">
-        <v>184.5647477632201</v>
+        <v>184.6323061632201</v>
       </c>
       <c r="O6">
-        <v>44.29553946317282</v>
+        <v>44.31175347917282</v>
       </c>
       <c r="P6">
-        <v>140.2692083000473</v>
+        <v>140.3205526840473</v>
       </c>
       <c r="Q6">
-        <v>142.6592083000473</v>
+        <v>142.7105526840473</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09070819886081033</v>
+        <v>0.09069978766437833</v>
       </c>
       <c r="T6">
         <v>0.6180624777039715</v>
       </c>
       <c r="U6">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V6">
         <v>0.24</v>
       </c>
       <c r="W6">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>53.05969432822572</v>
+        <v>54.09044292817238</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +1822,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08930916807892432</v>
+        <v>0.08924791289759172</v>
       </c>
       <c r="C7">
-        <v>1312.599707950992</v>
+        <v>1314.103102579398</v>
       </c>
       <c r="D7">
-        <v>1366.399707950992</v>
+        <v>1367.903102579397</v>
       </c>
       <c r="E7">
         <v>-860.4799999999999</v>
@@ -1855,37 +1855,37 @@
         <v>188.11</v>
       </c>
       <c r="M7">
-        <v>4.431565295974875</v>
+        <v>4.347117295974875</v>
       </c>
       <c r="N7">
-        <v>183.6784347040251</v>
+        <v>183.7628827040251</v>
       </c>
       <c r="O7">
-        <v>44.08282432896603</v>
+        <v>44.10309184896603</v>
       </c>
       <c r="P7">
-        <v>139.5956103750591</v>
+        <v>139.6597908550591</v>
       </c>
       <c r="Q7">
-        <v>141.9856103750591</v>
+        <v>142.0497908550591</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09107094683222236</v>
+        <v>0.09106246769397751</v>
       </c>
       <c r="T7">
         <v>0.6230549048259745</v>
       </c>
       <c r="U7">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V7">
         <v>0.24</v>
       </c>
       <c r="W7">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>42.44775546258058</v>
+        <v>43.27235434253791</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +1904,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08930505038082026</v>
+        <v>0.08923317476672978</v>
       </c>
       <c r="C8">
-        <v>1300.648893730952</v>
+        <v>1302.445200251098</v>
       </c>
       <c r="D8">
-        <v>1366.512893730952</v>
+        <v>1368.309200251098</v>
       </c>
       <c r="E8">
         <v>-848.4159999999999</v>
@@ -1937,37 +1937,37 @@
         <v>188.11</v>
       </c>
       <c r="M8">
-        <v>5.317878355169849</v>
+        <v>5.216540755169849</v>
       </c>
       <c r="N8">
-        <v>182.7921216448302</v>
+        <v>182.8934592448302</v>
       </c>
       <c r="O8">
-        <v>43.87010919475924</v>
+        <v>43.89443021875923</v>
       </c>
       <c r="P8">
-        <v>138.9220124500709</v>
+        <v>138.9990290260709</v>
       </c>
       <c r="Q8">
-        <v>141.3120124500709</v>
+        <v>141.3890290260709</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09144141284557933</v>
+        <v>0.09143286431995114</v>
       </c>
       <c r="T8">
         <v>0.6281535538016372</v>
       </c>
       <c r="U8">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V8">
         <v>0.24</v>
       </c>
       <c r="W8">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>35.37312955215049</v>
+        <v>36.06029528544826</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08930093268271622</v>
+        <v>0.08921843663586781</v>
       </c>
       <c r="C9">
-        <v>1288.698098263962</v>
+        <v>1290.78753911575</v>
       </c>
       <c r="D9">
-        <v>1366.626098263963</v>
+        <v>1368.71553911575</v>
       </c>
       <c r="E9">
         <v>-836.352</v>
@@ -2019,37 +2019,37 @@
         <v>188.11</v>
       </c>
       <c r="M9">
-        <v>6.204191414364825</v>
+        <v>6.085964214364824</v>
       </c>
       <c r="N9">
-        <v>181.9058085856352</v>
+        <v>182.0240357856352</v>
       </c>
       <c r="O9">
-        <v>43.65739406055244</v>
+        <v>43.68576858855244</v>
       </c>
       <c r="P9">
-        <v>138.2484145250828</v>
+        <v>138.3382671970828</v>
       </c>
       <c r="Q9">
-        <v>140.6384145250827</v>
+        <v>140.7282671970827</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09181984586997624</v>
+        <v>0.0918112264647629</v>
       </c>
       <c r="T9">
         <v>0.6333618511423678</v>
       </c>
       <c r="U9">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V9">
         <v>0.24</v>
       </c>
       <c r="W9">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>30.3198253304147</v>
+        <v>30.90882453038422</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +2068,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08929681498461217</v>
+        <v>0.08920369850500588</v>
       </c>
       <c r="C10">
-        <v>1276.747321554686</v>
+        <v>1279.130119388293</v>
       </c>
       <c r="D10">
-        <v>1366.739321554686</v>
+        <v>1369.122119388293</v>
       </c>
       <c r="E10">
         <v>-824.2879999999999</v>
@@ -2101,37 +2101,37 @@
         <v>188.11</v>
       </c>
       <c r="M10">
-        <v>7.0905044735598</v>
+        <v>6.9553876735598</v>
       </c>
       <c r="N10">
-        <v>181.0194955264402</v>
+        <v>181.1546123264402</v>
       </c>
       <c r="O10">
-        <v>43.44467892634565</v>
+        <v>43.47710695834564</v>
       </c>
       <c r="P10">
-        <v>137.5748166000946</v>
+        <v>137.6775053680946</v>
       </c>
       <c r="Q10">
-        <v>139.9648166000945</v>
+        <v>140.0675053680945</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09220650569925135</v>
+        <v>0.09219781387359233</v>
       </c>
       <c r="T10">
         <v>0.6386833723383316</v>
       </c>
       <c r="U10">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V10">
         <v>0.24</v>
       </c>
       <c r="W10">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.52984716411286</v>
+        <v>27.04522146408619</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +2150,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08929269728650811</v>
+        <v>0.08918896037414392</v>
       </c>
       <c r="C11">
-        <v>1264.796563607785</v>
+        <v>1267.472941283925</v>
       </c>
       <c r="D11">
-        <v>1366.852563607785</v>
+        <v>1369.528941283925</v>
       </c>
       <c r="E11">
         <v>-812.2239999999999</v>
@@ -2183,37 +2183,37 @@
         <v>188.11</v>
       </c>
       <c r="M11">
-        <v>7.976817532754774</v>
+        <v>7.824811132754775</v>
       </c>
       <c r="N11">
-        <v>180.1331824672452</v>
+        <v>180.2851888672452</v>
       </c>
       <c r="O11">
-        <v>43.23196379213886</v>
+        <v>43.26844532813885</v>
       </c>
       <c r="P11">
-        <v>136.9012186751064</v>
+        <v>137.0167435391064</v>
       </c>
       <c r="Q11">
-        <v>139.2912186751064</v>
+        <v>139.4067435391064</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09260166354675227</v>
+        <v>0.09259289770898942</v>
       </c>
       <c r="T11">
         <v>0.6441218500440969</v>
       </c>
       <c r="U11">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V11">
         <v>0.24</v>
       </c>
       <c r="W11">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.58208636810032</v>
+        <v>24.0401968569655</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +2232,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08928857958840408</v>
+        <v>0.08917422224328199</v>
       </c>
       <c r="C12">
-        <v>1252.845824427922</v>
+        <v>1255.816005018097</v>
       </c>
       <c r="D12">
-        <v>1366.965824427922</v>
+        <v>1369.936005018097</v>
       </c>
       <c r="E12">
         <v>-800.16</v>
@@ -2265,37 +2265,37 @@
         <v>188.11</v>
       </c>
       <c r="M12">
-        <v>8.86313059194975</v>
+        <v>8.694234591949749</v>
       </c>
       <c r="N12">
-        <v>179.2468694080503</v>
+        <v>179.4157654080503</v>
       </c>
       <c r="O12">
-        <v>43.01924865793206</v>
+        <v>43.05978369793206</v>
       </c>
       <c r="P12">
-        <v>136.2276207501182</v>
+        <v>136.3559817101182</v>
       </c>
       <c r="Q12">
-        <v>138.6176207501182</v>
+        <v>138.7459817101182</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09300560267975323</v>
+        <v>0.09299676118517314</v>
       </c>
       <c r="T12">
         <v>0.6496811828099905</v>
       </c>
       <c r="U12">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V12">
         <v>0.24</v>
       </c>
       <c r="W12">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.22387773129029</v>
+        <v>21.63617717126895</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +2314,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08928446189030002</v>
+        <v>0.08915948411242003</v>
       </c>
       <c r="C13">
-        <v>1240.895104019765</v>
+        <v>1244.159310806517</v>
       </c>
       <c r="D13">
-        <v>1367.079104019765</v>
+        <v>1370.343310806517</v>
       </c>
       <c r="E13">
         <v>-788.096</v>
@@ -2347,37 +2347,37 @@
         <v>188.11</v>
       </c>
       <c r="M13">
-        <v>9.749443651144723</v>
+        <v>9.563658051144724</v>
       </c>
       <c r="N13">
-        <v>178.3605563488553</v>
+        <v>178.5463419488553</v>
       </c>
       <c r="O13">
-        <v>42.80653352372526</v>
+        <v>42.85112206772526</v>
       </c>
       <c r="P13">
-        <v>135.55402282513</v>
+        <v>135.69521988113</v>
       </c>
       <c r="Q13">
-        <v>137.94402282513</v>
+        <v>138.08521988113</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09341861909664184</v>
+        <v>0.09340970024509129</v>
       </c>
       <c r="T13">
         <v>0.6553654444020838</v>
       </c>
       <c r="U13">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V13">
         <v>0.24</v>
       </c>
       <c r="W13">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.29443430117299</v>
+        <v>19.66925197388087</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +2396,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08928034419219597</v>
+        <v>0.08914474598155808</v>
       </c>
       <c r="C14">
-        <v>1228.944402387979</v>
+        <v>1232.502858865151</v>
       </c>
       <c r="D14">
-        <v>1367.192402387979</v>
+        <v>1370.750858865151</v>
       </c>
       <c r="E14">
         <v>-776.0319999999999</v>
@@ -2429,37 +2429,37 @@
         <v>188.11</v>
       </c>
       <c r="M14">
-        <v>10.6357567103397</v>
+        <v>10.4330815103397</v>
       </c>
       <c r="N14">
-        <v>177.4742432896603</v>
+        <v>177.6769184896603</v>
       </c>
       <c r="O14">
-        <v>42.59381838951847</v>
+        <v>42.64246043751847</v>
       </c>
       <c r="P14">
-        <v>134.8804249001418</v>
+        <v>135.0344580521418</v>
       </c>
       <c r="Q14">
-        <v>137.2704249001418</v>
+        <v>137.4244580521418</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09384102225027792</v>
+        <v>0.09383202428364396</v>
       </c>
       <c r="T14">
         <v>0.6611788937576337</v>
       </c>
       <c r="U14">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V14">
         <v>0.24</v>
       </c>
       <c r="W14">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.68656477607524</v>
+        <v>18.03014764272413</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +2478,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08927622649409193</v>
+        <v>0.08913000785069615</v>
       </c>
       <c r="C15">
-        <v>1216.993719537234</v>
+        <v>1220.846649410221</v>
       </c>
       <c r="D15">
-        <v>1367.305719537234</v>
+        <v>1371.158649410221</v>
       </c>
       <c r="E15">
         <v>-763.968</v>
@@ -2511,37 +2511,37 @@
         <v>188.11</v>
       </c>
       <c r="M15">
-        <v>11.52206976953467</v>
+        <v>11.30250496953468</v>
       </c>
       <c r="N15">
-        <v>176.5879302304653</v>
+        <v>176.8074950304653</v>
       </c>
       <c r="O15">
-        <v>42.38110325531168</v>
+        <v>42.43379880731167</v>
       </c>
       <c r="P15">
-        <v>134.2068269751537</v>
+        <v>134.3736962231537</v>
       </c>
       <c r="Q15">
-        <v>136.5968269751536</v>
+        <v>136.7636962231537</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09427313582123897</v>
+        <v>0.09426405692078405</v>
       </c>
       <c r="T15">
         <v>0.6671259856271045</v>
       </c>
       <c r="U15">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V15">
         <v>0.24</v>
       </c>
       <c r="W15">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.32605979330022</v>
+        <v>16.64321320866842</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +2560,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08927210879598788</v>
+        <v>0.0891152697198342</v>
       </c>
       <c r="C16">
-        <v>1205.043055472201</v>
+        <v>1209.190682658206</v>
       </c>
       <c r="D16">
-        <v>1367.419055472201</v>
+        <v>1371.566682658206</v>
       </c>
       <c r="E16">
         <v>-751.904</v>
@@ -2593,37 +2593,37 @@
         <v>188.11</v>
       </c>
       <c r="M16">
-        <v>12.40838282872965</v>
+        <v>12.17192842872965</v>
       </c>
       <c r="N16">
-        <v>175.7016171712704</v>
+        <v>175.9380715712704</v>
       </c>
       <c r="O16">
-        <v>42.16838812110488</v>
+        <v>42.22513717710489</v>
       </c>
       <c r="P16">
-        <v>133.5332290501655</v>
+        <v>133.7129343941655</v>
       </c>
       <c r="Q16">
-        <v>135.9232290501654</v>
+        <v>136.1029343941655</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09471529854501307</v>
+        <v>0.0947061368285553</v>
       </c>
       <c r="T16">
         <v>0.6732113819586558</v>
       </c>
       <c r="U16">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V16">
         <v>0.24</v>
       </c>
       <c r="W16">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.15991266520735</v>
+        <v>15.45441226519211</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +2642,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08926799109788382</v>
+        <v>0.08910053158897224</v>
       </c>
       <c r="C17">
-        <v>1193.09241019755</v>
+        <v>1197.534958825843</v>
       </c>
       <c r="D17">
-        <v>1367.53241019755</v>
+        <v>1371.974958825843</v>
       </c>
       <c r="E17">
         <v>-739.8399999999999</v>
@@ -2675,37 +2675,37 @@
         <v>188.11</v>
       </c>
       <c r="M17">
-        <v>13.29469588792462</v>
+        <v>13.04135188792462</v>
       </c>
       <c r="N17">
-        <v>174.8153041120754</v>
+        <v>175.0686481120754</v>
       </c>
       <c r="O17">
-        <v>41.95567298689809</v>
+        <v>42.01647554689809</v>
       </c>
       <c r="P17">
-        <v>132.8596311251773</v>
+        <v>133.0521725651773</v>
       </c>
       <c r="Q17">
-        <v>135.2496311251773</v>
+        <v>135.4421725651773</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09516786509758185</v>
+        <v>0.0951586186165094</v>
       </c>
       <c r="T17">
         <v>0.6794399640862436</v>
       </c>
       <c r="U17">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V17">
         <v>0.24</v>
       </c>
       <c r="W17">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.14925182086019</v>
+        <v>14.4241181141793</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +2724,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08926387339977977</v>
+        <v>0.0890857934581103</v>
       </c>
       <c r="C18">
-        <v>1181.141783717955</v>
+        <v>1185.879478130127</v>
       </c>
       <c r="D18">
-        <v>1367.645783717955</v>
+        <v>1372.383478130127</v>
       </c>
       <c r="E18">
         <v>-727.776</v>
@@ -2757,37 +2757,37 @@
         <v>188.11</v>
       </c>
       <c r="M18">
-        <v>14.1810089471196</v>
+        <v>13.9107753471196</v>
       </c>
       <c r="N18">
-        <v>173.9289910528804</v>
+        <v>174.1992246528804</v>
       </c>
       <c r="O18">
-        <v>41.7429578526913</v>
+        <v>41.8078139166913</v>
       </c>
       <c r="P18">
-        <v>132.1860332001891</v>
+        <v>132.3914107361891</v>
       </c>
       <c r="Q18">
-        <v>134.5760332001891</v>
+        <v>134.7814107361891</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09563120704425941</v>
+        <v>0.09562187378036718</v>
       </c>
       <c r="T18">
         <v>0.6858168457882979</v>
       </c>
       <c r="U18">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V18">
         <v>0.24</v>
       </c>
       <c r="W18">
-        <v>0.05583537176626168</v>
+        <v>0.05477137176626168</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.26492358205643</v>
+        <v>13.52261073204309</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +2806,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08940187570167572</v>
+        <v>0.08926485532724837</v>
       </c>
       <c r="C19">
-        <v>1165.288348715727</v>
+        <v>1168.868564900984</v>
       </c>
       <c r="D19">
-        <v>1363.856348715727</v>
+        <v>1367.436564900984</v>
       </c>
       <c r="E19">
         <v>-715.712</v>
@@ -2839,37 +2839,37 @@
         <v>188.11</v>
       </c>
       <c r="M19">
-        <v>15.29291880631457</v>
+        <v>15.08783080631457</v>
       </c>
       <c r="N19">
-        <v>172.8170811936855</v>
+        <v>173.0221691936854</v>
       </c>
       <c r="O19">
-        <v>41.47609948648451</v>
+        <v>41.52532060648451</v>
       </c>
       <c r="P19">
-        <v>131.3409817072009</v>
+        <v>131.4968485872009</v>
       </c>
       <c r="Q19">
-        <v>133.7309817072009</v>
+        <v>133.8868485872009</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09610571385712197</v>
+        <v>0.09609629171925768</v>
       </c>
       <c r="T19">
         <v>0.6923473872904017</v>
       </c>
       <c r="U19">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V19">
         <v>0.24</v>
       </c>
       <c r="W19">
-        <v>0.05667137176626167</v>
+        <v>0.05591137176626167</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.30046418099911</v>
+        <v>12.4676636698015</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08940611800357166</v>
+        <v>0.08926151719638642</v>
       </c>
       <c r="C20">
-        <v>1153.108191093922</v>
+        <v>1156.89646065163</v>
       </c>
       <c r="D20">
-        <v>1363.740191093922</v>
+        <v>1367.52846065163</v>
       </c>
       <c r="E20">
         <v>-703.6479999999999</v>
@@ -2921,37 +2921,37 @@
         <v>188.11</v>
       </c>
       <c r="M20">
-        <v>16.19250226550955</v>
+        <v>15.97535026550955</v>
       </c>
       <c r="N20">
-        <v>171.9174977344905</v>
+        <v>172.1346497344905</v>
       </c>
       <c r="O20">
-        <v>41.26019945627771</v>
+        <v>41.31231593627771</v>
       </c>
       <c r="P20">
-        <v>130.6572982782127</v>
+        <v>130.8223337982128</v>
       </c>
       <c r="Q20">
-        <v>133.0472982782127</v>
+        <v>133.2123337982127</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09659179400688361</v>
+        <v>0.0965822808273894</v>
       </c>
       <c r="T20">
         <v>0.6990372102925567</v>
       </c>
       <c r="U20">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V20">
         <v>0.24</v>
       </c>
       <c r="W20">
-        <v>0.05667137176626167</v>
+        <v>0.05591137176626167</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.61710505983249</v>
+        <v>11.77501568814586</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +2970,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08941036030546762</v>
+        <v>0.08925817906552445</v>
       </c>
       <c r="C21">
-        <v>1140.928053256376</v>
+        <v>1144.924368754434</v>
       </c>
       <c r="D21">
-        <v>1363.624053256376</v>
+        <v>1367.620368754434</v>
       </c>
       <c r="E21">
         <v>-691.5839999999999</v>
@@ -3003,37 +3003,37 @@
         <v>188.11</v>
       </c>
       <c r="M21">
-        <v>17.09208572470452</v>
+        <v>16.86286972470452</v>
       </c>
       <c r="N21">
-        <v>171.0179142752955</v>
+        <v>171.2471302752955</v>
       </c>
       <c r="O21">
-        <v>41.04429942607091</v>
+        <v>41.09931126607091</v>
       </c>
       <c r="P21">
-        <v>129.9736148492246</v>
+        <v>130.1478190092246</v>
       </c>
       <c r="Q21">
-        <v>132.3636148492245</v>
+        <v>132.5378190092246</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09708987613565173</v>
+        <v>0.0970802696665861</v>
       </c>
       <c r="T21">
         <v>0.7058922141095798</v>
       </c>
       <c r="U21">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V21">
         <v>0.24</v>
       </c>
       <c r="W21">
-        <v>0.05667137176626167</v>
+        <v>0.05591137176626167</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.00567847773604</v>
+        <v>11.15527802034871</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +3052,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08941460260736357</v>
+        <v>0.08925484093466252</v>
       </c>
       <c r="C22">
-        <v>1128.747935198036</v>
+        <v>1132.952289211887</v>
       </c>
       <c r="D22">
-        <v>1363.507935198036</v>
+        <v>1367.712289211887</v>
       </c>
       <c r="E22">
         <v>-679.52</v>
@@ -3085,37 +3085,37 @@
         <v>188.11</v>
       </c>
       <c r="M22">
-        <v>17.9916691838995</v>
+        <v>17.7503891838995</v>
       </c>
       <c r="N22">
-        <v>170.1183308161005</v>
+        <v>170.3596108161005</v>
       </c>
       <c r="O22">
-        <v>40.82839939586412</v>
+        <v>40.88630659586412</v>
       </c>
       <c r="P22">
-        <v>129.2899314202364</v>
+        <v>129.4733042202364</v>
       </c>
       <c r="Q22">
-        <v>131.6799314202364</v>
+        <v>131.8633042202364</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09760041031763904</v>
+        <v>0.09759070822676272</v>
       </c>
       <c r="T22">
         <v>0.7129185930220284</v>
       </c>
       <c r="U22">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V22">
         <v>0.24</v>
       </c>
       <c r="W22">
-        <v>0.05667137176626167</v>
+        <v>0.05591137176626167</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.45539455384924</v>
+        <v>10.59751411933127</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +3134,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08941884490925953</v>
+        <v>0.08925150280380056</v>
       </c>
       <c r="C23">
-        <v>1116.567836913849</v>
+        <v>1120.98022202648</v>
       </c>
       <c r="D23">
-        <v>1363.391836913849</v>
+        <v>1367.80422202648</v>
       </c>
       <c r="E23">
         <v>-667.4559999999999</v>
@@ -3167,37 +3167,37 @@
         <v>188.11</v>
       </c>
       <c r="M23">
-        <v>18.89125264309447</v>
+        <v>18.63790864309447</v>
       </c>
       <c r="N23">
-        <v>169.2187473569055</v>
+        <v>169.4720913569055</v>
       </c>
       <c r="O23">
-        <v>40.61249936565733</v>
+        <v>40.67330192565733</v>
       </c>
       <c r="P23">
-        <v>128.6062479912482</v>
+        <v>128.7987894312482</v>
       </c>
       <c r="Q23">
-        <v>130.9962479912482</v>
+        <v>131.1887894312482</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09812386941562604</v>
+        <v>0.09811406928213369</v>
       </c>
       <c r="T23">
         <v>0.7201228549449189</v>
       </c>
       <c r="U23">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V23">
         <v>0.24</v>
       </c>
       <c r="W23">
-        <v>0.05667137176626167</v>
+        <v>0.05591137176626167</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.957518622713563</v>
+        <v>10.09287058983931</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08979092721115547</v>
+        <v>0.08953240467293863</v>
       </c>
       <c r="C24">
-        <v>1094.39747158529</v>
+        <v>1101.223120393001</v>
       </c>
       <c r="D24">
-        <v>1353.28547158529</v>
+        <v>1360.111120393001</v>
       </c>
       <c r="E24">
         <v>-655.3919999999999</v>
@@ -3249,37 +3249,37 @@
         <v>188.11</v>
       </c>
       <c r="M24">
-        <v>20.37473370228945</v>
+        <v>19.97662170228945</v>
       </c>
       <c r="N24">
-        <v>167.7352662977106</v>
+        <v>168.1333782977106</v>
       </c>
       <c r="O24">
-        <v>40.25646391145053</v>
+        <v>40.35201079145054</v>
       </c>
       <c r="P24">
-        <v>127.47880238626</v>
+        <v>127.78136750626</v>
       </c>
       <c r="Q24">
-        <v>129.86880238626</v>
+        <v>130.17136750626</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09866075054176654</v>
+        <v>0.09865084985174494</v>
       </c>
       <c r="T24">
         <v>0.7275118415324988</v>
       </c>
       <c r="U24">
-        <v>0.07676759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V24">
         <v>0.24</v>
       </c>
       <c r="W24">
-        <v>0.05834337176626168</v>
+        <v>0.05720337176626168</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.232513305381884</v>
+        <v>9.41650709531339</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +3298,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08981188951305143</v>
+        <v>0.08954198654207667</v>
       </c>
       <c r="C25">
-        <v>1081.768557566793</v>
+        <v>1088.898226319257</v>
       </c>
       <c r="D25">
-        <v>1352.720557566793</v>
+        <v>1359.850226319257</v>
       </c>
       <c r="E25">
         <v>-643.328</v>
@@ -3331,37 +3331,37 @@
         <v>188.11</v>
       </c>
       <c r="M25">
-        <v>21.30085796148443</v>
+        <v>20.88464996148442</v>
       </c>
       <c r="N25">
-        <v>166.8091420385156</v>
+        <v>167.2253500385156</v>
       </c>
       <c r="O25">
-        <v>40.03419408924373</v>
+        <v>40.13408400924374</v>
       </c>
       <c r="P25">
-        <v>126.7749479492718</v>
+        <v>127.0912660292718</v>
       </c>
       <c r="Q25">
-        <v>129.1649479492718</v>
+        <v>129.4812660292718</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09921157663222238</v>
+        <v>0.09920157277381361</v>
       </c>
       <c r="T25">
         <v>0.7350927498496262</v>
       </c>
       <c r="U25">
-        <v>0.07676759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V25">
         <v>0.24</v>
       </c>
       <c r="W25">
-        <v>0.05834337176626168</v>
+        <v>0.05720337176626168</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.831099683408755</v>
+        <v>9.007093743343241</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +3380,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08983285181494736</v>
+        <v>0.08955156841121473</v>
       </c>
       <c r="C26">
-        <v>1069.14011498569</v>
+        <v>1076.573432314783</v>
       </c>
       <c r="D26">
-        <v>1352.15611498569</v>
+        <v>1359.589432314783</v>
       </c>
       <c r="E26">
         <v>-631.2639999999999</v>
@@ -3413,37 +3413,37 @@
         <v>188.11</v>
       </c>
       <c r="M26">
-        <v>22.2269822206794</v>
+        <v>21.7926782206794</v>
       </c>
       <c r="N26">
-        <v>165.8830177793206</v>
+        <v>166.3173217793206</v>
       </c>
       <c r="O26">
-        <v>39.81192426703695</v>
+        <v>39.91615722703695</v>
       </c>
       <c r="P26">
-        <v>126.0710935122837</v>
+        <v>126.4011645522837</v>
       </c>
       <c r="Q26">
-        <v>128.4610935122837</v>
+        <v>128.7911645522837</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09977689814611126</v>
+        <v>0.09976678840435779</v>
       </c>
       <c r="T26">
         <v>0.7428731557540464</v>
       </c>
       <c r="U26">
-        <v>0.07676759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V26">
         <v>0.24</v>
       </c>
       <c r="W26">
-        <v>0.05834337176626168</v>
+        <v>0.05720337176626168</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.463137196600062</v>
+        <v>8.631798170703942</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +3462,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08985381411684333</v>
+        <v>0.08956115028035277</v>
       </c>
       <c r="C27">
-        <v>1056.512143252083</v>
+        <v>1064.248738322017</v>
       </c>
       <c r="D27">
-        <v>1351.592143252083</v>
+        <v>1359.328738322017</v>
       </c>
       <c r="E27">
         <v>-619.1999999999999</v>
@@ -3495,37 +3495,37 @@
         <v>188.11</v>
       </c>
       <c r="M27">
-        <v>23.15310647987437</v>
+        <v>22.70070647987437</v>
       </c>
       <c r="N27">
-        <v>164.9568935201256</v>
+        <v>165.4092935201256</v>
       </c>
       <c r="O27">
-        <v>39.58965444483015</v>
+        <v>39.69823044483015</v>
       </c>
       <c r="P27">
-        <v>125.3672390752955</v>
+        <v>125.7110630752955</v>
       </c>
       <c r="Q27">
-        <v>127.7572390752955</v>
+        <v>128.1010630752955</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1003572949003705</v>
+        <v>0.1003470764517165</v>
       </c>
       <c r="T27">
         <v>0.7508610391492513</v>
       </c>
       <c r="U27">
-        <v>0.07676759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V27">
         <v>0.24</v>
       </c>
       <c r="W27">
-        <v>0.05834337176626168</v>
+        <v>0.05720337176626168</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.124611708736058</v>
+        <v>8.28652624387578</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +3544,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08987477641873927</v>
+        <v>0.08957073214949084</v>
       </c>
       <c r="C28">
-        <v>1043.88464177706</v>
+        <v>1051.924144283439</v>
       </c>
       <c r="D28">
-        <v>1351.02864177706</v>
+        <v>1359.068144283439</v>
       </c>
       <c r="E28">
         <v>-607.136</v>
@@ -3577,37 +3577,37 @@
         <v>188.11</v>
       </c>
       <c r="M28">
-        <v>24.07923073906935</v>
+        <v>23.60873473906935</v>
       </c>
       <c r="N28">
-        <v>164.0307692609307</v>
+        <v>164.5012652609307</v>
       </c>
       <c r="O28">
-        <v>39.36738462262336</v>
+        <v>39.48030366262336</v>
       </c>
       <c r="P28">
-        <v>124.6633846383073</v>
+        <v>125.0209615983073</v>
       </c>
       <c r="Q28">
-        <v>127.0533846383073</v>
+        <v>127.4109615983073</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1009533780533935</v>
+        <v>0.1009430479598146</v>
       </c>
       <c r="T28">
         <v>0.759064811284867</v>
       </c>
       <c r="U28">
-        <v>0.07676759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V28">
         <v>0.24</v>
       </c>
       <c r="W28">
-        <v>0.05834337176626168</v>
+        <v>0.05720337176626168</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.81212664301544</v>
+        <v>7.967813696034406</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +3626,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.09020353872063522</v>
+        <v>0.08958031401862887</v>
       </c>
       <c r="C29">
-        <v>1023.044037608596</v>
+        <v>1039.599650141575</v>
       </c>
       <c r="D29">
-        <v>1342.252037608596</v>
+        <v>1358.807650141575</v>
       </c>
       <c r="E29">
         <v>-595.0719999999999</v>
@@ -3659,45 +3659,45 @@
         <v>188.11</v>
       </c>
       <c r="M29">
-        <v>25.49394699826433</v>
+        <v>24.51676299826433</v>
       </c>
       <c r="N29">
-        <v>162.6160530017357</v>
+        <v>163.5932370017357</v>
       </c>
       <c r="O29">
-        <v>39.02785272041656</v>
+        <v>39.26237688041657</v>
       </c>
       <c r="P29">
-        <v>123.5882002813191</v>
+        <v>124.3308601213191</v>
       </c>
       <c r="Q29">
-        <v>125.9782002813191</v>
+        <v>126.7208601213191</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1015657922517049</v>
+        <v>0.1015553474544359</v>
       </c>
       <c r="T29">
         <v>0.7674933443009105</v>
       </c>
       <c r="U29">
-        <v>0.07826759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V29">
         <v>0.24</v>
       </c>
       <c r="W29">
-        <v>0.05948337176626168</v>
+        <v>0.05720337176626168</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.378614226067343</v>
+        <v>7.672709485070168</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.09023590102253116</v>
+        <v>0.08976013588776693</v>
       </c>
       <c r="C30">
-        <v>1010.122257855703</v>
+        <v>1022.665441145596</v>
       </c>
       <c r="D30">
-        <v>1341.394257855703</v>
+        <v>1353.937441145596</v>
       </c>
       <c r="E30">
         <v>-583.0079999999999</v>
@@ -3741,37 +3741,37 @@
         <v>188.11</v>
       </c>
       <c r="M30">
-        <v>26.4381672574593</v>
+        <v>25.69502485745929</v>
       </c>
       <c r="N30">
-        <v>161.6718327425407</v>
+        <v>162.4149751425407</v>
       </c>
       <c r="O30">
-        <v>38.80123985820977</v>
+        <v>38.97959403420978</v>
       </c>
       <c r="P30">
-        <v>122.8705928843309</v>
+        <v>123.4353811083309</v>
       </c>
       <c r="Q30">
-        <v>125.2605928843309</v>
+        <v>125.8253811083309</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1021952179555249</v>
+        <v>0.1021846552683523</v>
       </c>
       <c r="T30">
         <v>0.7761560032340665</v>
       </c>
       <c r="U30">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V30">
         <v>0.24</v>
       </c>
       <c r="W30">
-        <v>0.05948337176626168</v>
+        <v>0.05781137176626167</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.115092289422082</v>
+        <v>7.320872466305144</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +3790,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.09026826332442711</v>
+        <v>0.08977579775690497</v>
       </c>
       <c r="C31">
-        <v>997.2015737482975</v>
+        <v>1010.178914847795</v>
       </c>
       <c r="D31">
-        <v>1340.537573748298</v>
+        <v>1353.514914847795</v>
       </c>
       <c r="E31">
         <v>-570.944</v>
@@ -3823,37 +3823,37 @@
         <v>188.11</v>
       </c>
       <c r="M31">
-        <v>27.38238751665427</v>
+        <v>26.61270431665427</v>
       </c>
       <c r="N31">
-        <v>160.7276124833458</v>
+        <v>161.4972956833458</v>
       </c>
       <c r="O31">
-        <v>38.57462699600298</v>
+        <v>38.75935096400298</v>
       </c>
       <c r="P31">
-        <v>122.1529854873428</v>
+        <v>122.7379447193428</v>
       </c>
       <c r="Q31">
-        <v>124.5429854873428</v>
+        <v>125.1279447193428</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1028423739608609</v>
+        <v>0.1028316900629424</v>
       </c>
       <c r="T31">
         <v>0.7850626807287198</v>
       </c>
       <c r="U31">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V31">
         <v>0.24</v>
       </c>
       <c r="W31">
-        <v>0.05948337176626168</v>
+        <v>0.05781137176626167</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.869744279442012</v>
+        <v>7.068428588156692</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +3872,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.09030062562632304</v>
+        <v>0.08979145962604304</v>
       </c>
       <c r="C32">
-        <v>984.281983188509</v>
+        <v>997.6926521851815</v>
       </c>
       <c r="D32">
-        <v>1339.681983188509</v>
+        <v>1353.092652185182</v>
       </c>
       <c r="E32">
         <v>-558.8799999999999</v>
@@ -3905,37 +3905,37 @@
         <v>188.11</v>
       </c>
       <c r="M32">
-        <v>28.32660777584925</v>
+        <v>27.53038377584924</v>
       </c>
       <c r="N32">
-        <v>159.7833922241508</v>
+        <v>160.5796162241508</v>
       </c>
       <c r="O32">
-        <v>38.34801413379618</v>
+        <v>38.53910789379618</v>
       </c>
       <c r="P32">
-        <v>121.4353780903546</v>
+        <v>122.0405083303546</v>
       </c>
       <c r="Q32">
-        <v>123.8253780903546</v>
+        <v>124.4305083303546</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1035080201377779</v>
+        <v>0.1034972115659493</v>
       </c>
       <c r="T32">
         <v>0.7942238347232201</v>
       </c>
       <c r="U32">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V32">
         <v>0.24</v>
       </c>
       <c r="W32">
-        <v>0.05948337176626168</v>
+        <v>0.05781137176626167</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.64075280346061</v>
+        <v>6.832814301884801</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +3954,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.09033298792821901</v>
+        <v>0.08980712149518109</v>
       </c>
       <c r="C33">
-        <v>971.3634840838212</v>
+        <v>985.2066529110904</v>
       </c>
       <c r="D33">
-        <v>1338.827484083821</v>
+        <v>1352.67065291109</v>
       </c>
       <c r="E33">
         <v>-546.8159999999999</v>
@@ -3987,37 +3987,37 @@
         <v>188.11</v>
       </c>
       <c r="M33">
-        <v>29.27082803504422</v>
+        <v>28.44806323504422</v>
       </c>
       <c r="N33">
-        <v>158.8391719649558</v>
+        <v>159.6619367649558</v>
       </c>
       <c r="O33">
-        <v>38.12140127158939</v>
+        <v>38.31886482358939</v>
       </c>
       <c r="P33">
-        <v>120.7177706933664</v>
+        <v>121.3430719413664</v>
       </c>
       <c r="Q33">
-        <v>123.1077706933664</v>
+        <v>123.7330719413664</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1041929604067796</v>
+        <v>0.1041820235473043</v>
       </c>
       <c r="T33">
         <v>0.8036505294132135</v>
       </c>
       <c r="U33">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V33">
         <v>0.24</v>
       </c>
       <c r="W33">
-        <v>0.05948337176626168</v>
+        <v>0.05781137176626167</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.426534971090914</v>
+        <v>6.612400937307871</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +4036,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.09036535023011497</v>
+        <v>0.08982278336431915</v>
       </c>
       <c r="C34">
-        <v>958.446074347054</v>
+        <v>972.7209167791641</v>
       </c>
       <c r="D34">
-        <v>1337.974074347054</v>
+        <v>1352.248916779164</v>
       </c>
       <c r="E34">
         <v>-534.752</v>
@@ -4069,37 +4069,37 @@
         <v>188.11</v>
       </c>
       <c r="M34">
-        <v>30.2150482942392</v>
+        <v>29.3657426942392</v>
       </c>
       <c r="N34">
-        <v>157.8949517057608</v>
+        <v>158.7442573057608</v>
       </c>
       <c r="O34">
-        <v>37.89478840938259</v>
+        <v>38.0986217533826</v>
       </c>
       <c r="P34">
-        <v>120.0001632963782</v>
+        <v>120.6456355523782</v>
       </c>
       <c r="Q34">
-        <v>122.3901632963782</v>
+        <v>123.0356355523782</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1048980459778106</v>
+        <v>0.1048869770575227</v>
       </c>
       <c r="T34">
         <v>0.8133544798293829</v>
       </c>
       <c r="U34">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V34">
         <v>0.24</v>
       </c>
       <c r="W34">
-        <v>0.05948337176626168</v>
+        <v>0.05781137176626167</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.225705753244322</v>
+        <v>6.405763408017001</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +4118,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.09074883253201091</v>
+        <v>0.0898384452334572</v>
       </c>
       <c r="C35">
-        <v>936.3516675380793</v>
+        <v>960.2354435433506</v>
       </c>
       <c r="D35">
-        <v>1327.943667538079</v>
+        <v>1351.827443543351</v>
       </c>
       <c r="E35">
         <v>-522.6879999999999</v>
@@ -4151,45 +4151,45 @@
         <v>188.11</v>
       </c>
       <c r="M35">
-        <v>31.71662535343417</v>
+        <v>30.28342215343417</v>
       </c>
       <c r="N35">
-        <v>156.3933746465658</v>
+        <v>157.8265778465658</v>
       </c>
       <c r="O35">
-        <v>37.5344099151758</v>
+        <v>37.8783786831758</v>
       </c>
       <c r="P35">
-        <v>118.85896473139</v>
+        <v>119.94819916339</v>
       </c>
       <c r="Q35">
-        <v>121.24896473139</v>
+        <v>122.33819916339</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1056241788793202</v>
+        <v>0.1056129739561057</v>
       </c>
       <c r="T35">
         <v>0.8233481004072292</v>
       </c>
       <c r="U35">
-        <v>0.07966759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V35">
         <v>0.24</v>
       </c>
       <c r="W35">
-        <v>0.06054737176626167</v>
+        <v>0.05781137176626167</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y35">
-        <v>5.930958855294234</v>
+        <v>6.211649365349819</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +4200,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.09079183483390685</v>
+        <v>0.09011250710259525</v>
       </c>
       <c r="C36">
-        <v>923.1722641956898</v>
+        <v>940.8385155790135</v>
       </c>
       <c r="D36">
-        <v>1326.82826419569</v>
+        <v>1344.494515579014</v>
       </c>
       <c r="E36">
         <v>-510.6239999999999</v>
@@ -4233,37 +4233,37 @@
         <v>188.11</v>
       </c>
       <c r="M36">
-        <v>32.67773521262914</v>
+        <v>31.61127761262915</v>
       </c>
       <c r="N36">
-        <v>155.4322647873709</v>
+        <v>156.4987223873709</v>
       </c>
       <c r="O36">
-        <v>37.303743548969</v>
+        <v>37.55969337296901</v>
       </c>
       <c r="P36">
-        <v>118.1285212384018</v>
+        <v>118.9390290144019</v>
       </c>
       <c r="Q36">
-        <v>120.5185212384018</v>
+        <v>121.3290290144019</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1063723158081483</v>
+        <v>0.1063609707607065</v>
       </c>
       <c r="T36">
         <v>0.8336445579722829</v>
       </c>
       <c r="U36">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V36">
         <v>0.24</v>
       </c>
       <c r="W36">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.75651888896205</v>
+        <v>5.950724368218747</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +4282,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.0908348371358028</v>
+        <v>0.09013576897173331</v>
       </c>
       <c r="C37">
-        <v>909.9947330418934</v>
+        <v>928.1557711854525</v>
       </c>
       <c r="D37">
-        <v>1325.714733041893</v>
+        <v>1343.875771185453</v>
       </c>
       <c r="E37">
         <v>-498.5599999999999</v>
@@ -4315,37 +4315,37 @@
         <v>188.11</v>
       </c>
       <c r="M37">
-        <v>33.63884507182412</v>
+        <v>32.54102107182412</v>
       </c>
       <c r="N37">
-        <v>154.4711549281759</v>
+        <v>155.5689789281759</v>
       </c>
       <c r="O37">
-        <v>37.07307718276222</v>
+        <v>37.33655494276222</v>
       </c>
       <c r="P37">
-        <v>117.3980777454137</v>
+        <v>118.2324239854137</v>
       </c>
       <c r="Q37">
-        <v>119.7880777454137</v>
+        <v>120.6224239854137</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1071434723347865</v>
+        <v>0.1071319828516027</v>
       </c>
       <c r="T37">
         <v>0.8442578296162613</v>
       </c>
       <c r="U37">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V37">
         <v>0.24</v>
       </c>
       <c r="W37">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.592046920705992</v>
+        <v>5.780703671983927</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +4364,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.09087783943769877</v>
+        <v>0.09015903084087135</v>
       </c>
       <c r="C38">
-        <v>896.8190693669799</v>
+        <v>915.4735960296448</v>
       </c>
       <c r="D38">
-        <v>1324.60306936698</v>
+        <v>1343.257596029645</v>
       </c>
       <c r="E38">
         <v>-486.4959999999999</v>
@@ -4397,37 +4397,37 @@
         <v>188.11</v>
       </c>
       <c r="M38">
-        <v>34.5999549310191</v>
+        <v>33.47076453101909</v>
       </c>
       <c r="N38">
-        <v>153.5100450689809</v>
+        <v>154.6392354689809</v>
       </c>
       <c r="O38">
-        <v>36.84241081655541</v>
+        <v>37.11341651255542</v>
       </c>
       <c r="P38">
-        <v>116.6676342524255</v>
+        <v>117.5258189564255</v>
       </c>
       <c r="Q38">
-        <v>119.0576342524255</v>
+        <v>119.9158189564255</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1079387275028821</v>
+        <v>0.1079270890703393</v>
       </c>
       <c r="T38">
         <v>0.8552027659991139</v>
       </c>
       <c r="U38">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V38">
         <v>0.24</v>
       </c>
       <c r="W38">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.436712284019714</v>
+        <v>5.620128569984374</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +4446,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.09092084173959472</v>
+        <v>0.09018229271000941</v>
       </c>
       <c r="C39">
-        <v>883.6452684770237</v>
+        <v>902.7919893264119</v>
       </c>
       <c r="D39">
-        <v>1323.493268477024</v>
+        <v>1342.639989326412</v>
       </c>
       <c r="E39">
         <v>-474.4319999999999</v>
@@ -4479,37 +4479,37 @@
         <v>188.11</v>
       </c>
       <c r="M39">
-        <v>35.56106479021408</v>
+        <v>34.40050799021407</v>
       </c>
       <c r="N39">
-        <v>152.548935209786</v>
+        <v>153.7094920097859</v>
       </c>
       <c r="O39">
-        <v>36.61174445034862</v>
+        <v>36.89027808234862</v>
       </c>
       <c r="P39">
-        <v>115.9371907594373</v>
+        <v>116.8192139274373</v>
       </c>
       <c r="Q39">
-        <v>118.3271907594373</v>
+        <v>119.2092139274373</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1087592288667903</v>
+        <v>0.1087474367563374</v>
       </c>
       <c r="T39">
         <v>0.866495160679835</v>
       </c>
       <c r="U39">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V39">
         <v>0.24</v>
       </c>
       <c r="W39">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.289774114181344</v>
+        <v>5.468233203228038</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +4528,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.09096384404149067</v>
+        <v>0.09020555457914747</v>
       </c>
       <c r="C40">
-        <v>870.4733256938159</v>
+        <v>890.1109502920206</v>
       </c>
       <c r="D40">
-        <v>1322.385325693816</v>
+        <v>1342.022950292021</v>
       </c>
       <c r="E40">
         <v>-462.3679999999999</v>
@@ -4561,37 +4561,37 @@
         <v>188.11</v>
       </c>
       <c r="M40">
-        <v>36.52217464940905</v>
+        <v>35.33025144940904</v>
       </c>
       <c r="N40">
-        <v>151.587825350591</v>
+        <v>152.779748550591</v>
       </c>
       <c r="O40">
-        <v>36.38107808414183</v>
+        <v>36.66713965214183</v>
       </c>
       <c r="P40">
-        <v>115.2067472664491</v>
+        <v>116.1126088984491</v>
       </c>
       <c r="Q40">
-        <v>117.5967472664491</v>
+        <v>118.5026088984491</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.109606198016631</v>
+        <v>0.1095942472709162</v>
       </c>
       <c r="T40">
         <v>0.8781518261567084</v>
       </c>
       <c r="U40">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V40">
         <v>0.24</v>
       </c>
       <c r="W40">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.150569532229204</v>
+        <v>5.32433232945888</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +4610,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.09100684634338663</v>
+        <v>0.09022881644828554</v>
       </c>
       <c r="C41">
-        <v>857.3032363547998</v>
+        <v>877.4304781441774</v>
       </c>
       <c r="D41">
-        <v>1321.2792363548</v>
+        <v>1341.406478144178</v>
       </c>
       <c r="E41">
         <v>-450.3039999999999</v>
@@ -4643,37 +4643,37 @@
         <v>188.11</v>
       </c>
       <c r="M41">
-        <v>37.48328450860402</v>
+        <v>36.25999490860402</v>
       </c>
       <c r="N41">
-        <v>150.626715491396</v>
+        <v>151.850005091396</v>
       </c>
       <c r="O41">
-        <v>36.15041171793504</v>
+        <v>36.44400122193503</v>
       </c>
       <c r="P41">
-        <v>114.476303773461</v>
+        <v>115.406003869461</v>
       </c>
       <c r="Q41">
-        <v>116.866303773461</v>
+        <v>117.796003869461</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1104809366467944</v>
+        <v>0.1104688220646614</v>
       </c>
       <c r="T41">
         <v>0.8901906773869219</v>
       </c>
       <c r="U41">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V41">
         <v>0.24</v>
       </c>
       <c r="W41">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.018503646787429</v>
+        <v>5.187810987677882</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +4692,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.09104984864528257</v>
+        <v>0.09025207831742357</v>
       </c>
       <c r="C42">
-        <v>844.1349958130066</v>
+        <v>864.7505721020262</v>
       </c>
       <c r="D42">
-        <v>1320.174995813007</v>
+        <v>1340.790572102026</v>
       </c>
       <c r="E42">
         <v>-438.2399999999999</v>
@@ -4725,37 +4725,37 @@
         <v>188.11</v>
       </c>
       <c r="M42">
-        <v>38.444394367799</v>
+        <v>37.189738367799</v>
       </c>
       <c r="N42">
-        <v>149.665605632201</v>
+        <v>150.920261632201</v>
       </c>
       <c r="O42">
-        <v>35.91974535172825</v>
+        <v>36.22086279172824</v>
       </c>
       <c r="P42">
-        <v>113.7458602804728</v>
+        <v>114.6993988404728</v>
       </c>
       <c r="Q42">
-        <v>116.1358602804728</v>
+        <v>117.0893988404728</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1113848332312965</v>
+        <v>0.1113725493515315</v>
       </c>
       <c r="T42">
         <v>0.9026308236581426</v>
       </c>
       <c r="U42">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V42">
         <v>0.24</v>
       </c>
       <c r="W42">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.893041055617743</v>
+        <v>5.058115712985935</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +4774,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.09109285094717851</v>
+        <v>0.09027534018656164</v>
       </c>
       <c r="C43">
-        <v>830.9685994369875</v>
+        <v>852.0712313861418</v>
       </c>
       <c r="D43">
-        <v>1319.072599436988</v>
+        <v>1340.175231386142</v>
       </c>
       <c r="E43">
         <v>-426.1759999999999</v>
@@ -4807,37 +4807,37 @@
         <v>188.11</v>
       </c>
       <c r="M43">
-        <v>39.40550422699398</v>
+        <v>38.11948182699397</v>
       </c>
       <c r="N43">
-        <v>148.704495773006</v>
+        <v>149.9905181730061</v>
       </c>
       <c r="O43">
-        <v>35.68907898552145</v>
+        <v>35.99772436152145</v>
       </c>
       <c r="P43">
-        <v>113.0154167874846</v>
+        <v>113.9927938114846</v>
       </c>
       <c r="Q43">
-        <v>115.4054167874846</v>
+        <v>116.3827938114846</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1123193703779851</v>
+        <v>0.1123069114616853</v>
       </c>
       <c r="T43">
         <v>0.9154926698029637</v>
       </c>
       <c r="U43">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V43">
         <v>0.24</v>
       </c>
       <c r="W43">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.773698590846578</v>
+        <v>4.93474703705945</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +4856,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.09113585324907447</v>
+        <v>0.0902986020556997</v>
       </c>
       <c r="C44">
-        <v>817.8040426107502</v>
+        <v>839.3924552185317</v>
       </c>
       <c r="D44">
-        <v>1317.97204261075</v>
+        <v>1339.560455218532</v>
       </c>
       <c r="E44">
         <v>-414.1119999999999</v>
@@ -4889,37 +4889,37 @@
         <v>188.11</v>
       </c>
       <c r="M44">
-        <v>40.36661408618895</v>
+        <v>39.04922528618894</v>
       </c>
       <c r="N44">
-        <v>147.7433859138111</v>
+        <v>149.0607747138111</v>
       </c>
       <c r="O44">
-        <v>35.45841261931466</v>
+        <v>35.77458593131465</v>
       </c>
       <c r="P44">
-        <v>112.2849732944964</v>
+        <v>113.2861887824964</v>
       </c>
       <c r="Q44">
-        <v>114.6749732944964</v>
+        <v>115.6761887824964</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1132861329435251</v>
+        <v>0.1132734929549479</v>
       </c>
       <c r="T44">
         <v>0.9287980278838134</v>
       </c>
       <c r="U44">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V44">
         <v>0.24</v>
       </c>
       <c r="W44">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.660039100588326</v>
+        <v>4.817253059986605</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +4938,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.09117885555097043</v>
+        <v>0.09032186392483774</v>
       </c>
       <c r="C45">
-        <v>804.6413207336972</v>
+        <v>826.7142428226301</v>
       </c>
       <c r="D45">
-        <v>1316.873320733697</v>
+        <v>1338.94624282263</v>
       </c>
       <c r="E45">
         <v>-402.0479999999999</v>
@@ -4971,37 +4971,37 @@
         <v>188.11</v>
       </c>
       <c r="M45">
-        <v>41.32772394538392</v>
+        <v>39.97896874538392</v>
       </c>
       <c r="N45">
-        <v>146.7822760546161</v>
+        <v>148.1310312546161</v>
       </c>
       <c r="O45">
-        <v>35.22774625310786</v>
+        <v>35.55144750110786</v>
       </c>
       <c r="P45">
-        <v>111.5545298015082</v>
+        <v>112.5795837535082</v>
       </c>
       <c r="Q45">
-        <v>113.9445298015082</v>
+        <v>114.9695837535082</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1142868170025928</v>
+        <v>0.1142739895883249</v>
       </c>
       <c r="T45">
         <v>0.9425702406341664</v>
       </c>
       <c r="U45">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V45">
         <v>0.24</v>
       </c>
       <c r="W45">
-        <v>0.06054737176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.551666098249063</v>
+        <v>4.705223919056683</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +5020,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.09209129785286636</v>
+        <v>0.0903451257939758</v>
       </c>
       <c r="C46">
-        <v>769.6884514149876</v>
+        <v>814.0365934232932</v>
       </c>
       <c r="D46">
-        <v>1293.984451414988</v>
+        <v>1338.332593423293</v>
       </c>
       <c r="E46">
         <v>-389.9839999999999</v>
@@ -5053,45 +5053,45 @@
         <v>188.11</v>
       </c>
       <c r="M46">
-        <v>43.6689554045789</v>
+        <v>40.90871220457889</v>
       </c>
       <c r="N46">
-        <v>144.4410445954211</v>
+        <v>147.2012877954211</v>
       </c>
       <c r="O46">
-        <v>34.66585070290107</v>
+        <v>35.32830907090107</v>
       </c>
       <c r="P46">
-        <v>109.7751938925201</v>
+        <v>111.8729787245201</v>
       </c>
       <c r="Q46">
-        <v>112.1651938925201</v>
+        <v>114.2629787245201</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1153232397780558</v>
+        <v>0.1153102182443226</v>
       </c>
       <c r="T46">
         <v>0.9568343181256035</v>
       </c>
       <c r="U46">
-        <v>0.08226759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V46">
         <v>0.24</v>
       </c>
       <c r="W46">
-        <v>0.06252337176626169</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.307636815610107</v>
+        <v>4.598287011805397</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +5102,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.09215406015476232</v>
+        <v>0.09122338766311386</v>
       </c>
       <c r="C47">
-        <v>756.0792541436424</v>
+        <v>779.2085155137963</v>
       </c>
       <c r="D47">
-        <v>1292.439254143643</v>
+        <v>1315.568515513796</v>
       </c>
       <c r="E47">
         <v>-377.9199999999998</v>
@@ -5135,37 +5135,37 @@
         <v>188.11</v>
       </c>
       <c r="M47">
-        <v>44.66143166377388</v>
+        <v>43.19565566377388</v>
       </c>
       <c r="N47">
-        <v>143.4485683362261</v>
+        <v>144.9143443362261</v>
       </c>
       <c r="O47">
-        <v>34.42765640069427</v>
+        <v>34.77944264069427</v>
       </c>
       <c r="P47">
-        <v>109.0209119355318</v>
+        <v>110.1349016955319</v>
       </c>
       <c r="Q47">
-        <v>111.4109119355318</v>
+        <v>112.5249016955319</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1163973506544446</v>
+        <v>0.1163841279423565</v>
       </c>
       <c r="T47">
         <v>0.9716170893440021</v>
       </c>
       <c r="U47">
-        <v>0.08226759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V47">
         <v>0.24</v>
       </c>
       <c r="W47">
-        <v>0.06252337176626169</v>
+        <v>0.06047137176626168</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.211911553040992</v>
+        <v>4.354836085003771</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +5184,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.09221682245665827</v>
+        <v>0.09126564953225191</v>
       </c>
       <c r="C48">
-        <v>742.4737428313337</v>
+        <v>766.0686231256658</v>
       </c>
       <c r="D48">
-        <v>1290.897742831334</v>
+        <v>1314.492623125666</v>
       </c>
       <c r="E48">
         <v>-365.8559999999999</v>
@@ -5217,37 +5217,37 @@
         <v>188.11</v>
       </c>
       <c r="M48">
-        <v>45.65390792296885</v>
+        <v>44.15555912296885</v>
       </c>
       <c r="N48">
-        <v>142.4560920770312</v>
+        <v>143.9544408770312</v>
       </c>
       <c r="O48">
-        <v>34.18946209848748</v>
+        <v>34.54906581048748</v>
       </c>
       <c r="P48">
-        <v>108.2666299785437</v>
+        <v>109.4053750665437</v>
       </c>
       <c r="Q48">
-        <v>110.6566299785437</v>
+        <v>111.7953750665437</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1175112434151442</v>
+        <v>0.117497812073651</v>
       </c>
       <c r="T48">
         <v>0.9869473706075265</v>
       </c>
       <c r="U48">
-        <v>0.08226759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V48">
         <v>0.24</v>
       </c>
       <c r="W48">
-        <v>0.06252337176626169</v>
+        <v>0.06047137176626168</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.120348258409668</v>
+        <v>4.260165735329777</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +5266,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.09227958475855422</v>
+        <v>0.09130791140138994</v>
       </c>
       <c r="C49">
-        <v>728.8719043048798</v>
+        <v>752.930489062599</v>
       </c>
       <c r="D49">
-        <v>1289.35990430488</v>
+        <v>1313.418489062599</v>
       </c>
       <c r="E49">
         <v>-353.7919999999999</v>
@@ -5299,37 +5299,37 @@
         <v>188.11</v>
       </c>
       <c r="M49">
-        <v>46.64638418216382</v>
+        <v>45.11546258216381</v>
       </c>
       <c r="N49">
-        <v>141.4636158178362</v>
+        <v>142.9945374178362</v>
       </c>
       <c r="O49">
-        <v>33.95126779628069</v>
+        <v>34.31868898028068</v>
       </c>
       <c r="P49">
-        <v>107.5123480215555</v>
+        <v>108.6758484375555</v>
       </c>
       <c r="Q49">
-        <v>109.9023480215555</v>
+        <v>111.0658484375555</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1186671698649268</v>
+        <v>0.1186535220212207</v>
       </c>
       <c r="T49">
         <v>1.002856153050806</v>
       </c>
       <c r="U49">
-        <v>0.08226759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V49">
         <v>0.24</v>
       </c>
       <c r="W49">
-        <v>0.06252337176626169</v>
+        <v>0.06047137176626168</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.032681274188185</v>
+        <v>4.169523911173824</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +5348,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.09332730706045016</v>
+        <v>0.091350173270528</v>
       </c>
       <c r="C50">
-        <v>691.6665664421608</v>
+        <v>739.7941090176824</v>
       </c>
       <c r="D50">
-        <v>1264.218566442161</v>
+        <v>1312.346109017682</v>
       </c>
       <c r="E50">
         <v>-341.728</v>
@@ -5381,45 +5381,45 @@
         <v>188.11</v>
       </c>
       <c r="M50">
-        <v>49.20235484135879</v>
+        <v>46.07536604135879</v>
       </c>
       <c r="N50">
-        <v>138.9076451586412</v>
+        <v>142.0346339586412</v>
       </c>
       <c r="O50">
-        <v>33.3378348380739</v>
+        <v>34.08831215007389</v>
       </c>
       <c r="P50">
-        <v>105.5698103205673</v>
+        <v>107.9463218085673</v>
       </c>
       <c r="Q50">
-        <v>107.9598103205673</v>
+        <v>110.3363218085673</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1198675550243165</v>
+        <v>0.1198536823513892</v>
       </c>
       <c r="T50">
         <v>1.019376811741905</v>
       </c>
       <c r="U50">
-        <v>0.08496759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V50">
         <v>0.24</v>
       </c>
       <c r="W50">
-        <v>0.06457537176626167</v>
+        <v>0.06047137176626168</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.82319099576668</v>
+        <v>4.082658829691036</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +5430,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.0934105893623461</v>
+        <v>0.09269583513966605</v>
       </c>
       <c r="C51">
-        <v>677.6461094679902</v>
+        <v>694.4767977672033</v>
       </c>
       <c r="D51">
-        <v>1262.26210946799</v>
+        <v>1279.092797767203</v>
       </c>
       <c r="E51">
         <v>-329.6639999999999</v>
@@ -5463,37 +5463,37 @@
         <v>188.11</v>
       </c>
       <c r="M51">
-        <v>50.22740390055377</v>
+        <v>49.10424550055377</v>
       </c>
       <c r="N51">
-        <v>137.8825960994462</v>
+        <v>139.0057544994463</v>
       </c>
       <c r="O51">
-        <v>33.0918230638671</v>
+        <v>33.3613810798671</v>
       </c>
       <c r="P51">
-        <v>104.7907730355791</v>
+        <v>105.6443734195792</v>
       </c>
       <c r="Q51">
-        <v>107.1807730355791</v>
+        <v>108.0343734195792</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1211150141115253</v>
+        <v>0.1211009077925448</v>
       </c>
       <c r="T51">
         <v>1.036545339401282</v>
       </c>
       <c r="U51">
-        <v>0.08496759442929168</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V51">
         <v>0.24</v>
       </c>
       <c r="W51">
-        <v>0.06457537176626167</v>
+        <v>0.06313137176626167</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.745166689730624</v>
+        <v>3.830829658056321</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +5512,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.09349387166424206</v>
+        <v>0.0927646970088041</v>
       </c>
       <c r="C52">
-        <v>663.6316986151232</v>
+        <v>680.7563846860728</v>
       </c>
       <c r="D52">
-        <v>1260.311698615123</v>
+        <v>1277.436384686073</v>
       </c>
       <c r="E52">
         <v>-317.5999999999999</v>
@@ -5545,37 +5545,37 @@
         <v>188.11</v>
       </c>
       <c r="M52">
-        <v>51.25245295974874</v>
+        <v>50.10637295974875</v>
       </c>
       <c r="N52">
-        <v>136.8575470402513</v>
+        <v>138.0036270402513</v>
       </c>
       <c r="O52">
-        <v>32.8458112896603</v>
+        <v>33.12087048966031</v>
       </c>
       <c r="P52">
-        <v>104.011735750591</v>
+        <v>104.882756550591</v>
       </c>
       <c r="Q52">
-        <v>106.401735750591</v>
+        <v>107.272756550591</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1224123715622225</v>
+        <v>0.1223980222513465</v>
       </c>
       <c r="T52">
         <v>1.054400608167034</v>
       </c>
       <c r="U52">
-        <v>0.08496759442929168</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V52">
         <v>0.24</v>
       </c>
       <c r="W52">
-        <v>0.06457537176626167</v>
+        <v>0.06313137176626167</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.670263355936012</v>
+        <v>3.754213064895194</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +5594,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.093577153966138</v>
+        <v>0.09283355887794216</v>
       </c>
       <c r="C53">
-        <v>649.6233058999254</v>
+        <v>667.0402561350785</v>
       </c>
       <c r="D53">
-        <v>1258.367305899925</v>
+        <v>1275.784256135079</v>
       </c>
       <c r="E53">
         <v>-305.5359999999999</v>
@@ -5627,37 +5627,37 @@
         <v>188.11</v>
       </c>
       <c r="M53">
-        <v>52.27750201894371</v>
+        <v>51.10850041894372</v>
       </c>
       <c r="N53">
-        <v>135.8324979810563</v>
+        <v>137.0014995810563</v>
       </c>
       <c r="O53">
-        <v>32.59979951545351</v>
+        <v>32.88035989945351</v>
       </c>
       <c r="P53">
-        <v>103.2326984656028</v>
+        <v>104.1211396816028</v>
       </c>
       <c r="Q53">
-        <v>105.6226984656028</v>
+        <v>106.5111396816028</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1237626823782542</v>
+        <v>0.1237480801574463</v>
       </c>
       <c r="T53">
         <v>1.07298466341302</v>
       </c>
       <c r="U53">
-        <v>0.08496759442929168</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V53">
         <v>0.24</v>
       </c>
       <c r="W53">
-        <v>0.06457537176626167</v>
+        <v>0.06313137176626167</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.598297407780404</v>
+        <v>3.680601044014896</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +5676,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.09366043626803396</v>
+        <v>0.09290242074708022</v>
       </c>
       <c r="C54">
-        <v>635.6209035111859</v>
+        <v>653.3283955119415</v>
       </c>
       <c r="D54">
-        <v>1256.428903511186</v>
+        <v>1274.136395511942</v>
       </c>
       <c r="E54">
         <v>-293.4719999999999</v>
@@ -5709,37 +5709,37 @@
         <v>188.11</v>
       </c>
       <c r="M54">
-        <v>53.3025510781387</v>
+        <v>52.1106278781387</v>
       </c>
       <c r="N54">
-        <v>134.8074489218613</v>
+        <v>135.9993721218613</v>
       </c>
       <c r="O54">
-        <v>32.35378774124672</v>
+        <v>32.63984930924671</v>
       </c>
       <c r="P54">
-        <v>102.4536611806146</v>
+        <v>103.3595228126146</v>
       </c>
       <c r="Q54">
-        <v>104.8436611806146</v>
+        <v>105.7495228126146</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1251692561449539</v>
+        <v>0.1251543904763003</v>
       </c>
       <c r="T54">
         <v>1.092343054294256</v>
       </c>
       <c r="U54">
-        <v>0.08496759442929168</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V54">
         <v>0.24</v>
       </c>
       <c r="W54">
-        <v>0.06457537176626167</v>
+        <v>0.06313137176626167</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.529099380707704</v>
+        <v>3.609820254706917</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +5758,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.09563687856992992</v>
+        <v>0.09297128261621826</v>
       </c>
       <c r="C55">
-        <v>579.2457809598402</v>
+        <v>639.6207863000507</v>
       </c>
       <c r="D55">
-        <v>1212.11778095984</v>
+        <v>1272.492786300051</v>
       </c>
       <c r="E55">
         <v>-281.4079999999999</v>
@@ -5791,45 +5791,45 @@
         <v>188.11</v>
       </c>
       <c r="M55">
-        <v>57.33274253733367</v>
+        <v>53.11275533733367</v>
       </c>
       <c r="N55">
-        <v>130.7772574626663</v>
+        <v>134.9972446626663</v>
       </c>
       <c r="O55">
-        <v>31.38654179103992</v>
+        <v>32.39933871903992</v>
       </c>
       <c r="P55">
-        <v>99.39071567162642</v>
+        <v>102.5979059436264</v>
       </c>
       <c r="Q55">
-        <v>101.7807156716264</v>
+        <v>104.9879059436264</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.126635684114492</v>
+        <v>0.1266205437874459</v>
       </c>
       <c r="T55">
         <v>1.112525206489588</v>
       </c>
       <c r="U55">
-        <v>0.08966759442929167</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V55">
         <v>0.24</v>
       </c>
       <c r="W55">
-        <v>0.06814737176626168</v>
+        <v>0.06313137176626167</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.281022181653135</v>
+        <v>3.541710438580371</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +5840,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.09575588087182586</v>
+        <v>0.09418926448535632</v>
       </c>
       <c r="C56">
-        <v>564.6133396633284</v>
+        <v>599.1709062721045</v>
       </c>
       <c r="D56">
-        <v>1209.549339663329</v>
+        <v>1244.106906272105</v>
       </c>
       <c r="E56">
         <v>-269.3439999999998</v>
@@ -5873,37 +5873,37 @@
         <v>188.11</v>
       </c>
       <c r="M56">
-        <v>58.41449239652865</v>
+        <v>55.93895959652865</v>
       </c>
       <c r="N56">
-        <v>129.6955076034714</v>
+        <v>132.1710404034714</v>
       </c>
       <c r="O56">
-        <v>31.12692182483313</v>
+        <v>31.72104969683312</v>
       </c>
       <c r="P56">
-        <v>98.56858577863824</v>
+        <v>100.4499907066382</v>
       </c>
       <c r="Q56">
-        <v>100.9585857786382</v>
+        <v>102.8399907066382</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.128165869821836</v>
+        <v>0.1281504428947283</v>
       </c>
       <c r="T56">
         <v>1.133584843562977</v>
       </c>
       <c r="U56">
-        <v>0.08966759442929167</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V56">
         <v>0.24</v>
       </c>
       <c r="W56">
-        <v>0.06814737176626168</v>
+        <v>0.06525937176626168</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.220262511622521</v>
+        <v>3.362772589207637</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +5922,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.09587488317372181</v>
+        <v>0.09427940635449439</v>
       </c>
       <c r="C57">
-        <v>549.9917602512652</v>
+        <v>585.0563387941892</v>
       </c>
       <c r="D57">
-        <v>1206.991760251265</v>
+        <v>1242.056338794189</v>
       </c>
       <c r="E57">
         <v>-257.2799999999999</v>
@@ -5955,37 +5955,37 @@
         <v>188.11</v>
       </c>
       <c r="M57">
-        <v>59.49624225572362</v>
+        <v>56.97486625572362</v>
       </c>
       <c r="N57">
-        <v>128.6137577442764</v>
+        <v>131.1351337442764</v>
       </c>
       <c r="O57">
-        <v>30.86730185862633</v>
+        <v>31.47243209862634</v>
       </c>
       <c r="P57">
-        <v>97.74645588565006</v>
+        <v>99.66270164565006</v>
       </c>
       <c r="Q57">
-        <v>100.1364558856501</v>
+        <v>102.0527016456501</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1297640637828398</v>
+        <v>0.1297483375178899</v>
       </c>
       <c r="T57">
         <v>1.155580464506295</v>
       </c>
       <c r="U57">
-        <v>0.08966759442929167</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V57">
         <v>0.24</v>
       </c>
       <c r="W57">
-        <v>0.06814737176626168</v>
+        <v>0.06525937176626168</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.161712284138475</v>
+        <v>3.301631269403862</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +6004,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09599388547561777</v>
+        <v>0.09436954822363244</v>
       </c>
       <c r="C58">
-        <v>535.3809739670126</v>
+        <v>570.9485197843771</v>
       </c>
       <c r="D58">
-        <v>1204.444973967013</v>
+        <v>1240.012519784377</v>
       </c>
       <c r="E58">
         <v>-245.2159999999999</v>
@@ -6037,37 +6037,37 @@
         <v>188.11</v>
       </c>
       <c r="M58">
-        <v>60.57799211491859</v>
+        <v>58.01077291491859</v>
       </c>
       <c r="N58">
-        <v>127.5320078850814</v>
+        <v>130.0992270850814</v>
       </c>
       <c r="O58">
-        <v>30.60768189241954</v>
+        <v>31.22381450041954</v>
       </c>
       <c r="P58">
-        <v>96.92432599266188</v>
+        <v>98.87541258466189</v>
       </c>
       <c r="Q58">
-        <v>99.31432599266188</v>
+        <v>101.2654125846619</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1314349029238892</v>
+        <v>0.1314188637148316</v>
       </c>
       <c r="T58">
         <v>1.178575886401581</v>
       </c>
       <c r="U58">
-        <v>0.08966759442929167</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V58">
         <v>0.24</v>
       </c>
       <c r="W58">
-        <v>0.06814737176626168</v>
+        <v>0.06525937176626168</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.105253136207431</v>
+        <v>3.242673568164507</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +6086,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09611288777751371</v>
+        <v>0.0944596900927705</v>
       </c>
       <c r="C59">
-        <v>520.7809126330251</v>
+        <v>556.8474159833345</v>
       </c>
       <c r="D59">
-        <v>1201.908912633025</v>
+        <v>1237.975415983335</v>
       </c>
       <c r="E59">
         <v>-233.1519999999998</v>
@@ -6119,37 +6119,37 @@
         <v>188.11</v>
       </c>
       <c r="M59">
-        <v>61.65974197411357</v>
+        <v>59.04667957411358</v>
       </c>
       <c r="N59">
-        <v>126.4502580258864</v>
+        <v>129.0633204258864</v>
       </c>
       <c r="O59">
-        <v>30.34806192621274</v>
+        <v>30.97519690221274</v>
       </c>
       <c r="P59">
-        <v>96.10219609967371</v>
+        <v>98.0881235236737</v>
       </c>
       <c r="Q59">
-        <v>98.49219609967371</v>
+        <v>100.4781235236737</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1331834555133594</v>
+        <v>0.1331670888046543</v>
       </c>
       <c r="T59">
         <v>1.202640862803625</v>
       </c>
       <c r="U59">
-        <v>0.08966759442929167</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V59">
         <v>0.24</v>
       </c>
       <c r="W59">
-        <v>0.06814737176626168</v>
+        <v>0.06525937176626168</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.05077501101081</v>
+        <v>3.185784558196708</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +6168,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1003313300794097</v>
+        <v>0.09454983196190854</v>
       </c>
       <c r="C60">
-        <v>425.2377201662341</v>
+        <v>542.7529943499248</v>
       </c>
       <c r="D60">
-        <v>1118.429720166234</v>
+        <v>1235.944994349925</v>
       </c>
       <c r="E60">
         <v>-221.088</v>
@@ -6201,45 +6201,45 @@
         <v>188.11</v>
       </c>
       <c r="M60">
-        <v>69.24881343330854</v>
+        <v>60.08258623330854</v>
       </c>
       <c r="N60">
-        <v>118.8611865666915</v>
+        <v>128.0274137666915</v>
       </c>
       <c r="O60">
-        <v>28.52668477600595</v>
+        <v>30.72657930400595</v>
       </c>
       <c r="P60">
-        <v>90.33450179068552</v>
+        <v>97.30083446268551</v>
       </c>
       <c r="Q60">
-        <v>92.72450179068552</v>
+        <v>99.69083446268552</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1350152725118521</v>
+        <v>0.134998562708278</v>
       </c>
       <c r="T60">
         <v>1.227851790462909</v>
       </c>
       <c r="U60">
-        <v>0.09896759442929168</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V60">
         <v>0.24</v>
       </c>
       <c r="W60">
-        <v>0.07521537176626168</v>
+        <v>0.06525937176626168</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.716436436577547</v>
+        <v>3.1308572382278</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +6250,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1005210123813056</v>
+        <v>0.09463997383104659</v>
       </c>
       <c r="C61">
-        <v>409.6916632687435</v>
+        <v>528.6652220594196</v>
       </c>
       <c r="D61">
-        <v>1114.947663268744</v>
+        <v>1233.92122205942</v>
       </c>
       <c r="E61">
         <v>-209.0239999999999</v>
@@ -6283,45 +6283,45 @@
         <v>188.11</v>
       </c>
       <c r="M61">
-        <v>70.44275849250351</v>
+        <v>61.11849289250352</v>
       </c>
       <c r="N61">
-        <v>117.6672415074965</v>
+        <v>126.9915071074965</v>
       </c>
       <c r="O61">
-        <v>28.24013796179916</v>
+        <v>30.47796170579916</v>
       </c>
       <c r="P61">
-        <v>89.42710354569734</v>
+        <v>96.51354540169733</v>
       </c>
       <c r="Q61">
-        <v>91.81710354569734</v>
+        <v>98.90354540169733</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1369364464371005</v>
+        <v>0.1369193768023224</v>
       </c>
       <c r="T61">
         <v>1.254292519471427</v>
       </c>
       <c r="U61">
-        <v>0.09896759442929168</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V61">
         <v>0.24</v>
       </c>
       <c r="W61">
-        <v>0.07521537176626168</v>
+        <v>0.06525937176626168</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.670395141042334</v>
+        <v>3.077791861308684</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +6332,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1007106946832016</v>
+        <v>0.09473011570018464</v>
       </c>
       <c r="C62">
-        <v>394.1672207628395</v>
+        <v>514.5840665017344</v>
       </c>
       <c r="D62">
-        <v>1111.48722076284</v>
+        <v>1231.904066501734</v>
       </c>
       <c r="E62">
         <v>-196.9599999999999</v>
@@ -6365,45 +6365,45 @@
         <v>188.11</v>
       </c>
       <c r="M62">
-        <v>71.63670355169849</v>
+        <v>62.15439955169849</v>
       </c>
       <c r="N62">
-        <v>116.4732964483015</v>
+        <v>125.9556004483015</v>
       </c>
       <c r="O62">
-        <v>27.95359114759237</v>
+        <v>30.22934410759236</v>
       </c>
       <c r="P62">
-        <v>88.51970530070916</v>
+        <v>95.72625634070916</v>
       </c>
       <c r="Q62">
-        <v>90.90970530070916</v>
+        <v>98.11625634070916</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1389536790586114</v>
+        <v>0.1389362316010691</v>
       </c>
       <c r="T62">
         <v>1.28205528493037</v>
       </c>
       <c r="U62">
-        <v>0.09896759442929168</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V62">
         <v>0.24</v>
       </c>
       <c r="W62">
-        <v>0.07521537176626168</v>
+        <v>0.06525937176626168</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.625888555358295</v>
+        <v>3.026495330286874</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +6414,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1009003769850975</v>
+        <v>0.0984363375693227</v>
       </c>
       <c r="C63">
-        <v>378.6641920186464</v>
+        <v>424.9342433498982</v>
       </c>
       <c r="D63">
-        <v>1108.048192018646</v>
+        <v>1154.318243349898</v>
       </c>
       <c r="E63">
         <v>-184.896</v>
@@ -6447,37 +6447,37 @@
         <v>188.11</v>
       </c>
       <c r="M63">
-        <v>72.83064861089346</v>
+        <v>68.93035741089346</v>
       </c>
       <c r="N63">
-        <v>115.2793513891066</v>
+        <v>119.1796425891065</v>
       </c>
       <c r="O63">
-        <v>27.66704433338557</v>
+        <v>28.60311422138557</v>
       </c>
       <c r="P63">
-        <v>87.61230705572098</v>
+        <v>90.57652836772098</v>
       </c>
       <c r="Q63">
-        <v>90.00230705572098</v>
+        <v>92.96652836772098</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1410743595068664</v>
+        <v>0.1410565148510335</v>
       </c>
       <c r="T63">
         <v>1.311241781951311</v>
       </c>
       <c r="U63">
-        <v>0.09896759442929168</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V63">
         <v>0.24</v>
       </c>
       <c r="W63">
-        <v>0.07521537176626168</v>
+        <v>0.07118737176626168</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.582841201991766</v>
+        <v>2.728986285080134</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +6496,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1010900592869935</v>
+        <v>0.09858575943846076</v>
       </c>
       <c r="C64">
-        <v>363.1823788816896</v>
+        <v>409.9466803804896</v>
       </c>
       <c r="D64">
-        <v>1104.63037888169</v>
+        <v>1151.39468038049</v>
       </c>
       <c r="E64">
         <v>-172.8319999999999</v>
@@ -6529,37 +6529,37 @@
         <v>188.11</v>
       </c>
       <c r="M64">
-        <v>74.02459367008845</v>
+        <v>70.06036327008844</v>
       </c>
       <c r="N64">
-        <v>114.0854063299116</v>
+        <v>118.0496367299116</v>
       </c>
       <c r="O64">
-        <v>27.38049751917877</v>
+        <v>28.33191281517878</v>
       </c>
       <c r="P64">
-        <v>86.70490881073279</v>
+        <v>89.7177239147328</v>
       </c>
       <c r="Q64">
-        <v>89.09490881073279</v>
+        <v>92.1077239147328</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1433066547155558</v>
+        <v>0.1432883919562593</v>
       </c>
       <c r="T64">
         <v>1.341964410394407</v>
       </c>
       <c r="U64">
-        <v>0.09896759442929168</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V64">
         <v>0.24</v>
       </c>
       <c r="W64">
-        <v>0.07521537176626168</v>
+        <v>0.07118737176626168</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.541182472927382</v>
+        <v>2.68497037725626</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +6578,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1012797415888894</v>
+        <v>0.0987351813075988</v>
       </c>
       <c r="C65">
-        <v>347.7215856348331</v>
+        <v>394.9738891215217</v>
       </c>
       <c r="D65">
-        <v>1101.233585634833</v>
+        <v>1148.485889121522</v>
       </c>
       <c r="E65">
         <v>-160.7679999999999</v>
@@ -6611,37 +6611,37 @@
         <v>188.11</v>
       </c>
       <c r="M65">
-        <v>75.21853872928341</v>
+        <v>71.19036912928341</v>
       </c>
       <c r="N65">
-        <v>112.8914612707166</v>
+        <v>116.9196308707166</v>
       </c>
       <c r="O65">
-        <v>27.09395070497198</v>
+        <v>28.06071140897198</v>
       </c>
       <c r="P65">
-        <v>85.79751056574462</v>
+        <v>88.85891946174462</v>
       </c>
       <c r="Q65">
-        <v>88.18751056574462</v>
+        <v>91.24891946174462</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1456596145301204</v>
+        <v>0.1456409110671728</v>
       </c>
       <c r="T65">
         <v>1.374347721456047</v>
       </c>
       <c r="U65">
-        <v>0.09896759442929168</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V65">
         <v>0.24</v>
       </c>
       <c r="W65">
-        <v>0.07521537176626168</v>
+        <v>0.07118737176626168</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.500846243198377</v>
+        <v>2.642351799839495</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +6660,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1037555038907854</v>
+        <v>0.09888460317673683</v>
       </c>
       <c r="C66">
-        <v>293.1639804664245</v>
+        <v>380.0157579009164</v>
       </c>
       <c r="D66">
-        <v>1058.739980466425</v>
+        <v>1145.591757900916</v>
       </c>
       <c r="E66">
         <v>-148.7039999999998</v>
@@ -6693,45 +6693,45 @@
         <v>188.11</v>
       </c>
       <c r="M66">
-        <v>80.04133498847841</v>
+        <v>72.32037498847839</v>
       </c>
       <c r="N66">
-        <v>108.0686650115216</v>
+        <v>115.7896250115216</v>
       </c>
       <c r="O66">
-        <v>25.93647960276518</v>
+        <v>27.78951000276519</v>
       </c>
       <c r="P66">
-        <v>82.13218540875641</v>
+        <v>88.00011500875644</v>
       </c>
       <c r="Q66">
-        <v>84.52218540875641</v>
+        <v>90.39011500875644</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.148143294334383</v>
+        <v>0.1481241256842483</v>
       </c>
       <c r="T66">
         <v>1.408530105354446</v>
       </c>
       <c r="U66">
-        <v>0.1036675944292917</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V66">
         <v>0.24</v>
       </c>
       <c r="W66">
-        <v>0.07878737176626169</v>
+        <v>0.07118737176626168</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.35016070168092</v>
+        <v>2.601065052967003</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +6742,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1039809061926813</v>
+        <v>0.09903402504587491</v>
       </c>
       <c r="C67">
-        <v>277.3935164519296</v>
+        <v>365.0721761694003</v>
       </c>
       <c r="D67">
-        <v>1055.03351645193</v>
+        <v>1142.7121761694</v>
       </c>
       <c r="E67">
         <v>-136.6399999999999</v>
@@ -6775,45 +6775,45 @@
         <v>188.11</v>
       </c>
       <c r="M67">
-        <v>81.29198084767337</v>
+        <v>73.45038084767337</v>
       </c>
       <c r="N67">
-        <v>106.8180191523266</v>
+        <v>114.6596191523266</v>
       </c>
       <c r="O67">
-        <v>25.63632459655839</v>
+        <v>27.51830859655839</v>
       </c>
       <c r="P67">
-        <v>81.18169455576825</v>
+        <v>87.14131055576826</v>
       </c>
       <c r="Q67">
-        <v>83.57169455576825</v>
+        <v>89.53131055576826</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1507688986988892</v>
+        <v>0.1507492382794424</v>
       </c>
       <c r="T67">
         <v>1.444665768332754</v>
       </c>
       <c r="U67">
-        <v>0.1036675944292917</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V67">
         <v>0.24</v>
       </c>
       <c r="W67">
-        <v>0.07878737176626169</v>
+        <v>0.07118737176626168</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.314004383193522</v>
+        <v>2.561048667536741</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +6824,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1042063084945773</v>
+        <v>0.09918344691501296</v>
       </c>
       <c r="C68">
-        <v>261.6489132712912</v>
+        <v>350.1430344864297</v>
       </c>
       <c r="D68">
-        <v>1051.352913271291</v>
+        <v>1139.84703448643</v>
       </c>
       <c r="E68">
         <v>-124.5759999999999</v>
@@ -6857,45 +6857,45 @@
         <v>188.11</v>
       </c>
       <c r="M68">
-        <v>82.54262670686835</v>
+        <v>74.58038670686834</v>
       </c>
       <c r="N68">
-        <v>105.5673732931317</v>
+        <v>113.5296132931317</v>
       </c>
       <c r="O68">
-        <v>25.3361695903516</v>
+        <v>27.2471071903516</v>
       </c>
       <c r="P68">
-        <v>80.23120370278006</v>
+        <v>86.28250610278008</v>
       </c>
       <c r="Q68">
-        <v>82.62120370278006</v>
+        <v>88.67250610278008</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1535489503789546</v>
+        <v>0.153528769262589</v>
       </c>
       <c r="T68">
         <v>1.48292705854508</v>
       </c>
       <c r="U68">
-        <v>0.1036675944292917</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V68">
         <v>0.24</v>
       </c>
       <c r="W68">
-        <v>0.07878737176626169</v>
+        <v>0.07118737176626168</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.278943710720893</v>
+        <v>2.52224489984679</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +6906,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1044317107964732</v>
+        <v>0.101318748784151</v>
       </c>
       <c r="C69">
-        <v>245.9299012101472</v>
+        <v>298.6503587745841</v>
       </c>
       <c r="D69">
-        <v>1047.697901210147</v>
+        <v>1100.418358774584</v>
       </c>
       <c r="E69">
         <v>-112.5119999999998</v>
@@ -6939,37 +6939,37 @@
         <v>188.11</v>
       </c>
       <c r="M69">
-        <v>83.79327256606334</v>
+        <v>78.86271576606333</v>
       </c>
       <c r="N69">
-        <v>104.3167274339367</v>
+        <v>109.2472842339367</v>
       </c>
       <c r="O69">
-        <v>25.0360145841448</v>
+        <v>26.2193482161448</v>
       </c>
       <c r="P69">
-        <v>79.28071284979188</v>
+        <v>83.02793601779189</v>
       </c>
       <c r="Q69">
-        <v>81.67071284979188</v>
+        <v>85.41793601779189</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.15649749003963</v>
+        <v>0.1564767566689567</v>
       </c>
       <c r="T69">
         <v>1.523507214830879</v>
       </c>
       <c r="U69">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V69">
         <v>0.24</v>
       </c>
       <c r="W69">
-        <v>0.07878737176626169</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.244929625486252</v>
+        <v>2.385284328249683</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +6988,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1046571130983692</v>
+        <v>0.1014978106532891</v>
       </c>
       <c r="C70">
-        <v>230.2362142917755</v>
+        <v>283.4035589602915</v>
       </c>
       <c r="D70">
-        <v>1044.068214291776</v>
+        <v>1097.235558960292</v>
       </c>
       <c r="E70">
         <v>-100.4479999999999</v>
@@ -7021,37 +7021,37 @@
         <v>188.11</v>
       </c>
       <c r="M70">
-        <v>85.0439184252583</v>
+        <v>80.03977122525829</v>
       </c>
       <c r="N70">
-        <v>103.0660815747417</v>
+        <v>108.0702287747417</v>
       </c>
       <c r="O70">
-        <v>24.73585957793801</v>
+        <v>25.93685490593801</v>
       </c>
       <c r="P70">
-        <v>78.3302219968037</v>
+        <v>82.13337386880372</v>
       </c>
       <c r="Q70">
-        <v>80.7202219968037</v>
+        <v>84.52337386880372</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1596303134290976</v>
+        <v>0.1596089932882223</v>
       </c>
       <c r="T70">
         <v>1.566623630884542</v>
       </c>
       <c r="U70">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V70">
         <v>0.24</v>
       </c>
       <c r="W70">
-        <v>0.07878737176626169</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.211915954523219</v>
+        <v>2.350206617540128</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +7070,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1048825154002651</v>
+        <v>0.1016768725224271</v>
       </c>
       <c r="C71">
-        <v>214.5675902125679</v>
+        <v>268.1751176165003</v>
       </c>
       <c r="D71">
-        <v>1040.463590212568</v>
+        <v>1094.0711176165</v>
       </c>
       <c r="E71">
         <v>-88.38399999999979</v>
@@ -7103,37 +7103,37 @@
         <v>188.11</v>
       </c>
       <c r="M71">
-        <v>86.29456428445329</v>
+        <v>81.21682668445328</v>
       </c>
       <c r="N71">
-        <v>101.8154357155467</v>
+        <v>106.8931733155467</v>
       </c>
       <c r="O71">
-        <v>24.43570457173121</v>
+        <v>25.65436159573121</v>
       </c>
       <c r="P71">
-        <v>77.37973114381552</v>
+        <v>81.23881171981552</v>
       </c>
       <c r="Q71">
-        <v>79.76973114381552</v>
+        <v>83.62881171981552</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1629652544565954</v>
+        <v>0.1629433096893761</v>
       </c>
       <c r="T71">
         <v>1.612521751199731</v>
       </c>
       <c r="U71">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V71">
         <v>0.24</v>
       </c>
       <c r="W71">
-        <v>0.07878737176626169</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.179859201559115</v>
+        <v>2.316145652068532</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +7152,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1051079177021611</v>
+        <v>0.1018559343915652</v>
       </c>
       <c r="C72">
-        <v>198.923770278847</v>
+        <v>252.9648763617962</v>
       </c>
       <c r="D72">
-        <v>1036.883770278847</v>
+        <v>1090.924876361796</v>
       </c>
       <c r="E72">
         <v>-76.31999999999982</v>
@@ -7185,37 +7185,37 @@
         <v>188.11</v>
       </c>
       <c r="M72">
-        <v>87.54521014364826</v>
+        <v>82.39388214364826</v>
       </c>
       <c r="N72">
-        <v>100.5647898563518</v>
+        <v>105.7161178563518</v>
       </c>
       <c r="O72">
-        <v>24.13554956552442</v>
+        <v>25.37186828552442</v>
       </c>
       <c r="P72">
-        <v>76.42924029082732</v>
+        <v>80.34424957082734</v>
       </c>
       <c r="Q72">
-        <v>78.81924029082732</v>
+        <v>82.73424957082734</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1665225248859263</v>
+        <v>0.1664999138506067</v>
       </c>
       <c r="T72">
         <v>1.661479746202599</v>
       </c>
       <c r="U72">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V72">
         <v>0.24</v>
       </c>
       <c r="W72">
-        <v>0.07878737176626169</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.148718355822556</v>
+        <v>2.283057857038982</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +7234,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.105333320004057</v>
+        <v>0.1020349962607032</v>
       </c>
       <c r="C73">
-        <v>183.3044993449731</v>
+        <v>237.7726786313816</v>
       </c>
       <c r="D73">
-        <v>1033.328499344973</v>
+        <v>1087.796678631382</v>
       </c>
       <c r="E73">
         <v>-64.25599999999997</v>
@@ -7267,37 +7267,37 @@
         <v>188.11</v>
       </c>
       <c r="M73">
-        <v>88.79585600284322</v>
+        <v>83.57093760284322</v>
       </c>
       <c r="N73">
-        <v>99.31414399715679</v>
+        <v>104.5390623971568</v>
       </c>
       <c r="O73">
-        <v>23.83539455931763</v>
+        <v>25.08937497531763</v>
       </c>
       <c r="P73">
-        <v>75.47874943783916</v>
+        <v>79.44968742183917</v>
       </c>
       <c r="Q73">
-        <v>77.86874943783916</v>
+        <v>81.83968742183917</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1703251243103835</v>
+        <v>0.1703018010574394</v>
       </c>
       <c r="T73">
         <v>1.71381415465394</v>
       </c>
       <c r="U73">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V73">
         <v>0.24</v>
       </c>
       <c r="W73">
-        <v>0.07878737176626169</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.118454717008154</v>
+        <v>2.250902112573645</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +7316,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.105558722305953</v>
+        <v>0.1022140581298413</v>
       </c>
       <c r="C74">
-        <v>167.7095257527257</v>
+        <v>222.5983696511058</v>
       </c>
       <c r="D74">
-        <v>1029.797525752726</v>
+        <v>1084.686369651106</v>
       </c>
       <c r="E74">
         <v>-52.19199999999989</v>
@@ -7349,37 +7349,37 @@
         <v>188.11</v>
       </c>
       <c r="M74">
-        <v>90.0465018620382</v>
+        <v>84.74799306203819</v>
       </c>
       <c r="N74">
-        <v>98.06349813796182</v>
+        <v>103.3620069379618</v>
       </c>
       <c r="O74">
-        <v>23.53523955311083</v>
+        <v>24.80688166511084</v>
       </c>
       <c r="P74">
-        <v>74.52825858485099</v>
+        <v>78.55512527285099</v>
       </c>
       <c r="Q74">
-        <v>76.91825858485099</v>
+        <v>80.94512527285099</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1743993379794448</v>
+        <v>0.1743752516361888</v>
       </c>
       <c r="T74">
         <v>1.769886735137521</v>
       </c>
       <c r="U74">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V74">
         <v>0.24</v>
       </c>
       <c r="W74">
-        <v>0.07878737176626169</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.089031734827485</v>
+        <v>2.219639583232344</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +7398,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1057841246078489</v>
+        <v>0.1023931199989793</v>
       </c>
       <c r="C75">
-        <v>152.1386012719242</v>
+        <v>207.4417964119384</v>
       </c>
       <c r="D75">
-        <v>1026.290601271924</v>
+        <v>1081.593796411938</v>
       </c>
       <c r="E75">
         <v>-40.12799999999993</v>
@@ -7431,37 +7431,37 @@
         <v>188.11</v>
       </c>
       <c r="M75">
-        <v>91.29714772123317</v>
+        <v>85.92504852123317</v>
       </c>
       <c r="N75">
-        <v>96.81285227876684</v>
+        <v>102.1849514787668</v>
       </c>
       <c r="O75">
-        <v>23.23508454690404</v>
+        <v>24.52438835490404</v>
       </c>
       <c r="P75">
-        <v>73.57776773186279</v>
+        <v>77.6605631238628</v>
       </c>
       <c r="Q75">
-        <v>75.96776773186279</v>
+        <v>80.0505631238628</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1787753452536218</v>
+        <v>0.1787504392948456</v>
       </c>
       <c r="T75">
         <v>1.830112840101366</v>
       </c>
       <c r="U75">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V75">
         <v>0.24</v>
       </c>
       <c r="W75">
-        <v>0.07878737176626169</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.060414861747656</v>
+        <v>2.18923356154423</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +7480,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1060095269097449</v>
+        <v>0.1025721818681174</v>
       </c>
       <c r="C76">
-        <v>136.5914810422539</v>
+        <v>192.3028076448775</v>
       </c>
       <c r="D76">
-        <v>1022.807481042254</v>
+        <v>1078.518807644878</v>
       </c>
       <c r="E76">
         <v>-28.06399999999985</v>
@@ -7513,37 +7513,37 @@
         <v>188.11</v>
       </c>
       <c r="M76">
-        <v>92.54779358042815</v>
+        <v>87.10210398042814</v>
       </c>
       <c r="N76">
-        <v>95.56220641957187</v>
+        <v>101.0078960195719</v>
       </c>
       <c r="O76">
-        <v>22.93492954069725</v>
+        <v>24.24189504469725</v>
       </c>
       <c r="P76">
-        <v>72.62727687887462</v>
+        <v>76.76600097487463</v>
       </c>
       <c r="Q76">
-        <v>75.01727687887463</v>
+        <v>79.15600097487463</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1834879684719662</v>
+        <v>0.1834621798503221</v>
       </c>
       <c r="T76">
         <v>1.894971722370123</v>
       </c>
       <c r="U76">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V76">
         <v>0.24</v>
       </c>
       <c r="W76">
-        <v>0.07878737176626169</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.032571417669986</v>
+        <v>2.159649324226064</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +7562,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1062349292116408</v>
+        <v>0.1027512437372554</v>
       </c>
       <c r="C77">
-        <v>121.0679235162744</v>
+        <v>177.181253796285</v>
       </c>
       <c r="D77">
-        <v>1019.347923516274</v>
+        <v>1075.461253796285</v>
       </c>
       <c r="E77">
         <v>-15.99999999999989</v>
@@ -7595,37 +7595,37 @@
         <v>188.11</v>
       </c>
       <c r="M77">
-        <v>93.79843943962312</v>
+        <v>88.27915943962311</v>
       </c>
       <c r="N77">
-        <v>94.31156056037689</v>
+        <v>99.8308405603769</v>
       </c>
       <c r="O77">
-        <v>22.63477453449045</v>
+        <v>23.95940173449046</v>
       </c>
       <c r="P77">
-        <v>71.67678602588643</v>
+        <v>75.87143882588644</v>
       </c>
       <c r="Q77">
-        <v>74.06678602588643</v>
+        <v>78.26143882588644</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1885776015477782</v>
+        <v>0.1885508596502368</v>
       </c>
       <c r="T77">
         <v>1.965019315220381</v>
       </c>
       <c r="U77">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V77">
         <v>0.24</v>
       </c>
       <c r="W77">
-        <v>0.07878737176626169</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.005470465434386</v>
+        <v>2.13085399990305</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1158752115135368</v>
+        <v>0.1029303056063935</v>
       </c>
       <c r="C78">
-        <v>-19.82185850985229</v>
+        <v>162.0769870036415</v>
       </c>
       <c r="D78">
-        <v>890.5221414901478</v>
+        <v>1072.420987003642</v>
       </c>
       <c r="E78">
         <v>-3.935999999999922</v>
@@ -7677,45 +7677,45 @@
         <v>188.11</v>
       </c>
       <c r="M78">
-        <v>109.9939684988181</v>
+        <v>89.45621489881809</v>
       </c>
       <c r="N78">
-        <v>78.11603150118191</v>
+        <v>98.65378510118192</v>
       </c>
       <c r="O78">
-        <v>18.74784756028366</v>
+        <v>23.67690842428366</v>
       </c>
       <c r="P78">
-        <v>59.36818394089825</v>
+        <v>74.97687667689826</v>
       </c>
       <c r="Q78">
-        <v>61.75818394089825</v>
+        <v>77.36687667689826</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1940913707132412</v>
+        <v>0.1940635961001443</v>
       </c>
       <c r="T78">
         <v>2.040904207474826</v>
       </c>
       <c r="U78">
-        <v>0.1199675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V78">
         <v>0.24</v>
       </c>
       <c r="W78">
-        <v>0.09117537176626168</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.710184681644805</v>
+        <v>2.102816447272747</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +7726,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1162244938154327</v>
+        <v>0.1031093674755315</v>
       </c>
       <c r="C79">
-        <v>-35.94494042889426</v>
+        <v>146.9898610717089</v>
       </c>
       <c r="D79">
-        <v>886.4630595711059</v>
+        <v>1069.397861071709</v>
       </c>
       <c r="E79">
         <v>8.128000000000156</v>
@@ -7759,45 +7759,45 @@
         <v>188.11</v>
       </c>
       <c r="M79">
-        <v>111.4412575580131</v>
+        <v>90.63327035801308</v>
       </c>
       <c r="N79">
-        <v>76.66874244198692</v>
+        <v>97.47672964198694</v>
       </c>
       <c r="O79">
-        <v>18.40049818607686</v>
+        <v>23.39441511407686</v>
       </c>
       <c r="P79">
-        <v>58.26824425591006</v>
+        <v>74.08231452791007</v>
       </c>
       <c r="Q79">
-        <v>60.65824425591006</v>
+        <v>76.47231452791007</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2000845980670053</v>
+        <v>0.2000557009370003</v>
       </c>
       <c r="T79">
         <v>2.123387786012267</v>
       </c>
       <c r="U79">
-        <v>0.1199675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V79">
         <v>0.24</v>
       </c>
       <c r="W79">
-        <v>0.09117537176626168</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.687974490974093</v>
+        <v>2.075507142762711</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +7808,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1165737761173287</v>
+        <v>0.1032884293446696</v>
       </c>
       <c r="C80">
-        <v>-52.03118690897452</v>
+        <v>131.919731449097</v>
       </c>
       <c r="D80">
-        <v>882.4408130910256</v>
+        <v>1066.391731449097</v>
       </c>
       <c r="E80">
         <v>20.19200000000012</v>
@@ -7841,45 +7841,45 @@
         <v>188.11</v>
       </c>
       <c r="M80">
-        <v>112.8885466172081</v>
+        <v>91.81032581720804</v>
       </c>
       <c r="N80">
-        <v>75.22145338279195</v>
+        <v>96.29967418279197</v>
       </c>
       <c r="O80">
-        <v>18.05314881187007</v>
+        <v>23.11192180387007</v>
       </c>
       <c r="P80">
-        <v>57.16830457092188</v>
+        <v>73.1877523789219</v>
       </c>
       <c r="Q80">
-        <v>59.55830457092188</v>
+        <v>75.5777523789219</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2066226642711116</v>
+        <v>0.2065925425772068</v>
       </c>
       <c r="T80">
         <v>2.213369871689476</v>
       </c>
       <c r="U80">
-        <v>0.1199675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V80">
         <v>0.24</v>
       </c>
       <c r="W80">
-        <v>0.09117537176626168</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y80">
-        <v>1.666333792371862</v>
+        <v>2.048898076829856</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +7890,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1169230584192246</v>
+        <v>0.1034674912138077</v>
       </c>
       <c r="C81">
-        <v>-68.0810970977393</v>
+        <v>116.8664552052234</v>
       </c>
       <c r="D81">
-        <v>878.4549029022609</v>
+        <v>1063.402455205224</v>
       </c>
       <c r="E81">
         <v>32.2560000000002</v>
@@ -7923,45 +7923,45 @@
         <v>188.11</v>
       </c>
       <c r="M81">
-        <v>114.3358356764031</v>
+        <v>92.98738127640303</v>
       </c>
       <c r="N81">
-        <v>73.77416432359696</v>
+        <v>95.12261872359699</v>
       </c>
       <c r="O81">
-        <v>17.70579943766327</v>
+        <v>22.82942849366328</v>
       </c>
       <c r="P81">
-        <v>56.06836488593369</v>
+        <v>72.29319022993371</v>
       </c>
       <c r="Q81">
-        <v>58.45836488593369</v>
+        <v>74.68319022993371</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2137834034470376</v>
+        <v>0.2137519405640997</v>
       </c>
       <c r="T81">
         <v>2.311921679812133</v>
       </c>
       <c r="U81">
-        <v>0.1199675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V81">
         <v>0.24</v>
       </c>
       <c r="W81">
-        <v>0.09117537176626168</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y81">
-        <v>1.645240959557028</v>
+        <v>2.022962658135807</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +7972,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1172723407211206</v>
+        <v>0.1122801530829457</v>
       </c>
       <c r="C82">
-        <v>-84.09516116495604</v>
+        <v>-24.11862226332016</v>
       </c>
       <c r="D82">
-        <v>874.5048388350441</v>
+        <v>934.48137773668</v>
       </c>
       <c r="E82">
         <v>44.32000000000016</v>
@@ -8005,37 +8005,37 @@
         <v>188.11</v>
       </c>
       <c r="M82">
-        <v>115.783124735598</v>
+        <v>107.869140735598</v>
       </c>
       <c r="N82">
-        <v>72.32687526440199</v>
+        <v>80.240859264402</v>
       </c>
       <c r="O82">
-        <v>17.35845006345648</v>
+        <v>19.25780622345648</v>
       </c>
       <c r="P82">
-        <v>54.96842520094552</v>
+        <v>60.98305304094552</v>
       </c>
       <c r="Q82">
-        <v>57.35842520094552</v>
+        <v>63.37305304094552</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2216602165405561</v>
+        <v>0.2216272783496819</v>
       </c>
       <c r="T82">
         <v>2.420328668747055</v>
       </c>
       <c r="U82">
-        <v>0.1199675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V82">
         <v>0.24</v>
       </c>
       <c r="W82">
-        <v>0.09117537176626168</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.624675447562565</v>
+        <v>1.743872239244802</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +8054,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1176216230230165</v>
+        <v>0.1125671349520838</v>
       </c>
       <c r="C83">
-        <v>-100.073860503462</v>
+        <v>-39.85741684001823</v>
       </c>
       <c r="D83">
-        <v>870.5901394965381</v>
+        <v>930.8065831599819</v>
       </c>
       <c r="E83">
         <v>56.38400000000013</v>
@@ -8087,37 +8087,37 @@
         <v>188.11</v>
       </c>
       <c r="M83">
-        <v>117.230413794793</v>
+        <v>109.217504994793</v>
       </c>
       <c r="N83">
-        <v>70.87958620520703</v>
+        <v>78.89249500520704</v>
       </c>
       <c r="O83">
-        <v>17.01110068924969</v>
+        <v>18.93419880124969</v>
       </c>
       <c r="P83">
-        <v>53.86848551595735</v>
+        <v>59.95829620395735</v>
       </c>
       <c r="Q83">
-        <v>56.25848551595735</v>
+        <v>62.34829620395735</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.230366167854445</v>
+        <v>0.2303315990600622</v>
       </c>
       <c r="T83">
         <v>2.540146919675127</v>
       </c>
       <c r="U83">
-        <v>0.1199675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V83">
         <v>0.24</v>
       </c>
       <c r="W83">
-        <v>0.09117537176626168</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.604617725987719</v>
+        <v>1.722342952340546</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +8136,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1179709053249125</v>
+        <v>0.1128541168212218</v>
       </c>
       <c r="C84">
-        <v>-116.017667924735</v>
+        <v>-55.56742278731883</v>
       </c>
       <c r="D84">
-        <v>866.7103320752652</v>
+        <v>927.1605772126813</v>
       </c>
       <c r="E84">
         <v>68.44800000000021</v>
@@ -8169,37 +8169,37 @@
         <v>188.11</v>
       </c>
       <c r="M84">
-        <v>118.677702853988</v>
+        <v>110.565869253988</v>
       </c>
       <c r="N84">
-        <v>69.43229714601205</v>
+        <v>77.54413074601206</v>
       </c>
       <c r="O84">
-        <v>16.66375131504289</v>
+        <v>18.61059137904289</v>
       </c>
       <c r="P84">
-        <v>52.76854583096916</v>
+        <v>58.93353936696916</v>
       </c>
       <c r="Q84">
-        <v>55.15854583096916</v>
+        <v>61.32353936696916</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2400394470920994</v>
+        <v>0.2400030665160403</v>
       </c>
       <c r="T84">
         <v>2.673278309595208</v>
       </c>
       <c r="U84">
-        <v>0.1199675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V84">
         <v>0.24</v>
       </c>
       <c r="W84">
-        <v>0.09117537176626168</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.58504921713421</v>
+        <v>1.701338769994929</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +8218,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1183201876268084</v>
+        <v>0.1131410986903599</v>
       </c>
       <c r="C85">
-        <v>-131.927047849261</v>
+        <v>-71.24897708383958</v>
       </c>
       <c r="D85">
-        <v>862.8649521507391</v>
+        <v>923.5430229161606</v>
       </c>
       <c r="E85">
         <v>80.51200000000017</v>
@@ -8251,37 +8251,37 @@
         <v>188.11</v>
       </c>
       <c r="M85">
-        <v>120.1249919131829</v>
+        <v>111.9142335131829</v>
       </c>
       <c r="N85">
-        <v>67.98500808681707</v>
+        <v>76.19576648681709</v>
       </c>
       <c r="O85">
-        <v>16.3164019408361</v>
+        <v>18.2869839568361</v>
       </c>
       <c r="P85">
-        <v>51.66860614598097</v>
+        <v>57.90878252998099</v>
       </c>
       <c r="Q85">
-        <v>54.05860614598097</v>
+        <v>60.29878252998099</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2508507591812426</v>
+        <v>0.2508123536727218</v>
       </c>
       <c r="T85">
         <v>2.822072215976474</v>
       </c>
       <c r="U85">
-        <v>0.1199675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V85">
         <v>0.24</v>
       </c>
       <c r="W85">
-        <v>0.09117537176626168</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.565952238614521</v>
+        <v>1.680840712525111</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +8300,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1186694699287044</v>
+        <v>0.1134280805594979</v>
       </c>
       <c r="C86">
-        <v>-147.8024564918579</v>
+        <v>-86.90241146940571</v>
       </c>
       <c r="D86">
-        <v>859.0535435081422</v>
+        <v>919.9535885305944</v>
       </c>
       <c r="E86">
         <v>92.57600000000014</v>
@@ -8333,37 +8333,37 @@
         <v>188.11</v>
       </c>
       <c r="M86">
-        <v>121.5722809723779</v>
+        <v>113.2625977723779</v>
       </c>
       <c r="N86">
-        <v>66.5377190276221</v>
+        <v>74.84740222762211</v>
       </c>
       <c r="O86">
-        <v>15.9690525666293</v>
+        <v>17.9633765346293</v>
       </c>
       <c r="P86">
-        <v>50.5686664609928</v>
+        <v>56.88402569299281</v>
       </c>
       <c r="Q86">
-        <v>52.9586664609928</v>
+        <v>59.27402569299281</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2630134852815284</v>
+        <v>0.2629728017239882</v>
       </c>
       <c r="T86">
         <v>2.989465360655396</v>
       </c>
       <c r="U86">
-        <v>0.1199675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V86">
         <v>0.24</v>
       </c>
       <c r="W86">
-        <v>0.09117537176626168</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.547309950059586</v>
+        <v>1.660830704042669</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +8382,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1190187522306003</v>
+        <v>0.113715062428636</v>
       </c>
       <c r="C87">
-        <v>-163.6443420421031</v>
+        <v>-102.5280525464607</v>
       </c>
       <c r="D87">
-        <v>855.275657957897</v>
+        <v>916.3919474535394</v>
       </c>
       <c r="E87">
         <v>104.6400000000001</v>
@@ -8415,37 +8415,37 @@
         <v>188.11</v>
       </c>
       <c r="M87">
-        <v>123.0195700315729</v>
+        <v>114.6109620315729</v>
       </c>
       <c r="N87">
-        <v>65.09042996842713</v>
+        <v>73.49903796842715</v>
       </c>
       <c r="O87">
-        <v>15.62170319242251</v>
+        <v>17.63976911242251</v>
       </c>
       <c r="P87">
-        <v>49.46872677600462</v>
+        <v>55.85926885600463</v>
       </c>
       <c r="Q87">
-        <v>51.85872677600462</v>
+        <v>58.24926885600463</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2767979081951858</v>
+        <v>0.276754642848757</v>
       </c>
       <c r="T87">
         <v>3.179177591291511</v>
       </c>
       <c r="U87">
-        <v>0.1199675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V87">
         <v>0.24</v>
       </c>
       <c r="W87">
-        <v>0.09117537176626168</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.529106303588297</v>
+        <v>1.641291519289226</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +8464,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1193680345324963</v>
+        <v>0.114002044297774</v>
       </c>
       <c r="C88">
-        <v>-179.453144840028</v>
+        <v>-118.1262218791305</v>
       </c>
       <c r="D88">
-        <v>851.5308551599721</v>
+        <v>912.8577781208696</v>
       </c>
       <c r="E88">
         <v>116.7040000000002</v>
@@ -8497,37 +8497,37 @@
         <v>188.11</v>
       </c>
       <c r="M88">
-        <v>124.4668590907679</v>
+        <v>115.9593262907678</v>
       </c>
       <c r="N88">
-        <v>63.64314090923214</v>
+        <v>72.15067370923217</v>
       </c>
       <c r="O88">
-        <v>15.27435381821571</v>
+        <v>17.31616169021572</v>
       </c>
       <c r="P88">
-        <v>48.36878709101643</v>
+        <v>54.83451201901644</v>
       </c>
       <c r="Q88">
-        <v>50.75878709101643</v>
+        <v>57.22451201901644</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2925515343822229</v>
+        <v>0.2925053184199213</v>
       </c>
       <c r="T88">
         <v>3.395991569161355</v>
       </c>
       <c r="U88">
-        <v>0.1199675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V88">
         <v>0.24</v>
       </c>
       <c r="W88">
-        <v>0.09117537176626168</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.511325997732619</v>
+        <v>1.622206734181212</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +8546,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1645432678425046</v>
+        <v>0.1142890261669121</v>
       </c>
       <c r="C89">
-        <v>-499.3904744818807</v>
+        <v>-133.6972360900046</v>
       </c>
       <c r="D89">
-        <v>543.6575255181193</v>
+        <v>909.3507639099954</v>
       </c>
       <c r="E89">
         <v>128.768</v>
@@ -8579,45 +8579,45 @@
         <v>188.11</v>
       </c>
       <c r="M89">
-        <v>194.5558953499628</v>
+        <v>117.3076905499628</v>
       </c>
       <c r="N89">
-        <v>-6.445895349962797</v>
+        <v>70.8023094500372</v>
       </c>
       <c r="O89">
-        <v>-1.547014883991071</v>
+        <v>16.99255426800893</v>
       </c>
       <c r="P89">
-        <v>-4.898880465971725</v>
+        <v>53.80975518202827</v>
       </c>
       <c r="Q89">
-        <v>-2.508880465971725</v>
+        <v>56.19975518202827</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3130451883240332</v>
+        <v>0.3106791748481879</v>
       </c>
       <c r="T89">
-        <v>3.678041592404137</v>
+        <v>3.64616154362656</v>
       </c>
       <c r="U89">
-        <v>0.1853675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V89">
-        <v>0.232048481074252</v>
+        <v>0.24</v>
       </c>
       <c r="W89">
-        <v>0.1423533257015866</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.9668686711427168</v>
+        <v>1.603560679765336</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +8628,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1659389437867975</v>
+        <v>0.1145760080360501</v>
       </c>
       <c r="C90">
-        <v>-517.4600836578003</v>
+        <v>-149.2414069546961</v>
       </c>
       <c r="D90">
-        <v>537.6519163421998</v>
+        <v>905.870593045304</v>
       </c>
       <c r="E90">
         <v>140.8320000000001</v>
@@ -8661,45 +8661,45 @@
         <v>188.11</v>
       </c>
       <c r="M90">
-        <v>196.7921700091578</v>
+        <v>118.6560548091578</v>
       </c>
       <c r="N90">
-        <v>-8.682170009157772</v>
+        <v>69.45394519084222</v>
       </c>
       <c r="O90">
-        <v>-2.083720802197865</v>
+        <v>16.66894684580213</v>
       </c>
       <c r="P90">
-        <v>-6.598449206959907</v>
+        <v>52.78499834504009</v>
       </c>
       <c r="Q90">
-        <v>-4.208449206959907</v>
+        <v>55.17499834504009</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3353156206843693</v>
+        <v>0.3318820073478322</v>
       </c>
       <c r="T90">
-        <v>3.984545058437815</v>
+        <v>3.938026513835967</v>
       </c>
       <c r="U90">
-        <v>0.1853675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V90">
-        <v>0.2294115665165901</v>
+        <v>0.24</v>
       </c>
       <c r="W90">
-        <v>0.1428421242098559</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.9558815271524587</v>
+        <v>1.585338399313457</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +8710,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1673346197310905</v>
+        <v>0.1148629899051882</v>
       </c>
       <c r="C91">
-        <v>-535.3984584856352</v>
+        <v>-164.7590414942347</v>
       </c>
       <c r="D91">
-        <v>531.777541514365</v>
+        <v>902.4169585057655</v>
       </c>
       <c r="E91">
         <v>152.8960000000002</v>
@@ -8743,45 +8743,45 @@
         <v>188.11</v>
       </c>
       <c r="M91">
-        <v>199.0284446683528</v>
+        <v>120.0044190683528</v>
       </c>
       <c r="N91">
-        <v>-10.91844466835278</v>
+        <v>68.10558093164724</v>
       </c>
       <c r="O91">
-        <v>-2.620426720404666</v>
+        <v>16.34533942359534</v>
       </c>
       <c r="P91">
-        <v>-8.298017947948111</v>
+        <v>51.76024150805191</v>
       </c>
       <c r="Q91">
-        <v>-5.90801794794811</v>
+        <v>54.15024150805191</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3616352225647665</v>
+        <v>0.3569399003019573</v>
       </c>
       <c r="T91">
-        <v>4.346776427386708</v>
+        <v>4.282957842265265</v>
       </c>
       <c r="U91">
-        <v>0.1853675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V91">
-        <v>0.2268339084658418</v>
+        <v>0.24</v>
       </c>
       <c r="W91">
-        <v>0.1433199384819844</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.9451412852743409</v>
+        <v>1.567525608309935</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +8792,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1687302956753834</v>
+        <v>0.1151499717743263</v>
       </c>
       <c r="C92">
-        <v>-553.2098540663628</v>
+        <v>-180.2504420653585</v>
       </c>
       <c r="D92">
-        <v>526.0301459336374</v>
+        <v>898.9895579346418</v>
       </c>
       <c r="E92">
         <v>164.9600000000003</v>
@@ -8825,45 +8825,45 @@
         <v>188.11</v>
       </c>
       <c r="M92">
-        <v>201.2647193275478</v>
+        <v>121.3527833275478</v>
       </c>
       <c r="N92">
-        <v>-13.15471932754775</v>
+        <v>66.75721667245224</v>
       </c>
       <c r="O92">
-        <v>-3.15713263861146</v>
+        <v>16.02173200138854</v>
       </c>
       <c r="P92">
-        <v>-9.997586688936291</v>
+        <v>50.7354846710637</v>
       </c>
       <c r="Q92">
-        <v>-7.607586688936291</v>
+        <v>53.1254846710637</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3932187448212433</v>
+        <v>0.3870093718469074</v>
       </c>
       <c r="T92">
-        <v>4.781454070125379</v>
+        <v>4.696875436380424</v>
       </c>
       <c r="U92">
-        <v>0.1853675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V92">
-        <v>0.2243135317051103</v>
+        <v>0.24</v>
       </c>
       <c r="W92">
-        <v>0.1437871346591768</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.9346397154379594</v>
+        <v>1.550108657106491</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +8874,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1701259716196763</v>
+        <v>0.1154369536434643</v>
       </c>
       <c r="C93">
-        <v>-570.8983435131352</v>
+        <v>-195.7159064487532</v>
       </c>
       <c r="D93">
-        <v>520.4056564868649</v>
+        <v>895.5880935512469</v>
       </c>
       <c r="E93">
         <v>177.0240000000001</v>
@@ -8907,45 +8907,45 @@
         <v>188.11</v>
       </c>
       <c r="M93">
-        <v>203.5009939867427</v>
+        <v>122.7011475867427</v>
       </c>
       <c r="N93">
-        <v>-15.3909939867427</v>
+        <v>65.40885241325729</v>
       </c>
       <c r="O93">
-        <v>-3.693838556818248</v>
+        <v>15.69812457918175</v>
       </c>
       <c r="P93">
-        <v>-11.69715542992445</v>
+        <v>49.71072783407554</v>
       </c>
       <c r="Q93">
-        <v>-9.307155429924451</v>
+        <v>52.10072783407554</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4318208275791592</v>
+        <v>0.4237609481796242</v>
       </c>
       <c r="T93">
-        <v>5.312726744583755</v>
+        <v>5.202774718076729</v>
       </c>
       <c r="U93">
-        <v>0.1853675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V93">
-        <v>0.221848547840219</v>
+        <v>0.24</v>
       </c>
       <c r="W93">
-        <v>0.1442440627885186</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.9243689493342457</v>
+        <v>1.533074496039387</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1715216475639692</v>
+        <v>0.1157239355126023</v>
       </c>
       <c r="C94">
-        <v>-588.4678275777231</v>
+        <v>-211.1557279352988</v>
       </c>
       <c r="D94">
-        <v>514.900172422277</v>
+        <v>892.2122720647013</v>
       </c>
       <c r="E94">
         <v>189.0880000000002</v>
@@ -8989,45 +8989,45 @@
         <v>188.11</v>
       </c>
       <c r="M94">
-        <v>205.7372686459377</v>
+        <v>124.0495118459377</v>
       </c>
       <c r="N94">
-        <v>-17.6272686459377</v>
+        <v>64.06048815406231</v>
       </c>
       <c r="O94">
-        <v>-4.230544475025049</v>
+        <v>15.37451715697495</v>
       </c>
       <c r="P94">
-        <v>-13.39672417091266</v>
+        <v>48.68597099708736</v>
       </c>
       <c r="Q94">
-        <v>-11.00672417091265</v>
+        <v>51.07597099708736</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4800734310265543</v>
+        <v>0.4697004185955204</v>
       </c>
       <c r="T94">
-        <v>5.976817587656726</v>
+        <v>5.83514882019711</v>
       </c>
       <c r="U94">
-        <v>0.1853675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V94">
-        <v>0.2194371505810861</v>
+        <v>0.24</v>
       </c>
       <c r="W94">
-        <v>0.1446910576976575</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.9143214607545255</v>
+        <v>1.516410642821567</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +9038,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1729173235082621</v>
+        <v>0.1160109173817404</v>
       </c>
       <c r="C95">
-        <v>-605.9220436723126</v>
+        <v>-226.5701954103688</v>
       </c>
       <c r="D95">
-        <v>509.5099563276876</v>
+        <v>888.8618045896314</v>
       </c>
       <c r="E95">
         <v>201.1520000000003</v>
@@ -9071,45 +9071,45 @@
         <v>188.11</v>
       </c>
       <c r="M95">
-        <v>207.9735433051327</v>
+        <v>125.3978761051327</v>
       </c>
       <c r="N95">
-        <v>-19.86354330513268</v>
+        <v>62.71212389486733</v>
       </c>
       <c r="O95">
-        <v>-4.767250393231843</v>
+        <v>15.05090973476816</v>
       </c>
       <c r="P95">
-        <v>-15.09629291190084</v>
+        <v>47.66121416009917</v>
       </c>
       <c r="Q95">
-        <v>-12.70629291190084</v>
+        <v>50.05121416009917</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5421124926017763</v>
+        <v>0.5287654519873867</v>
       </c>
       <c r="T95">
-        <v>6.830648671607688</v>
+        <v>6.648201237209029</v>
       </c>
       <c r="U95">
-        <v>0.1853675944292917</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V95">
-        <v>0.2170776113275261</v>
+        <v>0.24</v>
       </c>
       <c r="W95">
-        <v>0.1451284398130514</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.9044900471980253</v>
+        <v>1.50010515203854</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +9120,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1743129994525551</v>
+        <v>0.1576388272383233</v>
       </c>
       <c r="C96">
-        <v>-623.2645743305088</v>
+        <v>-552.0738475401126</v>
       </c>
       <c r="D96">
-        <v>504.2314256694913</v>
+        <v>575.4221524598875</v>
       </c>
       <c r="E96">
         <v>213.2160000000001</v>
@@ -9153,37 +9153,37 @@
         <v>188.11</v>
       </c>
       <c r="M96">
-        <v>210.2098179643276</v>
+        <v>191.1583491643277</v>
       </c>
       <c r="N96">
-        <v>-22.09981796432763</v>
+        <v>-3.048349164327647</v>
       </c>
       <c r="O96">
-        <v>-5.303956311438631</v>
+        <v>-0.7316037994386352</v>
       </c>
       <c r="P96">
-        <v>-16.79586165288899</v>
+        <v>-2.316745364889012</v>
       </c>
       <c r="Q96">
-        <v>-14.40586165288899</v>
+        <v>0.07325463511098862</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6248312413687391</v>
+        <v>0.6101283711315436</v>
       </c>
       <c r="T96">
-        <v>7.969090116875638</v>
+        <v>7.768192444636532</v>
       </c>
       <c r="U96">
-        <v>0.1853675944292917</v>
+        <v>0.1685675944292917</v>
       </c>
       <c r="V96">
-        <v>0.2147682750368077</v>
+        <v>0.2361727865791009</v>
       </c>
       <c r="W96">
-        <v>0.1455565159259901</v>
+        <v>0.1287565159259902</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8948678126533655</v>
+        <v>0.9840532774129204</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +9202,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.175708675396848</v>
+        <v>0.1588665031826163</v>
       </c>
       <c r="C97">
-        <v>-640.4988551477941</v>
+        <v>-570.0604450797492</v>
       </c>
       <c r="D97">
-        <v>499.0611448522061</v>
+        <v>569.4995549202509</v>
       </c>
       <c r="E97">
         <v>225.2800000000002</v>
@@ -9235,37 +9235,37 @@
         <v>188.11</v>
       </c>
       <c r="M97">
-        <v>212.4460926235226</v>
+        <v>193.1919486235226</v>
       </c>
       <c r="N97">
-        <v>-24.33609262352263</v>
+        <v>-5.081948623522635</v>
       </c>
       <c r="O97">
-        <v>-5.840662229645432</v>
+        <v>-1.219667669645432</v>
       </c>
       <c r="P97">
-        <v>-18.4954303938772</v>
+        <v>-3.862280953877203</v>
       </c>
       <c r="Q97">
-        <v>-16.1054303938772</v>
+        <v>-1.472280953877203</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.7406374896424872</v>
+        <v>0.7229940453578529</v>
       </c>
       <c r="T97">
-        <v>9.562908140250769</v>
+        <v>9.321830933563845</v>
       </c>
       <c r="U97">
-        <v>0.1853675944292917</v>
+        <v>0.1685675944292917</v>
       </c>
       <c r="V97">
-        <v>0.2125075563522097</v>
+        <v>0.2336867572466892</v>
       </c>
       <c r="W97">
-        <v>0.1459755799102354</v>
+        <v>0.1291755799102355</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8854481514675405</v>
+        <v>0.9736948218612053</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +9284,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.1771043513411409</v>
+        <v>0.1600941791269092</v>
       </c>
       <c r="C98">
-        <v>-657.6281822384262</v>
+        <v>-587.9263666809978</v>
       </c>
       <c r="D98">
-        <v>493.9958177615738</v>
+        <v>563.6976333190022</v>
       </c>
       <c r="E98">
         <v>237.3440000000001</v>
@@ -9317,37 +9317,37 @@
         <v>188.11</v>
       </c>
       <c r="M98">
-        <v>214.6823672827176</v>
+        <v>195.2255480827176</v>
       </c>
       <c r="N98">
-        <v>-26.57236728271758</v>
+        <v>-7.115548082717595</v>
       </c>
       <c r="O98">
-        <v>-6.377368147852219</v>
+        <v>-1.707731539852223</v>
       </c>
       <c r="P98">
-        <v>-20.19499913486536</v>
+        <v>-5.407816542865373</v>
       </c>
       <c r="Q98">
-        <v>-17.80499913486536</v>
+        <v>-3.017816542865372</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.9143468620531073</v>
+        <v>0.8922925566973142</v>
       </c>
       <c r="T98">
-        <v>11.95363517531344</v>
+        <v>11.65228866695478</v>
       </c>
       <c r="U98">
-        <v>0.1853675944292917</v>
+        <v>0.1685675944292917</v>
       </c>
       <c r="V98">
-        <v>0.2102939359735409</v>
+        <v>0.2312525201920363</v>
       </c>
       <c r="W98">
-        <v>0.1463859133948089</v>
+        <v>0.129585913394809</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.876224733223087</v>
+        <v>0.9635521674668178</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +9366,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1785000272854338</v>
+        <v>0.1613218550712021</v>
       </c>
       <c r="C99">
-        <v>-674.6557192427883</v>
+        <v>-605.6752633982827</v>
       </c>
       <c r="D99">
-        <v>489.0322807572118</v>
+        <v>558.0127366017174</v>
       </c>
       <c r="E99">
         <v>249.4080000000001</v>
@@ -9399,37 +9399,37 @@
         <v>188.11</v>
       </c>
       <c r="M99">
-        <v>216.9186419419126</v>
+        <v>197.2591475419126</v>
       </c>
       <c r="N99">
-        <v>-28.80864194191255</v>
+        <v>-9.149147541912583</v>
       </c>
       <c r="O99">
-        <v>-6.914074066059013</v>
+        <v>-2.19579541005902</v>
       </c>
       <c r="P99">
-        <v>-21.89456787585354</v>
+        <v>-6.953352131853563</v>
       </c>
       <c r="Q99">
-        <v>-19.50456787585354</v>
+        <v>-4.563352131853563</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.203862482737476</v>
+        <v>1.174456742263086</v>
       </c>
       <c r="T99">
-        <v>15.93818023375125</v>
+        <v>15.53638488927304</v>
       </c>
       <c r="U99">
-        <v>0.1853675944292917</v>
+        <v>0.1685675944292917</v>
       </c>
       <c r="V99">
-        <v>0.2081259572521642</v>
+        <v>0.2288684735921184</v>
       </c>
       <c r="W99">
-        <v>0.1467877863951644</v>
+        <v>0.1299877863951644</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8671914885506841</v>
+        <v>0.9536186399671599</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +9448,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1798957032297267</v>
+        <v>0.162549531015495</v>
       </c>
       <c r="C100">
-        <v>-691.5845039164911</v>
+        <v>-623.3106404728624</v>
       </c>
       <c r="D100">
-        <v>484.167496083509</v>
+        <v>552.4413595271378</v>
       </c>
       <c r="E100">
         <v>261.4720000000002</v>
@@ -9481,37 +9481,37 @@
         <v>188.11</v>
       </c>
       <c r="M100">
-        <v>219.1549166011076</v>
+        <v>199.2927470011076</v>
       </c>
       <c r="N100">
-        <v>-31.04491660110756</v>
+        <v>-11.18274700110757</v>
       </c>
       <c r="O100">
-        <v>-7.450779984265814</v>
+        <v>-2.683859280265817</v>
       </c>
       <c r="P100">
-        <v>-23.59413661684174</v>
+        <v>-8.498887720841754</v>
       </c>
       <c r="Q100">
-        <v>-21.20413661684174</v>
+        <v>-6.108887720841754</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.782893724106215</v>
+        <v>1.738785113394628</v>
       </c>
       <c r="T100">
-        <v>23.90727035062687</v>
+        <v>23.30457733390956</v>
       </c>
       <c r="U100">
-        <v>0.1853675944292917</v>
+        <v>0.1685675944292917</v>
       </c>
       <c r="V100">
-        <v>0.206002222994489</v>
+        <v>0.2265330810044437</v>
       </c>
       <c r="W100">
-        <v>0.1471814579057167</v>
+        <v>0.1303814579057168</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8583425958103709</v>
+        <v>0.9438878375185153</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +9530,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.1812913791740197</v>
+        <v>0.163777206959788</v>
       </c>
       <c r="C101">
-        <v>-708.4174543300699</v>
+        <v>-640.8358645400951</v>
       </c>
       <c r="D101">
-        <v>479.3985456699301</v>
+        <v>546.9801354599049</v>
       </c>
       <c r="E101">
         <v>273.5360000000001</v>
@@ -9563,37 +9563,37 @@
         <v>188.11</v>
       </c>
       <c r="M101">
-        <v>221.3911912603025</v>
+        <v>201.3263464603025</v>
       </c>
       <c r="N101">
-        <v>-33.28119126030251</v>
+        <v>-13.21634646030253</v>
       </c>
       <c r="O101">
-        <v>-7.987485902472601</v>
+        <v>-3.171923150472607</v>
       </c>
       <c r="P101">
-        <v>-25.29370535782991</v>
+        <v>-10.04442330982992</v>
       </c>
       <c r="Q101">
-        <v>-22.90370535782991</v>
+        <v>-7.654423309829923</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.519987448212429</v>
+        <v>3.431770226789256</v>
       </c>
       <c r="T101">
-        <v>47.81454070125375</v>
+        <v>46.60915466781911</v>
       </c>
       <c r="U101">
-        <v>0.1853675944292917</v>
+        <v>0.1685675944292917</v>
       </c>
       <c r="V101">
-        <v>0.2039213924591911</v>
+        <v>0.2242448680650048</v>
       </c>
       <c r="W101">
-        <v>0.1475671764564599</v>
+        <v>0.1307671764564599</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.8496724685799631</v>
+        <v>0.9343536169375203</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/italy/italy_retail_rei_ts.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_retail_rei_ts.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08932160355190144</v>
+        <v>0.08930686542103949</v>
       </c>
       <c r="C2">
-        <v>1372.396224610062</v>
+        <v>1360.737119532206</v>
       </c>
       <c r="D2">
-        <v>1365.876224610062</v>
+        <v>1366.281119532206</v>
       </c>
       <c r="E2">
-        <v>-920.8</v>
+        <v>-908.736</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>12.064</v>
       </c>
       <c r="G2">
         <v>6.52</v>
@@ -1445,28 +1445,28 @@
         <v>188.11</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.869423459194975</v>
       </c>
       <c r="N2">
-        <v>188.11</v>
+        <v>187.2405765408051</v>
       </c>
       <c r="O2">
-        <v>45.1464</v>
+        <v>44.93773836979321</v>
       </c>
       <c r="P2">
-        <v>142.9636</v>
+        <v>142.3028381710118</v>
       </c>
       <c r="Q2">
-        <v>145.3536</v>
+        <v>144.6928381710118</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08932160355190144</v>
+        <v>0.08965570879128978</v>
       </c>
       <c r="T2">
-        <v>0.5990912546403601</v>
+        <v>0.6036903390194174</v>
       </c>
       <c r="U2">
         <v>0.07206759442929168</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>216.3617717126895</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08930686542103949</v>
+        <v>0.08929212729017755</v>
       </c>
       <c r="C3">
-        <v>1360.737119532206</v>
+        <v>1349.078254576416</v>
       </c>
       <c r="D3">
-        <v>1366.281119532206</v>
+        <v>1366.686254576416</v>
       </c>
       <c r="E3">
-        <v>-908.736</v>
+        <v>-896.6719999999999</v>
       </c>
       <c r="F3">
-        <v>12.064</v>
+        <v>24.128</v>
       </c>
       <c r="G3">
         <v>6.52</v>
@@ -1527,28 +1527,28 @@
         <v>188.11</v>
       </c>
       <c r="M3">
-        <v>0.869423459194975</v>
+        <v>1.73884691838995</v>
       </c>
       <c r="N3">
-        <v>187.2405765408051</v>
+        <v>186.3711530816101</v>
       </c>
       <c r="O3">
-        <v>44.93773836979321</v>
+        <v>44.72907673958641</v>
       </c>
       <c r="P3">
-        <v>142.3028381710118</v>
+        <v>141.6420763420236</v>
       </c>
       <c r="Q3">
-        <v>144.6928381710118</v>
+        <v>144.0320763420236</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08965570879128978</v>
+        <v>0.08999663250495135</v>
       </c>
       <c r="T3">
-        <v>0.6036903390194174</v>
+        <v>0.6083832822633534</v>
       </c>
       <c r="U3">
         <v>0.07206759442929168</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>216.3617717126895</v>
+        <v>108.1808858563448</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08929212729017755</v>
+        <v>0.08927738915931561</v>
       </c>
       <c r="C4">
-        <v>1349.078254576416</v>
+        <v>1337.41962995636</v>
       </c>
       <c r="D4">
-        <v>1366.686254576416</v>
+        <v>1367.09162995636</v>
       </c>
       <c r="E4">
-        <v>-896.6719999999999</v>
+        <v>-884.6079999999999</v>
       </c>
       <c r="F4">
-        <v>24.128</v>
+        <v>36.192</v>
       </c>
       <c r="G4">
         <v>6.52</v>
@@ -1609,28 +1609,28 @@
         <v>188.11</v>
       </c>
       <c r="M4">
-        <v>1.73884691838995</v>
+        <v>2.608270377584925</v>
       </c>
       <c r="N4">
-        <v>186.3711530816101</v>
+        <v>185.5017296224151</v>
       </c>
       <c r="O4">
-        <v>44.72907673958641</v>
+        <v>44.52041510937962</v>
       </c>
       <c r="P4">
-        <v>141.6420763420236</v>
+        <v>140.9813145130355</v>
       </c>
       <c r="Q4">
-        <v>144.0320763420236</v>
+        <v>143.3713145130355</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08999663250495135</v>
+        <v>0.09034458557353378</v>
       </c>
       <c r="T4">
-        <v>0.6083832822633534</v>
+        <v>0.6131729872236593</v>
       </c>
       <c r="U4">
         <v>0.07206759442929168</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>108.1808858563448</v>
+        <v>72.12059057089651</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08927738915931561</v>
+        <v>0.08926265102845365</v>
       </c>
       <c r="C5">
-        <v>1337.41962995636</v>
+        <v>1325.761245885962</v>
       </c>
       <c r="D5">
-        <v>1367.09162995636</v>
+        <v>1367.497245885962</v>
       </c>
       <c r="E5">
-        <v>-884.6079999999999</v>
+        <v>-872.544</v>
       </c>
       <c r="F5">
-        <v>36.192</v>
+        <v>48.25600000000001</v>
       </c>
       <c r="G5">
         <v>6.52</v>
@@ -1691,28 +1691,28 @@
         <v>188.11</v>
       </c>
       <c r="M5">
-        <v>2.608270377584925</v>
+        <v>3.4776938367799</v>
       </c>
       <c r="N5">
-        <v>185.5017296224151</v>
+        <v>184.6323061632201</v>
       </c>
       <c r="O5">
-        <v>44.52041510937962</v>
+        <v>44.31175347917282</v>
       </c>
       <c r="P5">
-        <v>140.9813145130355</v>
+        <v>140.3205526840473</v>
       </c>
       <c r="Q5">
-        <v>143.3713145130355</v>
+        <v>142.7105526840473</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09034458557353378</v>
+        <v>0.09069978766437833</v>
       </c>
       <c r="T5">
-        <v>0.6131729872236593</v>
+        <v>0.6180624777039715</v>
       </c>
       <c r="U5">
         <v>0.07206759442929168</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>72.12059057089651</v>
+        <v>54.09044292817238</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08926265102845365</v>
+        <v>0.08924791289759172</v>
       </c>
       <c r="C6">
-        <v>1325.761245885962</v>
+        <v>1314.103102579398</v>
       </c>
       <c r="D6">
-        <v>1367.497245885962</v>
+        <v>1367.903102579397</v>
       </c>
       <c r="E6">
-        <v>-872.544</v>
+        <v>-860.4799999999999</v>
       </c>
       <c r="F6">
-        <v>48.25600000000001</v>
+        <v>60.32000000000001</v>
       </c>
       <c r="G6">
         <v>6.52</v>
@@ -1773,28 +1773,28 @@
         <v>188.11</v>
       </c>
       <c r="M6">
-        <v>3.4776938367799</v>
+        <v>4.347117295974875</v>
       </c>
       <c r="N6">
-        <v>184.6323061632201</v>
+        <v>183.7628827040251</v>
       </c>
       <c r="O6">
-        <v>44.31175347917282</v>
+        <v>44.10309184896603</v>
       </c>
       <c r="P6">
-        <v>140.3205526840473</v>
+        <v>139.6597908550591</v>
       </c>
       <c r="Q6">
-        <v>142.7105526840473</v>
+        <v>142.0497908550591</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09069978766437833</v>
+        <v>0.09106246769397751</v>
       </c>
       <c r="T6">
-        <v>0.6180624777039715</v>
+        <v>0.6230549048259745</v>
       </c>
       <c r="U6">
         <v>0.07206759442929168</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>54.09044292817238</v>
+        <v>43.27235434253791</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08924791289759172</v>
+        <v>0.08923317476672978</v>
       </c>
       <c r="C7">
-        <v>1314.103102579398</v>
+        <v>1302.445200251098</v>
       </c>
       <c r="D7">
-        <v>1367.903102579397</v>
+        <v>1368.309200251098</v>
       </c>
       <c r="E7">
-        <v>-860.4799999999999</v>
+        <v>-848.4159999999999</v>
       </c>
       <c r="F7">
-        <v>60.32000000000001</v>
+        <v>72.38400000000001</v>
       </c>
       <c r="G7">
         <v>6.52</v>
@@ -1855,28 +1855,28 @@
         <v>188.11</v>
       </c>
       <c r="M7">
-        <v>4.347117295974875</v>
+        <v>5.21654075516985</v>
       </c>
       <c r="N7">
-        <v>183.7628827040251</v>
+        <v>182.8934592448302</v>
       </c>
       <c r="O7">
-        <v>44.10309184896603</v>
+        <v>43.89443021875923</v>
       </c>
       <c r="P7">
-        <v>139.6597908550591</v>
+        <v>138.9990290260709</v>
       </c>
       <c r="Q7">
-        <v>142.0497908550591</v>
+        <v>141.3890290260709</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09106246769397751</v>
+        <v>0.09143286431995114</v>
       </c>
       <c r="T7">
-        <v>0.6230549048259745</v>
+        <v>0.6281535538016372</v>
       </c>
       <c r="U7">
         <v>0.07206759442929168</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>43.27235434253791</v>
+        <v>36.06029528544825</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08923317476672978</v>
+        <v>0.08921843663586783</v>
       </c>
       <c r="C8">
-        <v>1302.445200251098</v>
+        <v>1290.78753911575</v>
       </c>
       <c r="D8">
-        <v>1368.309200251098</v>
+        <v>1368.71553911575</v>
       </c>
       <c r="E8">
-        <v>-848.4159999999999</v>
+        <v>-836.352</v>
       </c>
       <c r="F8">
-        <v>72.384</v>
+        <v>84.44799999999999</v>
       </c>
       <c r="G8">
         <v>6.52</v>
@@ -1937,28 +1937,28 @@
         <v>188.11</v>
       </c>
       <c r="M8">
-        <v>5.216540755169849</v>
+        <v>6.085964214364823</v>
       </c>
       <c r="N8">
-        <v>182.8934592448302</v>
+        <v>182.0240357856352</v>
       </c>
       <c r="O8">
-        <v>43.89443021875923</v>
+        <v>43.68576858855244</v>
       </c>
       <c r="P8">
-        <v>138.9990290260709</v>
+        <v>138.3382671970828</v>
       </c>
       <c r="Q8">
-        <v>141.3890290260709</v>
+        <v>140.7282671970827</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09143286431995114</v>
+        <v>0.0918112264647629</v>
       </c>
       <c r="T8">
-        <v>0.6281535538016372</v>
+        <v>0.6333618511423678</v>
       </c>
       <c r="U8">
         <v>0.07206759442929168</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.06029528544826</v>
+        <v>30.90882453038423</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08921843663586781</v>
+        <v>0.08920369850500588</v>
       </c>
       <c r="C9">
-        <v>1290.78753911575</v>
+        <v>1279.130119388293</v>
       </c>
       <c r="D9">
-        <v>1368.71553911575</v>
+        <v>1369.122119388293</v>
       </c>
       <c r="E9">
-        <v>-836.352</v>
+        <v>-824.2879999999999</v>
       </c>
       <c r="F9">
-        <v>84.44800000000001</v>
+        <v>96.51200000000001</v>
       </c>
       <c r="G9">
         <v>6.52</v>
@@ -2019,28 +2019,28 @@
         <v>188.11</v>
       </c>
       <c r="M9">
-        <v>6.085964214364824</v>
+        <v>6.9553876735598</v>
       </c>
       <c r="N9">
-        <v>182.0240357856352</v>
+        <v>181.1546123264402</v>
       </c>
       <c r="O9">
-        <v>43.68576858855244</v>
+        <v>43.47710695834564</v>
       </c>
       <c r="P9">
-        <v>138.3382671970828</v>
+        <v>137.6775053680946</v>
       </c>
       <c r="Q9">
-        <v>140.7282671970827</v>
+        <v>140.0675053680945</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0918112264647629</v>
+        <v>0.09219781387359233</v>
       </c>
       <c r="T9">
-        <v>0.6333618511423678</v>
+        <v>0.6386833723383316</v>
       </c>
       <c r="U9">
         <v>0.07206759442929168</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>30.90882453038422</v>
+        <v>27.04522146408619</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08920369850500588</v>
+        <v>0.08918896037414392</v>
       </c>
       <c r="C10">
-        <v>1279.130119388293</v>
+        <v>1267.472941283925</v>
       </c>
       <c r="D10">
-        <v>1369.122119388293</v>
+        <v>1369.528941283925</v>
       </c>
       <c r="E10">
-        <v>-824.2879999999999</v>
+        <v>-812.2239999999999</v>
       </c>
       <c r="F10">
-        <v>96.51200000000001</v>
+        <v>108.576</v>
       </c>
       <c r="G10">
         <v>6.52</v>
@@ -2101,28 +2101,28 @@
         <v>188.11</v>
       </c>
       <c r="M10">
-        <v>6.9553876735598</v>
+        <v>7.824811132754775</v>
       </c>
       <c r="N10">
-        <v>181.1546123264402</v>
+        <v>180.2851888672452</v>
       </c>
       <c r="O10">
-        <v>43.47710695834564</v>
+        <v>43.26844532813885</v>
       </c>
       <c r="P10">
-        <v>137.6775053680946</v>
+        <v>137.0167435391064</v>
       </c>
       <c r="Q10">
-        <v>140.0675053680945</v>
+        <v>139.4067435391064</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09219781387359233</v>
+        <v>0.09259289770898942</v>
       </c>
       <c r="T10">
-        <v>0.6386833723383316</v>
+        <v>0.6441218500440969</v>
       </c>
       <c r="U10">
         <v>0.07206759442929168</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.04522146408619</v>
+        <v>24.0401968569655</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08918896037414392</v>
+        <v>0.08917422224328199</v>
       </c>
       <c r="C11">
-        <v>1267.472941283925</v>
+        <v>1255.816005018097</v>
       </c>
       <c r="D11">
-        <v>1369.528941283925</v>
+        <v>1369.936005018097</v>
       </c>
       <c r="E11">
-        <v>-812.2239999999999</v>
+        <v>-800.16</v>
       </c>
       <c r="F11">
-        <v>108.576</v>
+        <v>120.64</v>
       </c>
       <c r="G11">
         <v>6.52</v>
@@ -2183,28 +2183,28 @@
         <v>188.11</v>
       </c>
       <c r="M11">
-        <v>7.824811132754775</v>
+        <v>8.694234591949749</v>
       </c>
       <c r="N11">
-        <v>180.2851888672452</v>
+        <v>179.4157654080503</v>
       </c>
       <c r="O11">
-        <v>43.26844532813885</v>
+        <v>43.05978369793206</v>
       </c>
       <c r="P11">
-        <v>137.0167435391064</v>
+        <v>136.3559817101182</v>
       </c>
       <c r="Q11">
-        <v>139.4067435391064</v>
+        <v>138.7459817101182</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09259289770898942</v>
+        <v>0.09299676118517314</v>
       </c>
       <c r="T11">
-        <v>0.6441218500440969</v>
+        <v>0.6496811828099905</v>
       </c>
       <c r="U11">
         <v>0.07206759442929168</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.0401968569655</v>
+        <v>21.63617717126895</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08917422224328199</v>
+        <v>0.08915948411242003</v>
       </c>
       <c r="C12">
-        <v>1255.816005018097</v>
+        <v>1244.159310806517</v>
       </c>
       <c r="D12">
-        <v>1369.936005018097</v>
+        <v>1370.343310806517</v>
       </c>
       <c r="E12">
-        <v>-800.16</v>
+        <v>-788.096</v>
       </c>
       <c r="F12">
-        <v>120.64</v>
+        <v>132.704</v>
       </c>
       <c r="G12">
         <v>6.52</v>
@@ -2265,28 +2265,28 @@
         <v>188.11</v>
       </c>
       <c r="M12">
-        <v>8.694234591949749</v>
+        <v>9.563658051144724</v>
       </c>
       <c r="N12">
-        <v>179.4157654080503</v>
+        <v>178.5463419488553</v>
       </c>
       <c r="O12">
-        <v>43.05978369793206</v>
+        <v>42.85112206772526</v>
       </c>
       <c r="P12">
-        <v>136.3559817101182</v>
+        <v>135.69521988113</v>
       </c>
       <c r="Q12">
-        <v>138.7459817101182</v>
+        <v>138.08521988113</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09299676118517314</v>
+        <v>0.09340970024509129</v>
       </c>
       <c r="T12">
-        <v>0.6496811828099905</v>
+        <v>0.6553654444020838</v>
       </c>
       <c r="U12">
         <v>0.07206759442929168</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.63617717126895</v>
+        <v>19.66925197388087</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08915948411242003</v>
+        <v>0.08914474598155808</v>
       </c>
       <c r="C13">
-        <v>1244.159310806517</v>
+        <v>1232.502858865151</v>
       </c>
       <c r="D13">
-        <v>1370.343310806517</v>
+        <v>1370.750858865151</v>
       </c>
       <c r="E13">
-        <v>-788.096</v>
+        <v>-776.0319999999999</v>
       </c>
       <c r="F13">
-        <v>132.704</v>
+        <v>144.768</v>
       </c>
       <c r="G13">
         <v>6.52</v>
@@ -2347,28 +2347,28 @@
         <v>188.11</v>
       </c>
       <c r="M13">
-        <v>9.563658051144724</v>
+        <v>10.4330815103397</v>
       </c>
       <c r="N13">
-        <v>178.5463419488553</v>
+        <v>177.6769184896603</v>
       </c>
       <c r="O13">
-        <v>42.85112206772526</v>
+        <v>42.64246043751847</v>
       </c>
       <c r="P13">
-        <v>135.69521988113</v>
+        <v>135.0344580521418</v>
       </c>
       <c r="Q13">
-        <v>138.08521988113</v>
+        <v>137.4244580521418</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09340970024509129</v>
+        <v>0.09383202428364396</v>
       </c>
       <c r="T13">
-        <v>0.6553654444020838</v>
+        <v>0.6611788937576337</v>
       </c>
       <c r="U13">
         <v>0.07206759442929168</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.66925197388087</v>
+        <v>18.03014764272413</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08914474598155808</v>
+        <v>0.08913000785069615</v>
       </c>
       <c r="C14">
-        <v>1232.502858865151</v>
+        <v>1220.846649410221</v>
       </c>
       <c r="D14">
-        <v>1370.750858865151</v>
+        <v>1371.158649410221</v>
       </c>
       <c r="E14">
-        <v>-776.0319999999999</v>
+        <v>-763.968</v>
       </c>
       <c r="F14">
-        <v>144.768</v>
+        <v>156.832</v>
       </c>
       <c r="G14">
         <v>6.52</v>
@@ -2429,28 +2429,28 @@
         <v>188.11</v>
       </c>
       <c r="M14">
-        <v>10.4330815103397</v>
+        <v>11.30250496953468</v>
       </c>
       <c r="N14">
-        <v>177.6769184896603</v>
+        <v>176.8074950304653</v>
       </c>
       <c r="O14">
-        <v>42.64246043751847</v>
+        <v>42.43379880731167</v>
       </c>
       <c r="P14">
-        <v>135.0344580521418</v>
+        <v>134.3736962231537</v>
       </c>
       <c r="Q14">
-        <v>137.4244580521418</v>
+        <v>136.7636962231537</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09383202428364396</v>
+        <v>0.09426405692078405</v>
       </c>
       <c r="T14">
-        <v>0.6611788937576337</v>
+        <v>0.6671259856271045</v>
       </c>
       <c r="U14">
         <v>0.07206759442929168</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.03014764272413</v>
+        <v>16.64321320866842</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08913000785069615</v>
+        <v>0.0891152697198342</v>
       </c>
       <c r="C15">
-        <v>1220.846649410221</v>
+        <v>1209.190682658206</v>
       </c>
       <c r="D15">
-        <v>1371.158649410221</v>
+        <v>1371.566682658206</v>
       </c>
       <c r="E15">
-        <v>-763.968</v>
+        <v>-751.904</v>
       </c>
       <c r="F15">
-        <v>156.832</v>
+        <v>168.896</v>
       </c>
       <c r="G15">
         <v>6.52</v>
@@ -2511,28 +2511,28 @@
         <v>188.11</v>
       </c>
       <c r="M15">
-        <v>11.30250496953468</v>
+        <v>12.17192842872965</v>
       </c>
       <c r="N15">
-        <v>176.8074950304653</v>
+        <v>175.9380715712704</v>
       </c>
       <c r="O15">
-        <v>42.43379880731167</v>
+        <v>42.22513717710489</v>
       </c>
       <c r="P15">
-        <v>134.3736962231537</v>
+        <v>133.7129343941655</v>
       </c>
       <c r="Q15">
-        <v>136.7636962231537</v>
+        <v>136.1029343941655</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09426405692078405</v>
+        <v>0.0947061368285553</v>
       </c>
       <c r="T15">
-        <v>0.6671259856271045</v>
+        <v>0.6732113819586558</v>
       </c>
       <c r="U15">
         <v>0.07206759442929168</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.64321320866842</v>
+        <v>15.45441226519211</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0891152697198342</v>
+        <v>0.08910053158897226</v>
       </c>
       <c r="C16">
-        <v>1209.190682658206</v>
+        <v>1197.534958825843</v>
       </c>
       <c r="D16">
-        <v>1371.566682658206</v>
+        <v>1371.974958825843</v>
       </c>
       <c r="E16">
-        <v>-751.904</v>
+        <v>-739.8399999999999</v>
       </c>
       <c r="F16">
-        <v>168.896</v>
+        <v>180.96</v>
       </c>
       <c r="G16">
         <v>6.52</v>
@@ -2593,28 +2593,28 @@
         <v>188.11</v>
       </c>
       <c r="M16">
-        <v>12.17192842872965</v>
+        <v>13.04135188792463</v>
       </c>
       <c r="N16">
-        <v>175.9380715712704</v>
+        <v>175.0686481120754</v>
       </c>
       <c r="O16">
-        <v>42.22513717710489</v>
+        <v>42.01647554689809</v>
       </c>
       <c r="P16">
-        <v>133.7129343941655</v>
+        <v>133.0521725651773</v>
       </c>
       <c r="Q16">
-        <v>136.1029343941655</v>
+        <v>135.4421725651773</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0947061368285553</v>
+        <v>0.09515861861650941</v>
       </c>
       <c r="T16">
-        <v>0.6732113819586558</v>
+        <v>0.6794399640862437</v>
       </c>
       <c r="U16">
         <v>0.07206759442929168</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.45441226519211</v>
+        <v>14.4241181141793</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08910053158897224</v>
+        <v>0.0890857934581103</v>
       </c>
       <c r="C17">
-        <v>1197.534958825843</v>
+        <v>1185.879478130127</v>
       </c>
       <c r="D17">
-        <v>1371.974958825843</v>
+        <v>1372.383478130127</v>
       </c>
       <c r="E17">
-        <v>-739.8399999999999</v>
+        <v>-727.776</v>
       </c>
       <c r="F17">
-        <v>180.96</v>
+        <v>193.024</v>
       </c>
       <c r="G17">
         <v>6.52</v>
@@ -2675,28 +2675,28 @@
         <v>188.11</v>
       </c>
       <c r="M17">
-        <v>13.04135188792462</v>
+        <v>13.9107753471196</v>
       </c>
       <c r="N17">
-        <v>175.0686481120754</v>
+        <v>174.1992246528804</v>
       </c>
       <c r="O17">
-        <v>42.01647554689809</v>
+        <v>41.8078139166913</v>
       </c>
       <c r="P17">
-        <v>133.0521725651773</v>
+        <v>132.3914107361891</v>
       </c>
       <c r="Q17">
-        <v>135.4421725651773</v>
+        <v>134.7814107361891</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0951586186165094</v>
+        <v>0.09562187378036718</v>
       </c>
       <c r="T17">
-        <v>0.6794399640862436</v>
+        <v>0.6858168457882979</v>
       </c>
       <c r="U17">
         <v>0.07206759442929168</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.4241181141793</v>
+        <v>13.52261073204309</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0890857934581103</v>
+        <v>0.08926485532724837</v>
       </c>
       <c r="C18">
-        <v>1185.879478130127</v>
+        <v>1168.868564900984</v>
       </c>
       <c r="D18">
-        <v>1372.383478130127</v>
+        <v>1367.436564900984</v>
       </c>
       <c r="E18">
-        <v>-727.776</v>
+        <v>-715.712</v>
       </c>
       <c r="F18">
-        <v>193.024</v>
+        <v>205.088</v>
       </c>
       <c r="G18">
         <v>6.52</v>
@@ -2757,45 +2757,45 @@
         <v>188.11</v>
       </c>
       <c r="M18">
-        <v>13.9107753471196</v>
+        <v>15.08783080631457</v>
       </c>
       <c r="N18">
-        <v>174.1992246528804</v>
+        <v>173.0221691936854</v>
       </c>
       <c r="O18">
-        <v>41.8078139166913</v>
+        <v>41.52532060648451</v>
       </c>
       <c r="P18">
-        <v>132.3914107361891</v>
+        <v>131.4968485872009</v>
       </c>
       <c r="Q18">
-        <v>134.7814107361891</v>
+        <v>133.8868485872009</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09562187378036718</v>
+        <v>0.09609629171925768</v>
       </c>
       <c r="T18">
-        <v>0.6858168457882979</v>
+        <v>0.6923473872904017</v>
       </c>
       <c r="U18">
-        <v>0.07206759442929168</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V18">
         <v>0.24</v>
       </c>
       <c r="W18">
-        <v>0.05477137176626168</v>
+        <v>0.05591137176626167</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.52261073204309</v>
+        <v>12.4676636698015</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08926485532724837</v>
+        <v>0.08926151719638641</v>
       </c>
       <c r="C19">
-        <v>1168.868564900984</v>
+        <v>1156.89646065163</v>
       </c>
       <c r="D19">
-        <v>1367.436564900984</v>
+        <v>1367.52846065163</v>
       </c>
       <c r="E19">
-        <v>-715.712</v>
+        <v>-703.6479999999999</v>
       </c>
       <c r="F19">
-        <v>205.088</v>
+        <v>217.152</v>
       </c>
       <c r="G19">
         <v>6.52</v>
@@ -2839,28 +2839,28 @@
         <v>188.11</v>
       </c>
       <c r="M19">
-        <v>15.08783080631457</v>
+        <v>15.97535026550955</v>
       </c>
       <c r="N19">
-        <v>173.0221691936854</v>
+        <v>172.1346497344905</v>
       </c>
       <c r="O19">
-        <v>41.52532060648451</v>
+        <v>41.31231593627771</v>
       </c>
       <c r="P19">
-        <v>131.4968485872009</v>
+        <v>130.8223337982128</v>
       </c>
       <c r="Q19">
-        <v>133.8868485872009</v>
+        <v>133.2123337982127</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09609629171925768</v>
+        <v>0.0965822808273894</v>
       </c>
       <c r="T19">
-        <v>0.6923473872904017</v>
+        <v>0.6990372102925568</v>
       </c>
       <c r="U19">
         <v>0.07356759442929167</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.4676636698015</v>
+        <v>11.77501568814586</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08926151719638642</v>
+        <v>0.08925817906552445</v>
       </c>
       <c r="C20">
-        <v>1156.89646065163</v>
+        <v>1144.924368754434</v>
       </c>
       <c r="D20">
-        <v>1367.52846065163</v>
+        <v>1367.620368754434</v>
       </c>
       <c r="E20">
-        <v>-703.6479999999999</v>
+        <v>-691.5839999999999</v>
       </c>
       <c r="F20">
-        <v>217.152</v>
+        <v>229.216</v>
       </c>
       <c r="G20">
         <v>6.52</v>
@@ -2921,28 +2921,28 @@
         <v>188.11</v>
       </c>
       <c r="M20">
-        <v>15.97535026550955</v>
+        <v>16.86286972470452</v>
       </c>
       <c r="N20">
-        <v>172.1346497344905</v>
+        <v>171.2471302752955</v>
       </c>
       <c r="O20">
-        <v>41.31231593627771</v>
+        <v>41.09931126607091</v>
       </c>
       <c r="P20">
-        <v>130.8223337982128</v>
+        <v>130.1478190092246</v>
       </c>
       <c r="Q20">
-        <v>133.2123337982127</v>
+        <v>132.5378190092246</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0965822808273894</v>
+        <v>0.0970802696665861</v>
       </c>
       <c r="T20">
-        <v>0.6990372102925567</v>
+        <v>0.7058922141095798</v>
       </c>
       <c r="U20">
         <v>0.07356759442929167</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.77501568814586</v>
+        <v>11.15527802034871</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08925817906552445</v>
+        <v>0.08925484093466252</v>
       </c>
       <c r="C21">
-        <v>1144.924368754434</v>
+        <v>1132.952289211887</v>
       </c>
       <c r="D21">
-        <v>1367.620368754434</v>
+        <v>1367.712289211887</v>
       </c>
       <c r="E21">
-        <v>-691.5839999999999</v>
+        <v>-679.52</v>
       </c>
       <c r="F21">
-        <v>229.216</v>
+        <v>241.28</v>
       </c>
       <c r="G21">
         <v>6.52</v>
@@ -3003,28 +3003,28 @@
         <v>188.11</v>
       </c>
       <c r="M21">
-        <v>16.86286972470452</v>
+        <v>17.7503891838995</v>
       </c>
       <c r="N21">
-        <v>171.2471302752955</v>
+        <v>170.3596108161005</v>
       </c>
       <c r="O21">
-        <v>41.09931126607091</v>
+        <v>40.88630659586412</v>
       </c>
       <c r="P21">
-        <v>130.1478190092246</v>
+        <v>129.4733042202364</v>
       </c>
       <c r="Q21">
-        <v>132.5378190092246</v>
+        <v>131.8633042202364</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0970802696665861</v>
+        <v>0.09759070822676272</v>
       </c>
       <c r="T21">
-        <v>0.7058922141095798</v>
+        <v>0.7129185930220284</v>
       </c>
       <c r="U21">
         <v>0.07356759442929167</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.15527802034871</v>
+        <v>10.59751411933127</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08925484093466252</v>
+        <v>0.08925150280380056</v>
       </c>
       <c r="C22">
-        <v>1132.952289211887</v>
+        <v>1120.98022202648</v>
       </c>
       <c r="D22">
-        <v>1367.712289211887</v>
+        <v>1367.80422202648</v>
       </c>
       <c r="E22">
-        <v>-679.52</v>
+        <v>-667.4559999999999</v>
       </c>
       <c r="F22">
-        <v>241.28</v>
+        <v>253.3440000000001</v>
       </c>
       <c r="G22">
         <v>6.52</v>
@@ -3085,28 +3085,28 @@
         <v>188.11</v>
       </c>
       <c r="M22">
-        <v>17.7503891838995</v>
+        <v>18.63790864309447</v>
       </c>
       <c r="N22">
-        <v>170.3596108161005</v>
+        <v>169.4720913569055</v>
       </c>
       <c r="O22">
-        <v>40.88630659586412</v>
+        <v>40.67330192565733</v>
       </c>
       <c r="P22">
-        <v>129.4733042202364</v>
+        <v>128.7987894312482</v>
       </c>
       <c r="Q22">
-        <v>131.8633042202364</v>
+        <v>131.1887894312482</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09759070822676272</v>
+        <v>0.09811406928213369</v>
       </c>
       <c r="T22">
-        <v>0.7129185930220284</v>
+        <v>0.7201228549449189</v>
       </c>
       <c r="U22">
         <v>0.07356759442929167</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.59751411933127</v>
+        <v>10.09287058983931</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08925150280380056</v>
+        <v>0.08953240467293863</v>
       </c>
       <c r="C23">
-        <v>1120.98022202648</v>
+        <v>1101.223120393001</v>
       </c>
       <c r="D23">
-        <v>1367.80422202648</v>
+        <v>1360.111120393001</v>
       </c>
       <c r="E23">
-        <v>-667.4559999999999</v>
+        <v>-655.3919999999999</v>
       </c>
       <c r="F23">
-        <v>253.344</v>
+        <v>265.408</v>
       </c>
       <c r="G23">
         <v>6.52</v>
@@ -3167,45 +3167,45 @@
         <v>188.11</v>
       </c>
       <c r="M23">
-        <v>18.63790864309447</v>
+        <v>19.97662170228945</v>
       </c>
       <c r="N23">
-        <v>169.4720913569055</v>
+        <v>168.1333782977106</v>
       </c>
       <c r="O23">
-        <v>40.67330192565733</v>
+        <v>40.35201079145054</v>
       </c>
       <c r="P23">
-        <v>128.7987894312482</v>
+        <v>127.78136750626</v>
       </c>
       <c r="Q23">
-        <v>131.1887894312482</v>
+        <v>130.17136750626</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09811406928213369</v>
+        <v>0.09865084985174494</v>
       </c>
       <c r="T23">
-        <v>0.7201228549449189</v>
+        <v>0.7275118415324988</v>
       </c>
       <c r="U23">
-        <v>0.07356759442929167</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V23">
         <v>0.24</v>
       </c>
       <c r="W23">
-        <v>0.05591137176626167</v>
+        <v>0.05720337176626168</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>10.09287058983931</v>
+        <v>9.41650709531339</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08953240467293863</v>
+        <v>0.08954198654207667</v>
       </c>
       <c r="C24">
-        <v>1101.223120393001</v>
+        <v>1088.898226319257</v>
       </c>
       <c r="D24">
-        <v>1360.111120393001</v>
+        <v>1359.850226319257</v>
       </c>
       <c r="E24">
-        <v>-655.3919999999999</v>
+        <v>-643.328</v>
       </c>
       <c r="F24">
-        <v>265.408</v>
+        <v>277.472</v>
       </c>
       <c r="G24">
         <v>6.52</v>
@@ -3249,28 +3249,28 @@
         <v>188.11</v>
       </c>
       <c r="M24">
-        <v>19.97662170228945</v>
+        <v>20.88464996148442</v>
       </c>
       <c r="N24">
-        <v>168.1333782977106</v>
+        <v>167.2253500385156</v>
       </c>
       <c r="O24">
-        <v>40.35201079145054</v>
+        <v>40.13408400924374</v>
       </c>
       <c r="P24">
-        <v>127.78136750626</v>
+        <v>127.0912660292718</v>
       </c>
       <c r="Q24">
-        <v>130.17136750626</v>
+        <v>129.4812660292718</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09865084985174494</v>
+        <v>0.09920157277381361</v>
       </c>
       <c r="T24">
-        <v>0.7275118415324988</v>
+        <v>0.7350927498496262</v>
       </c>
       <c r="U24">
         <v>0.07526759442929168</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.41650709531339</v>
+        <v>9.007093743343241</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08954198654207667</v>
+        <v>0.08955156841121473</v>
       </c>
       <c r="C25">
-        <v>1088.898226319257</v>
+        <v>1076.573432314783</v>
       </c>
       <c r="D25">
-        <v>1359.850226319257</v>
+        <v>1359.589432314783</v>
       </c>
       <c r="E25">
-        <v>-643.328</v>
+        <v>-631.2639999999999</v>
       </c>
       <c r="F25">
-        <v>277.472</v>
+        <v>289.5360000000001</v>
       </c>
       <c r="G25">
         <v>6.52</v>
@@ -3331,28 +3331,28 @@
         <v>188.11</v>
       </c>
       <c r="M25">
-        <v>20.88464996148442</v>
+        <v>21.7926782206794</v>
       </c>
       <c r="N25">
-        <v>167.2253500385156</v>
+        <v>166.3173217793206</v>
       </c>
       <c r="O25">
-        <v>40.13408400924374</v>
+        <v>39.91615722703695</v>
       </c>
       <c r="P25">
-        <v>127.0912660292718</v>
+        <v>126.4011645522837</v>
       </c>
       <c r="Q25">
-        <v>129.4812660292718</v>
+        <v>128.7911645522837</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09920157277381361</v>
+        <v>0.09976678840435779</v>
       </c>
       <c r="T25">
-        <v>0.7350927498496262</v>
+        <v>0.7428731557540464</v>
       </c>
       <c r="U25">
         <v>0.07526759442929168</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.007093743343241</v>
+        <v>8.63179817070394</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08955156841121473</v>
+        <v>0.08956115028035277</v>
       </c>
       <c r="C26">
-        <v>1076.573432314783</v>
+        <v>1064.248738322017</v>
       </c>
       <c r="D26">
-        <v>1359.589432314783</v>
+        <v>1359.328738322017</v>
       </c>
       <c r="E26">
-        <v>-631.2639999999999</v>
+        <v>-619.1999999999999</v>
       </c>
       <c r="F26">
-        <v>289.536</v>
+        <v>301.6</v>
       </c>
       <c r="G26">
         <v>6.52</v>
@@ -3413,28 +3413,28 @@
         <v>188.11</v>
       </c>
       <c r="M26">
-        <v>21.7926782206794</v>
+        <v>22.70070647987437</v>
       </c>
       <c r="N26">
-        <v>166.3173217793206</v>
+        <v>165.4092935201256</v>
       </c>
       <c r="O26">
-        <v>39.91615722703695</v>
+        <v>39.69823044483015</v>
       </c>
       <c r="P26">
-        <v>126.4011645522837</v>
+        <v>125.7110630752955</v>
       </c>
       <c r="Q26">
-        <v>128.7911645522837</v>
+        <v>128.1010630752955</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09976678840435779</v>
+        <v>0.1003470764517165</v>
       </c>
       <c r="T26">
-        <v>0.7428731557540464</v>
+        <v>0.7508610391492513</v>
       </c>
       <c r="U26">
         <v>0.07526759442929168</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.631798170703942</v>
+        <v>8.28652624387578</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08956115028035277</v>
+        <v>0.08957073214949084</v>
       </c>
       <c r="C27">
-        <v>1064.248738322017</v>
+        <v>1051.924144283439</v>
       </c>
       <c r="D27">
-        <v>1359.328738322017</v>
+        <v>1359.068144283439</v>
       </c>
       <c r="E27">
-        <v>-619.1999999999999</v>
+        <v>-607.136</v>
       </c>
       <c r="F27">
-        <v>301.6</v>
+        <v>313.664</v>
       </c>
       <c r="G27">
         <v>6.52</v>
@@ -3495,28 +3495,28 @@
         <v>188.11</v>
       </c>
       <c r="M27">
-        <v>22.70070647987437</v>
+        <v>23.60873473906935</v>
       </c>
       <c r="N27">
-        <v>165.4092935201256</v>
+        <v>164.5012652609307</v>
       </c>
       <c r="O27">
-        <v>39.69823044483015</v>
+        <v>39.48030366262336</v>
       </c>
       <c r="P27">
-        <v>125.7110630752955</v>
+        <v>125.0209615983073</v>
       </c>
       <c r="Q27">
-        <v>128.1010630752955</v>
+        <v>127.4109615983073</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1003470764517165</v>
+        <v>0.1009430479598146</v>
       </c>
       <c r="T27">
-        <v>0.7508610391492513</v>
+        <v>0.759064811284867</v>
       </c>
       <c r="U27">
         <v>0.07526759442929168</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.28652624387578</v>
+        <v>7.967813696034406</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08957073214949084</v>
+        <v>0.08958031401862887</v>
       </c>
       <c r="C28">
-        <v>1051.924144283439</v>
+        <v>1039.599650141575</v>
       </c>
       <c r="D28">
-        <v>1359.068144283439</v>
+        <v>1358.807650141575</v>
       </c>
       <c r="E28">
-        <v>-607.136</v>
+        <v>-595.0719999999999</v>
       </c>
       <c r="F28">
-        <v>313.664</v>
+        <v>325.7280000000001</v>
       </c>
       <c r="G28">
         <v>6.52</v>
@@ -3577,28 +3577,28 @@
         <v>188.11</v>
       </c>
       <c r="M28">
-        <v>23.60873473906935</v>
+        <v>24.51676299826433</v>
       </c>
       <c r="N28">
-        <v>164.5012652609307</v>
+        <v>163.5932370017357</v>
       </c>
       <c r="O28">
-        <v>39.48030366262336</v>
+        <v>39.26237688041657</v>
       </c>
       <c r="P28">
-        <v>125.0209615983073</v>
+        <v>124.3308601213191</v>
       </c>
       <c r="Q28">
-        <v>127.4109615983073</v>
+        <v>126.7208601213191</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1009430479598146</v>
+        <v>0.1015553474544359</v>
       </c>
       <c r="T28">
-        <v>0.759064811284867</v>
+        <v>0.7674933443009105</v>
       </c>
       <c r="U28">
         <v>0.07526759442929168</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.967813696034406</v>
+        <v>7.672709485070168</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08958031401862887</v>
+        <v>0.08976013588776693</v>
       </c>
       <c r="C29">
-        <v>1039.599650141575</v>
+        <v>1022.665441145596</v>
       </c>
       <c r="D29">
-        <v>1358.807650141575</v>
+        <v>1353.937441145596</v>
       </c>
       <c r="E29">
-        <v>-595.0719999999999</v>
+        <v>-583.0079999999999</v>
       </c>
       <c r="F29">
-        <v>325.7280000000001</v>
+        <v>337.792</v>
       </c>
       <c r="G29">
         <v>6.52</v>
@@ -3659,45 +3659,45 @@
         <v>188.11</v>
       </c>
       <c r="M29">
-        <v>24.51676299826433</v>
+        <v>25.69502485745929</v>
       </c>
       <c r="N29">
-        <v>163.5932370017357</v>
+        <v>162.4149751425407</v>
       </c>
       <c r="O29">
-        <v>39.26237688041657</v>
+        <v>38.97959403420978</v>
       </c>
       <c r="P29">
-        <v>124.3308601213191</v>
+        <v>123.4353811083309</v>
       </c>
       <c r="Q29">
-        <v>126.7208601213191</v>
+        <v>125.8253811083309</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1015553474544359</v>
+        <v>0.1021846552683523</v>
       </c>
       <c r="T29">
-        <v>0.7674933443009105</v>
+        <v>0.7761560032340665</v>
       </c>
       <c r="U29">
-        <v>0.07526759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V29">
         <v>0.24</v>
       </c>
       <c r="W29">
-        <v>0.05720337176626168</v>
+        <v>0.05781137176626167</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.672709485070168</v>
+        <v>7.320872466305144</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08976013588776693</v>
+        <v>0.08977579775690499</v>
       </c>
       <c r="C30">
-        <v>1022.665441145596</v>
+        <v>1010.178914847794</v>
       </c>
       <c r="D30">
-        <v>1353.937441145596</v>
+        <v>1353.514914847794</v>
       </c>
       <c r="E30">
-        <v>-583.0079999999999</v>
+        <v>-570.944</v>
       </c>
       <c r="F30">
-        <v>337.792</v>
+        <v>349.8560000000001</v>
       </c>
       <c r="G30">
         <v>6.52</v>
@@ -3741,28 +3741,28 @@
         <v>188.11</v>
       </c>
       <c r="M30">
-        <v>25.69502485745929</v>
+        <v>26.61270431665427</v>
       </c>
       <c r="N30">
-        <v>162.4149751425407</v>
+        <v>161.4972956833457</v>
       </c>
       <c r="O30">
-        <v>38.97959403420978</v>
+        <v>38.75935096400297</v>
       </c>
       <c r="P30">
-        <v>123.4353811083309</v>
+        <v>122.7379447193427</v>
       </c>
       <c r="Q30">
-        <v>125.8253811083309</v>
+        <v>125.1279447193428</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1021846552683523</v>
+        <v>0.1028316900629424</v>
       </c>
       <c r="T30">
-        <v>0.7761560032340665</v>
+        <v>0.7850626807287198</v>
       </c>
       <c r="U30">
         <v>0.07606759442929167</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.320872466305144</v>
+        <v>7.06842858815669</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08977579775690497</v>
+        <v>0.08979145962604304</v>
       </c>
       <c r="C31">
-        <v>1010.178914847795</v>
+        <v>997.6926521851815</v>
       </c>
       <c r="D31">
-        <v>1353.514914847795</v>
+        <v>1353.092652185182</v>
       </c>
       <c r="E31">
-        <v>-570.944</v>
+        <v>-558.8799999999999</v>
       </c>
       <c r="F31">
-        <v>349.856</v>
+        <v>361.92</v>
       </c>
       <c r="G31">
         <v>6.52</v>
@@ -3823,28 +3823,28 @@
         <v>188.11</v>
       </c>
       <c r="M31">
-        <v>26.61270431665427</v>
+        <v>27.53038377584924</v>
       </c>
       <c r="N31">
-        <v>161.4972956833458</v>
+        <v>160.5796162241508</v>
       </c>
       <c r="O31">
-        <v>38.75935096400298</v>
+        <v>38.53910789379618</v>
       </c>
       <c r="P31">
-        <v>122.7379447193428</v>
+        <v>122.0405083303546</v>
       </c>
       <c r="Q31">
-        <v>125.1279447193428</v>
+        <v>124.4305083303546</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1028316900629424</v>
+        <v>0.1034972115659493</v>
       </c>
       <c r="T31">
-        <v>0.7850626807287198</v>
+        <v>0.7942238347232201</v>
       </c>
       <c r="U31">
         <v>0.07606759442929167</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.068428588156692</v>
+        <v>6.832814301884801</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08979145962604304</v>
+        <v>0.08980712149518109</v>
       </c>
       <c r="C32">
-        <v>997.6926521851815</v>
+        <v>985.2066529110904</v>
       </c>
       <c r="D32">
-        <v>1353.092652185182</v>
+        <v>1352.67065291109</v>
       </c>
       <c r="E32">
-        <v>-558.8799999999999</v>
+        <v>-546.8159999999999</v>
       </c>
       <c r="F32">
-        <v>361.92</v>
+        <v>373.984</v>
       </c>
       <c r="G32">
         <v>6.52</v>
@@ -3905,28 +3905,28 @@
         <v>188.11</v>
       </c>
       <c r="M32">
-        <v>27.53038377584924</v>
+        <v>28.44806323504422</v>
       </c>
       <c r="N32">
-        <v>160.5796162241508</v>
+        <v>159.6619367649558</v>
       </c>
       <c r="O32">
-        <v>38.53910789379618</v>
+        <v>38.31886482358939</v>
       </c>
       <c r="P32">
-        <v>122.0405083303546</v>
+        <v>121.3430719413664</v>
       </c>
       <c r="Q32">
-        <v>124.4305083303546</v>
+        <v>123.7330719413664</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1034972115659493</v>
+        <v>0.1041820235473043</v>
       </c>
       <c r="T32">
-        <v>0.7942238347232201</v>
+        <v>0.8036505294132135</v>
       </c>
       <c r="U32">
         <v>0.07606759442929167</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.832814301884801</v>
+        <v>6.612400937307871</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08980712149518109</v>
+        <v>0.08982278336431915</v>
       </c>
       <c r="C33">
-        <v>985.2066529110904</v>
+        <v>972.7209167791641</v>
       </c>
       <c r="D33">
-        <v>1352.67065291109</v>
+        <v>1352.248916779164</v>
       </c>
       <c r="E33">
-        <v>-546.8159999999999</v>
+        <v>-534.752</v>
       </c>
       <c r="F33">
-        <v>373.984</v>
+        <v>386.0480000000001</v>
       </c>
       <c r="G33">
         <v>6.52</v>
@@ -3987,28 +3987,28 @@
         <v>188.11</v>
       </c>
       <c r="M33">
-        <v>28.44806323504422</v>
+        <v>29.3657426942392</v>
       </c>
       <c r="N33">
-        <v>159.6619367649558</v>
+        <v>158.7442573057608</v>
       </c>
       <c r="O33">
-        <v>38.31886482358939</v>
+        <v>38.0986217533826</v>
       </c>
       <c r="P33">
-        <v>121.3430719413664</v>
+        <v>120.6456355523782</v>
       </c>
       <c r="Q33">
-        <v>123.7330719413664</v>
+        <v>123.0356355523782</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1041820235473043</v>
+        <v>0.1048869770575227</v>
       </c>
       <c r="T33">
-        <v>0.8036505294132135</v>
+        <v>0.8133544798293829</v>
       </c>
       <c r="U33">
         <v>0.07606759442929167</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.612400937307871</v>
+        <v>6.405763408017001</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08982278336431915</v>
+        <v>0.0898384452334572</v>
       </c>
       <c r="C34">
-        <v>972.7209167791641</v>
+        <v>960.2354435433506</v>
       </c>
       <c r="D34">
-        <v>1352.248916779164</v>
+        <v>1351.827443543351</v>
       </c>
       <c r="E34">
-        <v>-534.752</v>
+        <v>-522.6879999999999</v>
       </c>
       <c r="F34">
-        <v>386.0480000000001</v>
+        <v>398.112</v>
       </c>
       <c r="G34">
         <v>6.52</v>
@@ -4069,28 +4069,28 @@
         <v>188.11</v>
       </c>
       <c r="M34">
-        <v>29.3657426942392</v>
+        <v>30.28342215343417</v>
       </c>
       <c r="N34">
-        <v>158.7442573057608</v>
+        <v>157.8265778465658</v>
       </c>
       <c r="O34">
-        <v>38.0986217533826</v>
+        <v>37.8783786831758</v>
       </c>
       <c r="P34">
-        <v>120.6456355523782</v>
+        <v>119.94819916339</v>
       </c>
       <c r="Q34">
-        <v>123.0356355523782</v>
+        <v>122.33819916339</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1048869770575227</v>
+        <v>0.1056129739561057</v>
       </c>
       <c r="T34">
-        <v>0.8133544798293829</v>
+        <v>0.8233481004072292</v>
       </c>
       <c r="U34">
         <v>0.07606759442929167</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.405763408017001</v>
+        <v>6.211649365349819</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0898384452334572</v>
+        <v>0.09011250710259525</v>
       </c>
       <c r="C35">
-        <v>960.2354435433506</v>
+        <v>940.8385155790135</v>
       </c>
       <c r="D35">
-        <v>1351.827443543351</v>
+        <v>1344.494515579014</v>
       </c>
       <c r="E35">
-        <v>-522.6879999999999</v>
+        <v>-510.6239999999999</v>
       </c>
       <c r="F35">
-        <v>398.112</v>
+        <v>410.176</v>
       </c>
       <c r="G35">
         <v>6.52</v>
@@ -4151,45 +4151,45 @@
         <v>188.11</v>
       </c>
       <c r="M35">
-        <v>30.28342215343417</v>
+        <v>31.61127761262915</v>
       </c>
       <c r="N35">
-        <v>157.8265778465658</v>
+        <v>156.4987223873709</v>
       </c>
       <c r="O35">
-        <v>37.8783786831758</v>
+        <v>37.55969337296901</v>
       </c>
       <c r="P35">
-        <v>119.94819916339</v>
+        <v>118.9390290144019</v>
       </c>
       <c r="Q35">
-        <v>122.33819916339</v>
+        <v>121.3290290144019</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1056129739561057</v>
+        <v>0.1063609707607065</v>
       </c>
       <c r="T35">
-        <v>0.8233481004072292</v>
+        <v>0.8336445579722829</v>
       </c>
       <c r="U35">
-        <v>0.07606759442929167</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V35">
         <v>0.24</v>
       </c>
       <c r="W35">
-        <v>0.05781137176626167</v>
+        <v>0.05857137176626168</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.211649365349819</v>
+        <v>5.950724368218747</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09011250710259525</v>
+        <v>0.09013576897173331</v>
       </c>
       <c r="C36">
-        <v>940.8385155790135</v>
+        <v>928.1557711854525</v>
       </c>
       <c r="D36">
-        <v>1344.494515579014</v>
+        <v>1343.875771185453</v>
       </c>
       <c r="E36">
-        <v>-510.6239999999999</v>
+        <v>-498.5599999999999</v>
       </c>
       <c r="F36">
-        <v>410.176</v>
+        <v>422.2400000000001</v>
       </c>
       <c r="G36">
         <v>6.52</v>
@@ -4233,28 +4233,28 @@
         <v>188.11</v>
       </c>
       <c r="M36">
-        <v>31.61127761262915</v>
+        <v>32.54102107182412</v>
       </c>
       <c r="N36">
-        <v>156.4987223873709</v>
+        <v>155.5689789281759</v>
       </c>
       <c r="O36">
-        <v>37.55969337296901</v>
+        <v>37.33655494276222</v>
       </c>
       <c r="P36">
-        <v>118.9390290144019</v>
+        <v>118.2324239854137</v>
       </c>
       <c r="Q36">
-        <v>121.3290290144019</v>
+        <v>120.6224239854137</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1063609707607065</v>
+        <v>0.1071319828516027</v>
       </c>
       <c r="T36">
-        <v>0.8336445579722829</v>
+        <v>0.8442578296162613</v>
       </c>
       <c r="U36">
         <v>0.07706759442929167</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.950724368218747</v>
+        <v>5.780703671983927</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09013576897173331</v>
+        <v>0.09015903084087136</v>
       </c>
       <c r="C37">
-        <v>928.1557711854525</v>
+        <v>915.4735960296443</v>
       </c>
       <c r="D37">
-        <v>1343.875771185453</v>
+        <v>1343.257596029644</v>
       </c>
       <c r="E37">
-        <v>-498.5599999999999</v>
+        <v>-486.4959999999999</v>
       </c>
       <c r="F37">
-        <v>422.2400000000001</v>
+        <v>434.3040000000001</v>
       </c>
       <c r="G37">
         <v>6.52</v>
@@ -4315,28 +4315,28 @@
         <v>188.11</v>
       </c>
       <c r="M37">
-        <v>32.54102107182412</v>
+        <v>33.4707645310191</v>
       </c>
       <c r="N37">
-        <v>155.5689789281759</v>
+        <v>154.6392354689809</v>
       </c>
       <c r="O37">
-        <v>37.33655494276222</v>
+        <v>37.11341651255542</v>
       </c>
       <c r="P37">
-        <v>118.2324239854137</v>
+        <v>117.5258189564255</v>
       </c>
       <c r="Q37">
-        <v>120.6224239854137</v>
+        <v>119.9158189564255</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1071319828516027</v>
+        <v>0.1079270890703393</v>
       </c>
       <c r="T37">
-        <v>0.8442578296162613</v>
+        <v>0.8552027659991142</v>
       </c>
       <c r="U37">
         <v>0.07706759442929167</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.780703671983927</v>
+        <v>5.620128569984373</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09015903084087135</v>
+        <v>0.09018229271000941</v>
       </c>
       <c r="C38">
-        <v>915.4735960296448</v>
+        <v>902.7919893264119</v>
       </c>
       <c r="D38">
-        <v>1343.257596029645</v>
+        <v>1342.639989326412</v>
       </c>
       <c r="E38">
-        <v>-486.4959999999999</v>
+        <v>-474.4319999999999</v>
       </c>
       <c r="F38">
-        <v>434.304</v>
+        <v>446.3680000000001</v>
       </c>
       <c r="G38">
         <v>6.52</v>
@@ -4397,28 +4397,28 @@
         <v>188.11</v>
       </c>
       <c r="M38">
-        <v>33.47076453101909</v>
+        <v>34.40050799021407</v>
       </c>
       <c r="N38">
-        <v>154.6392354689809</v>
+        <v>153.7094920097859</v>
       </c>
       <c r="O38">
-        <v>37.11341651255542</v>
+        <v>36.89027808234862</v>
       </c>
       <c r="P38">
-        <v>117.5258189564255</v>
+        <v>116.8192139274373</v>
       </c>
       <c r="Q38">
-        <v>119.9158189564255</v>
+        <v>119.2092139274373</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1079270890703393</v>
+        <v>0.1087474367563374</v>
       </c>
       <c r="T38">
-        <v>0.8552027659991139</v>
+        <v>0.866495160679835</v>
       </c>
       <c r="U38">
         <v>0.07706759442929167</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.620128569984374</v>
+        <v>5.468233203228038</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09018229271000941</v>
+        <v>0.09020555457914747</v>
       </c>
       <c r="C39">
-        <v>902.7919893264119</v>
+        <v>890.1109502920206</v>
       </c>
       <c r="D39">
-        <v>1342.639989326412</v>
+        <v>1342.022950292021</v>
       </c>
       <c r="E39">
-        <v>-474.4319999999999</v>
+        <v>-462.3679999999999</v>
       </c>
       <c r="F39">
-        <v>446.3680000000001</v>
+        <v>458.432</v>
       </c>
       <c r="G39">
         <v>6.52</v>
@@ -4479,28 +4479,28 @@
         <v>188.11</v>
       </c>
       <c r="M39">
-        <v>34.40050799021407</v>
+        <v>35.33025144940904</v>
       </c>
       <c r="N39">
-        <v>153.7094920097859</v>
+        <v>152.779748550591</v>
       </c>
       <c r="O39">
-        <v>36.89027808234862</v>
+        <v>36.66713965214183</v>
       </c>
       <c r="P39">
-        <v>116.8192139274373</v>
+        <v>116.1126088984491</v>
       </c>
       <c r="Q39">
-        <v>119.2092139274373</v>
+        <v>118.5026088984491</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1087474367563374</v>
+        <v>0.1095942472709162</v>
       </c>
       <c r="T39">
-        <v>0.866495160679835</v>
+        <v>0.8781518261567084</v>
       </c>
       <c r="U39">
         <v>0.07706759442929167</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.468233203228038</v>
+        <v>5.32433232945888</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09020555457914747</v>
+        <v>0.09022881644828554</v>
       </c>
       <c r="C40">
-        <v>890.1109502920206</v>
+        <v>877.4304781441774</v>
       </c>
       <c r="D40">
-        <v>1342.022950292021</v>
+        <v>1341.406478144178</v>
       </c>
       <c r="E40">
-        <v>-462.3679999999999</v>
+        <v>-450.3039999999999</v>
       </c>
       <c r="F40">
-        <v>458.432</v>
+        <v>470.496</v>
       </c>
       <c r="G40">
         <v>6.52</v>
@@ -4561,28 +4561,28 @@
         <v>188.11</v>
       </c>
       <c r="M40">
-        <v>35.33025144940904</v>
+        <v>36.25999490860402</v>
       </c>
       <c r="N40">
-        <v>152.779748550591</v>
+        <v>151.850005091396</v>
       </c>
       <c r="O40">
-        <v>36.66713965214183</v>
+        <v>36.44400122193503</v>
       </c>
       <c r="P40">
-        <v>116.1126088984491</v>
+        <v>115.406003869461</v>
       </c>
       <c r="Q40">
-        <v>118.5026088984491</v>
+        <v>117.796003869461</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1095942472709162</v>
+        <v>0.1104688220646614</v>
       </c>
       <c r="T40">
-        <v>0.8781518261567084</v>
+        <v>0.8901906773869219</v>
       </c>
       <c r="U40">
         <v>0.07706759442929167</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.32433232945888</v>
+        <v>5.187810987677882</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09022881644828554</v>
+        <v>0.09025207831742357</v>
       </c>
       <c r="C41">
-        <v>877.4304781441774</v>
+        <v>864.7505721020262</v>
       </c>
       <c r="D41">
-        <v>1341.406478144178</v>
+        <v>1340.790572102026</v>
       </c>
       <c r="E41">
-        <v>-450.3039999999999</v>
+        <v>-438.2399999999999</v>
       </c>
       <c r="F41">
-        <v>470.496</v>
+        <v>482.5600000000001</v>
       </c>
       <c r="G41">
         <v>6.52</v>
@@ -4643,28 +4643,28 @@
         <v>188.11</v>
       </c>
       <c r="M41">
-        <v>36.25999490860402</v>
+        <v>37.189738367799</v>
       </c>
       <c r="N41">
-        <v>151.850005091396</v>
+        <v>150.920261632201</v>
       </c>
       <c r="O41">
-        <v>36.44400122193503</v>
+        <v>36.22086279172824</v>
       </c>
       <c r="P41">
-        <v>115.406003869461</v>
+        <v>114.6993988404728</v>
       </c>
       <c r="Q41">
-        <v>117.796003869461</v>
+        <v>117.0893988404728</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1104688220646614</v>
+        <v>0.1113725493515315</v>
       </c>
       <c r="T41">
-        <v>0.8901906773869219</v>
+        <v>0.9026308236581426</v>
       </c>
       <c r="U41">
         <v>0.07706759442929167</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.187810987677882</v>
+        <v>5.058115712985935</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09025207831742357</v>
+        <v>0.09027534018656164</v>
       </c>
       <c r="C42">
-        <v>864.7505721020262</v>
+        <v>852.0712313861418</v>
       </c>
       <c r="D42">
-        <v>1340.790572102026</v>
+        <v>1340.175231386142</v>
       </c>
       <c r="E42">
-        <v>-438.2399999999999</v>
+        <v>-426.1759999999999</v>
       </c>
       <c r="F42">
-        <v>482.5600000000001</v>
+        <v>494.6240000000001</v>
       </c>
       <c r="G42">
         <v>6.52</v>
@@ -4725,28 +4725,28 @@
         <v>188.11</v>
       </c>
       <c r="M42">
-        <v>37.189738367799</v>
+        <v>38.11948182699397</v>
       </c>
       <c r="N42">
-        <v>150.920261632201</v>
+        <v>149.9905181730061</v>
       </c>
       <c r="O42">
-        <v>36.22086279172824</v>
+        <v>35.99772436152145</v>
       </c>
       <c r="P42">
-        <v>114.6993988404728</v>
+        <v>113.9927938114846</v>
       </c>
       <c r="Q42">
-        <v>117.0893988404728</v>
+        <v>116.3827938114846</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1113725493515315</v>
+        <v>0.1123069114616853</v>
       </c>
       <c r="T42">
-        <v>0.9026308236581426</v>
+        <v>0.9154926698029637</v>
       </c>
       <c r="U42">
         <v>0.07706759442929167</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.058115712985935</v>
+        <v>4.93474703705945</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09027534018656164</v>
+        <v>0.09029860205569969</v>
       </c>
       <c r="C43">
-        <v>852.0712313861418</v>
+        <v>839.3924552185319</v>
       </c>
       <c r="D43">
-        <v>1340.175231386142</v>
+        <v>1339.560455218532</v>
       </c>
       <c r="E43">
-        <v>-426.1759999999999</v>
+        <v>-414.1119999999999</v>
       </c>
       <c r="F43">
-        <v>494.6240000000001</v>
+        <v>506.6880000000001</v>
       </c>
       <c r="G43">
         <v>6.52</v>
@@ -4807,28 +4807,28 @@
         <v>188.11</v>
       </c>
       <c r="M43">
-        <v>38.11948182699397</v>
+        <v>39.04922528618895</v>
       </c>
       <c r="N43">
-        <v>149.9905181730061</v>
+        <v>149.0607747138111</v>
       </c>
       <c r="O43">
-        <v>35.99772436152145</v>
+        <v>35.77458593131465</v>
       </c>
       <c r="P43">
-        <v>113.9927938114846</v>
+        <v>113.2861887824964</v>
       </c>
       <c r="Q43">
-        <v>116.3827938114846</v>
+        <v>115.6761887824964</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1123069114616853</v>
+        <v>0.1132734929549479</v>
       </c>
       <c r="T43">
-        <v>0.9154926698029637</v>
+        <v>0.9287980278838135</v>
       </c>
       <c r="U43">
         <v>0.07706759442929167</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.93474703705945</v>
+        <v>4.817253059986605</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0902986020556997</v>
+        <v>0.09032186392483774</v>
       </c>
       <c r="C44">
-        <v>839.3924552185317</v>
+        <v>826.7142428226301</v>
       </c>
       <c r="D44">
-        <v>1339.560455218532</v>
+        <v>1338.94624282263</v>
       </c>
       <c r="E44">
-        <v>-414.1119999999999</v>
+        <v>-402.0479999999999</v>
       </c>
       <c r="F44">
-        <v>506.688</v>
+        <v>518.7520000000001</v>
       </c>
       <c r="G44">
         <v>6.52</v>
@@ -4889,28 +4889,28 @@
         <v>188.11</v>
       </c>
       <c r="M44">
-        <v>39.04922528618894</v>
+        <v>39.97896874538392</v>
       </c>
       <c r="N44">
-        <v>149.0607747138111</v>
+        <v>148.1310312546161</v>
       </c>
       <c r="O44">
-        <v>35.77458593131465</v>
+        <v>35.55144750110786</v>
       </c>
       <c r="P44">
-        <v>113.2861887824964</v>
+        <v>112.5795837535082</v>
       </c>
       <c r="Q44">
-        <v>115.6761887824964</v>
+        <v>114.9695837535082</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1132734929549479</v>
+        <v>0.1142739895883249</v>
       </c>
       <c r="T44">
-        <v>0.9287980278838134</v>
+        <v>0.9425702406341664</v>
       </c>
       <c r="U44">
         <v>0.07706759442929167</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.817253059986605</v>
+        <v>4.705223919056683</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09032186392483774</v>
+        <v>0.0903451257939758</v>
       </c>
       <c r="C45">
-        <v>826.7142428226301</v>
+        <v>814.0365934232932</v>
       </c>
       <c r="D45">
-        <v>1338.94624282263</v>
+        <v>1338.332593423293</v>
       </c>
       <c r="E45">
-        <v>-402.0479999999999</v>
+        <v>-389.9839999999999</v>
       </c>
       <c r="F45">
-        <v>518.7520000000001</v>
+        <v>530.816</v>
       </c>
       <c r="G45">
         <v>6.52</v>
@@ -4971,28 +4971,28 @@
         <v>188.11</v>
       </c>
       <c r="M45">
-        <v>39.97896874538392</v>
+        <v>40.90871220457889</v>
       </c>
       <c r="N45">
-        <v>148.1310312546161</v>
+        <v>147.2012877954211</v>
       </c>
       <c r="O45">
-        <v>35.55144750110786</v>
+        <v>35.32830907090107</v>
       </c>
       <c r="P45">
-        <v>112.5795837535082</v>
+        <v>111.8729787245201</v>
       </c>
       <c r="Q45">
-        <v>114.9695837535082</v>
+        <v>114.2629787245201</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1142739895883249</v>
+        <v>0.1153102182443226</v>
       </c>
       <c r="T45">
-        <v>0.9425702406341664</v>
+        <v>0.9568343181256035</v>
       </c>
       <c r="U45">
         <v>0.07706759442929167</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.705223919056683</v>
+        <v>4.598287011805397</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0903451257939758</v>
+        <v>0.09122338766311386</v>
       </c>
       <c r="C46">
-        <v>814.0365934232932</v>
+        <v>779.2085155137963</v>
       </c>
       <c r="D46">
-        <v>1338.332593423293</v>
+        <v>1315.568515513796</v>
       </c>
       <c r="E46">
-        <v>-389.9839999999999</v>
+        <v>-377.9199999999998</v>
       </c>
       <c r="F46">
-        <v>530.816</v>
+        <v>542.8800000000001</v>
       </c>
       <c r="G46">
         <v>6.52</v>
@@ -5053,45 +5053,45 @@
         <v>188.11</v>
       </c>
       <c r="M46">
-        <v>40.90871220457889</v>
+        <v>43.19565566377388</v>
       </c>
       <c r="N46">
-        <v>147.2012877954211</v>
+        <v>144.9143443362261</v>
       </c>
       <c r="O46">
-        <v>35.32830907090107</v>
+        <v>34.77944264069427</v>
       </c>
       <c r="P46">
-        <v>111.8729787245201</v>
+        <v>110.1349016955319</v>
       </c>
       <c r="Q46">
-        <v>114.2629787245201</v>
+        <v>112.5249016955319</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1153102182443226</v>
+        <v>0.1163841279423565</v>
       </c>
       <c r="T46">
-        <v>0.9568343181256035</v>
+        <v>0.9716170893440021</v>
       </c>
       <c r="U46">
-        <v>0.07706759442929167</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V46">
         <v>0.24</v>
       </c>
       <c r="W46">
-        <v>0.05857137176626168</v>
+        <v>0.06047137176626168</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.598287011805397</v>
+        <v>4.354836085003771</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09122338766311386</v>
+        <v>0.09126564953225191</v>
       </c>
       <c r="C47">
-        <v>779.2085155137963</v>
+        <v>766.0686231256658</v>
       </c>
       <c r="D47">
-        <v>1315.568515513796</v>
+        <v>1314.492623125666</v>
       </c>
       <c r="E47">
-        <v>-377.9199999999998</v>
+        <v>-365.8559999999999</v>
       </c>
       <c r="F47">
-        <v>542.8800000000001</v>
+        <v>554.9440000000001</v>
       </c>
       <c r="G47">
         <v>6.52</v>
@@ -5135,28 +5135,28 @@
         <v>188.11</v>
       </c>
       <c r="M47">
-        <v>43.19565566377388</v>
+        <v>44.15555912296885</v>
       </c>
       <c r="N47">
-        <v>144.9143443362261</v>
+        <v>143.9544408770312</v>
       </c>
       <c r="O47">
-        <v>34.77944264069427</v>
+        <v>34.54906581048748</v>
       </c>
       <c r="P47">
-        <v>110.1349016955319</v>
+        <v>109.4053750665437</v>
       </c>
       <c r="Q47">
-        <v>112.5249016955319</v>
+        <v>111.7953750665437</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1163841279423565</v>
+        <v>0.117497812073651</v>
       </c>
       <c r="T47">
-        <v>0.9716170893440021</v>
+        <v>0.9869473706075265</v>
       </c>
       <c r="U47">
         <v>0.07956759442929168</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.354836085003771</v>
+        <v>4.260165735329777</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09126564953225191</v>
+        <v>0.09130791140138994</v>
       </c>
       <c r="C48">
-        <v>766.0686231256658</v>
+        <v>752.930489062599</v>
       </c>
       <c r="D48">
-        <v>1314.492623125666</v>
+        <v>1313.418489062599</v>
       </c>
       <c r="E48">
-        <v>-365.8559999999999</v>
+        <v>-353.7919999999999</v>
       </c>
       <c r="F48">
-        <v>554.9440000000001</v>
+        <v>567.008</v>
       </c>
       <c r="G48">
         <v>6.52</v>
@@ -5217,28 +5217,28 @@
         <v>188.11</v>
       </c>
       <c r="M48">
-        <v>44.15555912296885</v>
+        <v>45.11546258216381</v>
       </c>
       <c r="N48">
-        <v>143.9544408770312</v>
+        <v>142.9945374178362</v>
       </c>
       <c r="O48">
-        <v>34.54906581048748</v>
+        <v>34.31868898028068</v>
       </c>
       <c r="P48">
-        <v>109.4053750665437</v>
+        <v>108.6758484375555</v>
       </c>
       <c r="Q48">
-        <v>111.7953750665437</v>
+        <v>111.0658484375555</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.117497812073651</v>
+        <v>0.1186535220212207</v>
       </c>
       <c r="T48">
-        <v>0.9869473706075265</v>
+        <v>1.002856153050806</v>
       </c>
       <c r="U48">
         <v>0.07956759442929168</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.260165735329777</v>
+        <v>4.169523911173824</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09130791140138994</v>
+        <v>0.091350173270528</v>
       </c>
       <c r="C49">
-        <v>752.930489062599</v>
+        <v>739.7941090176823</v>
       </c>
       <c r="D49">
-        <v>1313.418489062599</v>
+        <v>1312.346109017682</v>
       </c>
       <c r="E49">
-        <v>-353.7919999999999</v>
+        <v>-341.7279999999998</v>
       </c>
       <c r="F49">
-        <v>567.008</v>
+        <v>579.0720000000001</v>
       </c>
       <c r="G49">
         <v>6.52</v>
@@ -5299,28 +5299,28 @@
         <v>188.11</v>
       </c>
       <c r="M49">
-        <v>45.11546258216381</v>
+        <v>46.0753660413588</v>
       </c>
       <c r="N49">
-        <v>142.9945374178362</v>
+        <v>142.0346339586412</v>
       </c>
       <c r="O49">
-        <v>34.31868898028068</v>
+        <v>34.08831215007389</v>
       </c>
       <c r="P49">
-        <v>108.6758484375555</v>
+        <v>107.9463218085673</v>
       </c>
       <c r="Q49">
-        <v>111.0658484375555</v>
+        <v>110.3363218085673</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1186535220212207</v>
+        <v>0.1198536823513892</v>
       </c>
       <c r="T49">
-        <v>1.002856153050806</v>
+        <v>1.019376811741905</v>
       </c>
       <c r="U49">
         <v>0.07956759442929168</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.169523911173824</v>
+        <v>4.082658829691036</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.091350173270528</v>
+        <v>0.09269583513966605</v>
       </c>
       <c r="C50">
-        <v>739.7941090176824</v>
+        <v>694.4767977672033</v>
       </c>
       <c r="D50">
-        <v>1312.346109017682</v>
+        <v>1279.092797767203</v>
       </c>
       <c r="E50">
-        <v>-341.728</v>
+        <v>-329.6639999999999</v>
       </c>
       <c r="F50">
-        <v>579.072</v>
+        <v>591.1360000000001</v>
       </c>
       <c r="G50">
         <v>6.52</v>
@@ -5381,45 +5381,45 @@
         <v>188.11</v>
       </c>
       <c r="M50">
-        <v>46.07536604135879</v>
+        <v>49.10424550055377</v>
       </c>
       <c r="N50">
-        <v>142.0346339586412</v>
+        <v>139.0057544994463</v>
       </c>
       <c r="O50">
-        <v>34.08831215007389</v>
+        <v>33.3613810798671</v>
       </c>
       <c r="P50">
-        <v>107.9463218085673</v>
+        <v>105.6443734195792</v>
       </c>
       <c r="Q50">
-        <v>110.3363218085673</v>
+        <v>108.0343734195792</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1198536823513892</v>
+        <v>0.1211009077925448</v>
       </c>
       <c r="T50">
-        <v>1.019376811741905</v>
+        <v>1.036545339401282</v>
       </c>
       <c r="U50">
-        <v>0.07956759442929168</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V50">
         <v>0.24</v>
       </c>
       <c r="W50">
-        <v>0.06047137176626168</v>
+        <v>0.06313137176626167</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.082658829691036</v>
+        <v>3.830829658056321</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09269583513966605</v>
+        <v>0.0927646970088041</v>
       </c>
       <c r="C51">
-        <v>694.4767977672033</v>
+        <v>680.7563846860728</v>
       </c>
       <c r="D51">
-        <v>1279.092797767203</v>
+        <v>1277.436384686073</v>
       </c>
       <c r="E51">
-        <v>-329.6639999999999</v>
+        <v>-317.5999999999999</v>
       </c>
       <c r="F51">
-        <v>591.1360000000001</v>
+        <v>603.2</v>
       </c>
       <c r="G51">
         <v>6.52</v>
@@ -5463,28 +5463,28 @@
         <v>188.11</v>
       </c>
       <c r="M51">
-        <v>49.10424550055377</v>
+        <v>50.10637295974875</v>
       </c>
       <c r="N51">
-        <v>139.0057544994463</v>
+        <v>138.0036270402513</v>
       </c>
       <c r="O51">
-        <v>33.3613810798671</v>
+        <v>33.12087048966031</v>
       </c>
       <c r="P51">
-        <v>105.6443734195792</v>
+        <v>104.882756550591</v>
       </c>
       <c r="Q51">
-        <v>108.0343734195792</v>
+        <v>107.272756550591</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1211009077925448</v>
+        <v>0.1223980222513465</v>
       </c>
       <c r="T51">
-        <v>1.036545339401282</v>
+        <v>1.054400608167034</v>
       </c>
       <c r="U51">
         <v>0.08306759442929168</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.830829658056321</v>
+        <v>3.754213064895194</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0927646970088041</v>
+        <v>0.09283355887794216</v>
       </c>
       <c r="C52">
-        <v>680.7563846860728</v>
+        <v>667.0402561350785</v>
       </c>
       <c r="D52">
-        <v>1277.436384686073</v>
+        <v>1275.784256135079</v>
       </c>
       <c r="E52">
-        <v>-317.5999999999999</v>
+        <v>-305.5359999999999</v>
       </c>
       <c r="F52">
-        <v>603.2</v>
+        <v>615.264</v>
       </c>
       <c r="G52">
         <v>6.52</v>
@@ -5545,28 +5545,28 @@
         <v>188.11</v>
       </c>
       <c r="M52">
-        <v>50.10637295974875</v>
+        <v>51.10850041894372</v>
       </c>
       <c r="N52">
-        <v>138.0036270402513</v>
+        <v>137.0014995810563</v>
       </c>
       <c r="O52">
-        <v>33.12087048966031</v>
+        <v>32.88035989945351</v>
       </c>
       <c r="P52">
-        <v>104.882756550591</v>
+        <v>104.1211396816028</v>
       </c>
       <c r="Q52">
-        <v>107.272756550591</v>
+        <v>106.5111396816028</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1223980222513465</v>
+        <v>0.1237480801574463</v>
       </c>
       <c r="T52">
-        <v>1.054400608167034</v>
+        <v>1.07298466341302</v>
       </c>
       <c r="U52">
         <v>0.08306759442929168</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.754213064895194</v>
+        <v>3.680601044014896</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09283355887794216</v>
+        <v>0.09290242074708022</v>
       </c>
       <c r="C53">
-        <v>667.0402561350785</v>
+        <v>653.3283955119415</v>
       </c>
       <c r="D53">
-        <v>1275.784256135079</v>
+        <v>1274.136395511942</v>
       </c>
       <c r="E53">
-        <v>-305.5359999999999</v>
+        <v>-293.4719999999999</v>
       </c>
       <c r="F53">
-        <v>615.264</v>
+        <v>627.3280000000001</v>
       </c>
       <c r="G53">
         <v>6.52</v>
@@ -5627,28 +5627,28 @@
         <v>188.11</v>
       </c>
       <c r="M53">
-        <v>51.10850041894372</v>
+        <v>52.1106278781387</v>
       </c>
       <c r="N53">
-        <v>137.0014995810563</v>
+        <v>135.9993721218613</v>
       </c>
       <c r="O53">
-        <v>32.88035989945351</v>
+        <v>32.63984930924671</v>
       </c>
       <c r="P53">
-        <v>104.1211396816028</v>
+        <v>103.3595228126146</v>
       </c>
       <c r="Q53">
-        <v>106.5111396816028</v>
+        <v>105.7495228126146</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1237480801574463</v>
+        <v>0.1251543904763003</v>
       </c>
       <c r="T53">
-        <v>1.07298466341302</v>
+        <v>1.092343054294256</v>
       </c>
       <c r="U53">
         <v>0.08306759442929168</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.680601044014896</v>
+        <v>3.609820254706917</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09290242074708022</v>
+        <v>0.09297128261621826</v>
       </c>
       <c r="C54">
-        <v>653.3283955119415</v>
+        <v>639.6207863000507</v>
       </c>
       <c r="D54">
-        <v>1274.136395511942</v>
+        <v>1272.492786300051</v>
       </c>
       <c r="E54">
-        <v>-293.4719999999999</v>
+        <v>-281.4079999999999</v>
       </c>
       <c r="F54">
-        <v>627.3280000000001</v>
+        <v>639.3920000000001</v>
       </c>
       <c r="G54">
         <v>6.52</v>
@@ -5709,28 +5709,28 @@
         <v>188.11</v>
       </c>
       <c r="M54">
-        <v>52.1106278781387</v>
+        <v>53.11275533733367</v>
       </c>
       <c r="N54">
-        <v>135.9993721218613</v>
+        <v>134.9972446626663</v>
       </c>
       <c r="O54">
-        <v>32.63984930924671</v>
+        <v>32.39933871903992</v>
       </c>
       <c r="P54">
-        <v>103.3595228126146</v>
+        <v>102.5979059436264</v>
       </c>
       <c r="Q54">
-        <v>105.7495228126146</v>
+        <v>104.9879059436264</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1251543904763003</v>
+        <v>0.1266205437874459</v>
       </c>
       <c r="T54">
-        <v>1.092343054294256</v>
+        <v>1.112525206489588</v>
       </c>
       <c r="U54">
         <v>0.08306759442929168</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.609820254706917</v>
+        <v>3.541710438580371</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09297128261621826</v>
+        <v>0.09418926448535632</v>
       </c>
       <c r="C55">
-        <v>639.6207863000507</v>
+        <v>599.1709062721045</v>
       </c>
       <c r="D55">
-        <v>1272.492786300051</v>
+        <v>1244.106906272105</v>
       </c>
       <c r="E55">
-        <v>-281.4079999999999</v>
+        <v>-269.3439999999998</v>
       </c>
       <c r="F55">
-        <v>639.3920000000001</v>
+        <v>651.4560000000001</v>
       </c>
       <c r="G55">
         <v>6.52</v>
@@ -5791,45 +5791,45 @@
         <v>188.11</v>
       </c>
       <c r="M55">
-        <v>53.11275533733367</v>
+        <v>55.93895959652865</v>
       </c>
       <c r="N55">
-        <v>134.9972446626663</v>
+        <v>132.1710404034714</v>
       </c>
       <c r="O55">
-        <v>32.39933871903992</v>
+        <v>31.72104969683312</v>
       </c>
       <c r="P55">
-        <v>102.5979059436264</v>
+        <v>100.4499907066382</v>
       </c>
       <c r="Q55">
-        <v>104.9879059436264</v>
+        <v>102.8399907066382</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1266205437874459</v>
+        <v>0.1281504428947283</v>
       </c>
       <c r="T55">
-        <v>1.112525206489588</v>
+        <v>1.133584843562977</v>
       </c>
       <c r="U55">
-        <v>0.08306759442929168</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V55">
         <v>0.24</v>
       </c>
       <c r="W55">
-        <v>0.06313137176626167</v>
+        <v>0.06525937176626168</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.541710438580371</v>
+        <v>3.362772589207637</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09418926448535632</v>
+        <v>0.09427940635449439</v>
       </c>
       <c r="C56">
-        <v>599.1709062721045</v>
+        <v>585.0563387941892</v>
       </c>
       <c r="D56">
-        <v>1244.106906272105</v>
+        <v>1242.056338794189</v>
       </c>
       <c r="E56">
-        <v>-269.3439999999998</v>
+        <v>-257.2799999999999</v>
       </c>
       <c r="F56">
-        <v>651.4560000000001</v>
+        <v>663.5200000000001</v>
       </c>
       <c r="G56">
         <v>6.52</v>
@@ -5873,28 +5873,28 @@
         <v>188.11</v>
       </c>
       <c r="M56">
-        <v>55.93895959652865</v>
+        <v>56.97486625572362</v>
       </c>
       <c r="N56">
-        <v>132.1710404034714</v>
+        <v>131.1351337442764</v>
       </c>
       <c r="O56">
-        <v>31.72104969683312</v>
+        <v>31.47243209862634</v>
       </c>
       <c r="P56">
-        <v>100.4499907066382</v>
+        <v>99.66270164565006</v>
       </c>
       <c r="Q56">
-        <v>102.8399907066382</v>
+        <v>102.0527016456501</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1281504428947283</v>
+        <v>0.1297483375178899</v>
       </c>
       <c r="T56">
-        <v>1.133584843562977</v>
+        <v>1.155580464506295</v>
       </c>
       <c r="U56">
         <v>0.08586759442929168</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.362772589207637</v>
+        <v>3.301631269403862</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09427940635449439</v>
+        <v>0.09436954822363244</v>
       </c>
       <c r="C57">
-        <v>585.0563387941892</v>
+        <v>570.9485197843771</v>
       </c>
       <c r="D57">
-        <v>1242.056338794189</v>
+        <v>1240.012519784377</v>
       </c>
       <c r="E57">
-        <v>-257.2799999999999</v>
+        <v>-245.2159999999999</v>
       </c>
       <c r="F57">
-        <v>663.5200000000001</v>
+        <v>675.5840000000001</v>
       </c>
       <c r="G57">
         <v>6.52</v>
@@ -5955,28 +5955,28 @@
         <v>188.11</v>
       </c>
       <c r="M57">
-        <v>56.97486625572362</v>
+        <v>58.01077291491859</v>
       </c>
       <c r="N57">
-        <v>131.1351337442764</v>
+        <v>130.0992270850814</v>
       </c>
       <c r="O57">
-        <v>31.47243209862634</v>
+        <v>31.22381450041954</v>
       </c>
       <c r="P57">
-        <v>99.66270164565006</v>
+        <v>98.87541258466189</v>
       </c>
       <c r="Q57">
-        <v>102.0527016456501</v>
+        <v>101.2654125846619</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1297483375178899</v>
+        <v>0.1314188637148316</v>
       </c>
       <c r="T57">
-        <v>1.155580464506295</v>
+        <v>1.178575886401581</v>
       </c>
       <c r="U57">
         <v>0.08586759442929168</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.301631269403862</v>
+        <v>3.242673568164507</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09436954822363244</v>
+        <v>0.0944596900927705</v>
       </c>
       <c r="C58">
-        <v>570.9485197843771</v>
+        <v>556.8474159833345</v>
       </c>
       <c r="D58">
-        <v>1240.012519784377</v>
+        <v>1237.975415983335</v>
       </c>
       <c r="E58">
-        <v>-245.2159999999999</v>
+        <v>-233.1519999999998</v>
       </c>
       <c r="F58">
-        <v>675.5840000000001</v>
+        <v>687.6480000000001</v>
       </c>
       <c r="G58">
         <v>6.52</v>
@@ -6037,28 +6037,28 @@
         <v>188.11</v>
       </c>
       <c r="M58">
-        <v>58.01077291491859</v>
+        <v>59.04667957411358</v>
       </c>
       <c r="N58">
-        <v>130.0992270850814</v>
+        <v>129.0633204258864</v>
       </c>
       <c r="O58">
-        <v>31.22381450041954</v>
+        <v>30.97519690221274</v>
       </c>
       <c r="P58">
-        <v>98.87541258466189</v>
+        <v>98.0881235236737</v>
       </c>
       <c r="Q58">
-        <v>101.2654125846619</v>
+        <v>100.4781235236737</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1314188637148316</v>
+        <v>0.1331670888046543</v>
       </c>
       <c r="T58">
-        <v>1.178575886401581</v>
+        <v>1.202640862803625</v>
       </c>
       <c r="U58">
         <v>0.08586759442929168</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.242673568164507</v>
+        <v>3.185784558196708</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0944596900927705</v>
+        <v>0.09454983196190853</v>
       </c>
       <c r="C59">
-        <v>556.8474159833345</v>
+        <v>542.752994349925</v>
       </c>
       <c r="D59">
-        <v>1237.975415983335</v>
+        <v>1235.944994349925</v>
       </c>
       <c r="E59">
-        <v>-233.1519999999998</v>
+        <v>-221.0879999999999</v>
       </c>
       <c r="F59">
-        <v>687.6480000000001</v>
+        <v>699.7120000000001</v>
       </c>
       <c r="G59">
         <v>6.52</v>
@@ -6119,28 +6119,28 @@
         <v>188.11</v>
       </c>
       <c r="M59">
-        <v>59.04667957411358</v>
+        <v>60.08258623330855</v>
       </c>
       <c r="N59">
-        <v>129.0633204258864</v>
+        <v>128.0274137666915</v>
       </c>
       <c r="O59">
-        <v>30.97519690221274</v>
+        <v>30.72657930400595</v>
       </c>
       <c r="P59">
-        <v>98.0881235236737</v>
+        <v>97.30083446268551</v>
       </c>
       <c r="Q59">
-        <v>100.4781235236737</v>
+        <v>99.69083446268552</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1331670888046543</v>
+        <v>0.134998562708278</v>
       </c>
       <c r="T59">
-        <v>1.202640862803625</v>
+        <v>1.227851790462909</v>
       </c>
       <c r="U59">
         <v>0.08586759442929168</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.185784558196708</v>
+        <v>3.130857238227799</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09454983196190854</v>
+        <v>0.09463997383104659</v>
       </c>
       <c r="C60">
-        <v>542.7529943499248</v>
+        <v>528.6652220594196</v>
       </c>
       <c r="D60">
-        <v>1235.944994349925</v>
+        <v>1233.92122205942</v>
       </c>
       <c r="E60">
-        <v>-221.088</v>
+        <v>-209.0239999999999</v>
       </c>
       <c r="F60">
-        <v>699.712</v>
+        <v>711.7760000000001</v>
       </c>
       <c r="G60">
         <v>6.52</v>
@@ -6201,28 +6201,28 @@
         <v>188.11</v>
       </c>
       <c r="M60">
-        <v>60.08258623330854</v>
+        <v>61.11849289250352</v>
       </c>
       <c r="N60">
-        <v>128.0274137666915</v>
+        <v>126.9915071074965</v>
       </c>
       <c r="O60">
-        <v>30.72657930400595</v>
+        <v>30.47796170579916</v>
       </c>
       <c r="P60">
-        <v>97.30083446268551</v>
+        <v>96.51354540169733</v>
       </c>
       <c r="Q60">
-        <v>99.69083446268552</v>
+        <v>98.90354540169733</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.134998562708278</v>
+        <v>0.1369193768023224</v>
       </c>
       <c r="T60">
-        <v>1.227851790462909</v>
+        <v>1.254292519471427</v>
       </c>
       <c r="U60">
         <v>0.08586759442929168</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.1308572382278</v>
+        <v>3.077791861308684</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09463997383104659</v>
+        <v>0.09473011570018464</v>
       </c>
       <c r="C61">
-        <v>528.6652220594196</v>
+        <v>514.5840665017344</v>
       </c>
       <c r="D61">
-        <v>1233.92122205942</v>
+        <v>1231.904066501734</v>
       </c>
       <c r="E61">
-        <v>-209.0239999999999</v>
+        <v>-196.9599999999999</v>
       </c>
       <c r="F61">
-        <v>711.7760000000001</v>
+        <v>723.84</v>
       </c>
       <c r="G61">
         <v>6.52</v>
@@ -6283,28 +6283,28 @@
         <v>188.11</v>
       </c>
       <c r="M61">
-        <v>61.11849289250352</v>
+        <v>62.15439955169849</v>
       </c>
       <c r="N61">
-        <v>126.9915071074965</v>
+        <v>125.9556004483015</v>
       </c>
       <c r="O61">
-        <v>30.47796170579916</v>
+        <v>30.22934410759236</v>
       </c>
       <c r="P61">
-        <v>96.51354540169733</v>
+        <v>95.72625634070916</v>
       </c>
       <c r="Q61">
-        <v>98.90354540169733</v>
+        <v>98.11625634070916</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1369193768023224</v>
+        <v>0.1389362316010691</v>
       </c>
       <c r="T61">
-        <v>1.254292519471427</v>
+        <v>1.28205528493037</v>
       </c>
       <c r="U61">
         <v>0.08586759442929168</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.077791861308684</v>
+        <v>3.026495330286874</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09473011570018464</v>
+        <v>0.0984363375693227</v>
       </c>
       <c r="C62">
-        <v>514.5840665017344</v>
+        <v>424.9342433498982</v>
       </c>
       <c r="D62">
-        <v>1231.904066501734</v>
+        <v>1154.318243349898</v>
       </c>
       <c r="E62">
-        <v>-196.9599999999999</v>
+        <v>-184.896</v>
       </c>
       <c r="F62">
-        <v>723.84</v>
+        <v>735.904</v>
       </c>
       <c r="G62">
         <v>6.52</v>
@@ -6365,45 +6365,45 @@
         <v>188.11</v>
       </c>
       <c r="M62">
-        <v>62.15439955169849</v>
+        <v>68.93035741089346</v>
       </c>
       <c r="N62">
-        <v>125.9556004483015</v>
+        <v>119.1796425891065</v>
       </c>
       <c r="O62">
-        <v>30.22934410759236</v>
+        <v>28.60311422138557</v>
       </c>
       <c r="P62">
-        <v>95.72625634070916</v>
+        <v>90.57652836772098</v>
       </c>
       <c r="Q62">
-        <v>98.11625634070916</v>
+        <v>92.96652836772098</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1389362316010691</v>
+        <v>0.1410565148510335</v>
       </c>
       <c r="T62">
-        <v>1.28205528493037</v>
+        <v>1.311241781951311</v>
       </c>
       <c r="U62">
-        <v>0.08586759442929168</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V62">
         <v>0.24</v>
       </c>
       <c r="W62">
-        <v>0.06525937176626168</v>
+        <v>0.07118737176626168</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>3.026495330286874</v>
+        <v>2.728986285080134</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0984363375693227</v>
+        <v>0.09858575943846076</v>
       </c>
       <c r="C63">
-        <v>424.9342433498982</v>
+        <v>409.9466803804896</v>
       </c>
       <c r="D63">
-        <v>1154.318243349898</v>
+        <v>1151.39468038049</v>
       </c>
       <c r="E63">
-        <v>-184.896</v>
+        <v>-172.8319999999999</v>
       </c>
       <c r="F63">
-        <v>735.904</v>
+        <v>747.9680000000001</v>
       </c>
       <c r="G63">
         <v>6.52</v>
@@ -6447,28 +6447,28 @@
         <v>188.11</v>
       </c>
       <c r="M63">
-        <v>68.93035741089346</v>
+        <v>70.06036327008844</v>
       </c>
       <c r="N63">
-        <v>119.1796425891065</v>
+        <v>118.0496367299116</v>
       </c>
       <c r="O63">
-        <v>28.60311422138557</v>
+        <v>28.33191281517878</v>
       </c>
       <c r="P63">
-        <v>90.57652836772098</v>
+        <v>89.7177239147328</v>
       </c>
       <c r="Q63">
-        <v>92.96652836772098</v>
+        <v>92.1077239147328</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1410565148510335</v>
+        <v>0.1432883919562593</v>
       </c>
       <c r="T63">
-        <v>1.311241781951311</v>
+        <v>1.341964410394407</v>
       </c>
       <c r="U63">
         <v>0.09366759442929168</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.728986285080134</v>
+        <v>2.68497037725626</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09858575943846076</v>
+        <v>0.0987351813075988</v>
       </c>
       <c r="C64">
-        <v>409.9466803804896</v>
+        <v>394.9738891215217</v>
       </c>
       <c r="D64">
-        <v>1151.39468038049</v>
+        <v>1148.485889121522</v>
       </c>
       <c r="E64">
-        <v>-172.8319999999999</v>
+        <v>-160.7679999999999</v>
       </c>
       <c r="F64">
-        <v>747.9680000000001</v>
+        <v>760.032</v>
       </c>
       <c r="G64">
         <v>6.52</v>
@@ -6529,28 +6529,28 @@
         <v>188.11</v>
       </c>
       <c r="M64">
-        <v>70.06036327008844</v>
+        <v>71.19036912928341</v>
       </c>
       <c r="N64">
-        <v>118.0496367299116</v>
+        <v>116.9196308707166</v>
       </c>
       <c r="O64">
-        <v>28.33191281517878</v>
+        <v>28.06071140897198</v>
       </c>
       <c r="P64">
-        <v>89.7177239147328</v>
+        <v>88.85891946174462</v>
       </c>
       <c r="Q64">
-        <v>92.1077239147328</v>
+        <v>91.24891946174462</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1432883919562593</v>
+        <v>0.1456409110671728</v>
       </c>
       <c r="T64">
-        <v>1.341964410394407</v>
+        <v>1.374347721456047</v>
       </c>
       <c r="U64">
         <v>0.09366759442929168</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.68497037725626</v>
+        <v>2.642351799839495</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0987351813075988</v>
+        <v>0.09888460317673683</v>
       </c>
       <c r="C65">
-        <v>394.9738891215217</v>
+        <v>380.0157579009164</v>
       </c>
       <c r="D65">
-        <v>1148.485889121522</v>
+        <v>1145.591757900916</v>
       </c>
       <c r="E65">
-        <v>-160.7679999999999</v>
+        <v>-148.7039999999998</v>
       </c>
       <c r="F65">
-        <v>760.032</v>
+        <v>772.0960000000001</v>
       </c>
       <c r="G65">
         <v>6.52</v>
@@ -6611,28 +6611,28 @@
         <v>188.11</v>
       </c>
       <c r="M65">
-        <v>71.19036912928341</v>
+        <v>72.32037498847839</v>
       </c>
       <c r="N65">
-        <v>116.9196308707166</v>
+        <v>115.7896250115216</v>
       </c>
       <c r="O65">
-        <v>28.06071140897198</v>
+        <v>27.78951000276519</v>
       </c>
       <c r="P65">
-        <v>88.85891946174462</v>
+        <v>88.00011500875644</v>
       </c>
       <c r="Q65">
-        <v>91.24891946174462</v>
+        <v>90.39011500875644</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1456409110671728</v>
+        <v>0.1481241256842483</v>
       </c>
       <c r="T65">
-        <v>1.374347721456047</v>
+        <v>1.408530105354446</v>
       </c>
       <c r="U65">
         <v>0.09366759442929168</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.642351799839495</v>
+        <v>2.601065052967003</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09888460317673683</v>
+        <v>0.09903402504587491</v>
       </c>
       <c r="C66">
-        <v>380.0157579009164</v>
+        <v>365.0721761694003</v>
       </c>
       <c r="D66">
-        <v>1145.591757900916</v>
+        <v>1142.7121761694</v>
       </c>
       <c r="E66">
-        <v>-148.7039999999998</v>
+        <v>-136.6399999999999</v>
       </c>
       <c r="F66">
-        <v>772.0960000000001</v>
+        <v>784.1600000000001</v>
       </c>
       <c r="G66">
         <v>6.52</v>
@@ -6693,28 +6693,28 @@
         <v>188.11</v>
       </c>
       <c r="M66">
-        <v>72.32037498847839</v>
+        <v>73.45038084767337</v>
       </c>
       <c r="N66">
-        <v>115.7896250115216</v>
+        <v>114.6596191523266</v>
       </c>
       <c r="O66">
-        <v>27.78951000276519</v>
+        <v>27.51830859655839</v>
       </c>
       <c r="P66">
-        <v>88.00011500875644</v>
+        <v>87.14131055576826</v>
       </c>
       <c r="Q66">
-        <v>90.39011500875644</v>
+        <v>89.53131055576826</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1481241256842483</v>
+        <v>0.1507492382794424</v>
       </c>
       <c r="T66">
-        <v>1.408530105354446</v>
+        <v>1.444665768332754</v>
       </c>
       <c r="U66">
         <v>0.09366759442929168</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.601065052967003</v>
+        <v>2.561048667536741</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09903402504587491</v>
+        <v>0.09918344691501296</v>
       </c>
       <c r="C67">
-        <v>365.0721761694003</v>
+        <v>350.1430344864297</v>
       </c>
       <c r="D67">
-        <v>1142.7121761694</v>
+        <v>1139.84703448643</v>
       </c>
       <c r="E67">
-        <v>-136.6399999999999</v>
+        <v>-124.5759999999999</v>
       </c>
       <c r="F67">
-        <v>784.1600000000001</v>
+        <v>796.224</v>
       </c>
       <c r="G67">
         <v>6.52</v>
@@ -6775,28 +6775,28 @@
         <v>188.11</v>
       </c>
       <c r="M67">
-        <v>73.45038084767337</v>
+        <v>74.58038670686834</v>
       </c>
       <c r="N67">
-        <v>114.6596191523266</v>
+        <v>113.5296132931317</v>
       </c>
       <c r="O67">
-        <v>27.51830859655839</v>
+        <v>27.2471071903516</v>
       </c>
       <c r="P67">
-        <v>87.14131055576826</v>
+        <v>86.28250610278008</v>
       </c>
       <c r="Q67">
-        <v>89.53131055576826</v>
+        <v>88.67250610278008</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1507492382794424</v>
+        <v>0.153528769262589</v>
       </c>
       <c r="T67">
-        <v>1.444665768332754</v>
+        <v>1.48292705854508</v>
       </c>
       <c r="U67">
         <v>0.09366759442929168</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.561048667536741</v>
+        <v>2.52224489984679</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09918344691501296</v>
+        <v>0.101318748784151</v>
       </c>
       <c r="C68">
-        <v>350.1430344864297</v>
+        <v>298.6503587745841</v>
       </c>
       <c r="D68">
-        <v>1139.84703448643</v>
+        <v>1100.418358774584</v>
       </c>
       <c r="E68">
-        <v>-124.5759999999999</v>
+        <v>-112.5119999999998</v>
       </c>
       <c r="F68">
-        <v>796.224</v>
+        <v>808.2880000000001</v>
       </c>
       <c r="G68">
         <v>6.52</v>
@@ -6857,45 +6857,45 @@
         <v>188.11</v>
       </c>
       <c r="M68">
-        <v>74.58038670686834</v>
+        <v>78.86271576606333</v>
       </c>
       <c r="N68">
-        <v>113.5296132931317</v>
+        <v>109.2472842339367</v>
       </c>
       <c r="O68">
-        <v>27.2471071903516</v>
+        <v>26.2193482161448</v>
       </c>
       <c r="P68">
-        <v>86.28250610278008</v>
+        <v>83.02793601779189</v>
       </c>
       <c r="Q68">
-        <v>88.67250610278008</v>
+        <v>85.41793601779189</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.153528769262589</v>
+        <v>0.1564767566689567</v>
       </c>
       <c r="T68">
-        <v>1.48292705854508</v>
+        <v>1.523507214830879</v>
       </c>
       <c r="U68">
-        <v>0.09366759442929168</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V68">
         <v>0.24</v>
       </c>
       <c r="W68">
-        <v>0.07118737176626168</v>
+        <v>0.07415137176626167</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.52224489984679</v>
+        <v>2.385284328249683</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.101318748784151</v>
+        <v>0.1014978106532891</v>
       </c>
       <c r="C69">
-        <v>298.6503587745841</v>
+        <v>283.4035589602915</v>
       </c>
       <c r="D69">
-        <v>1100.418358774584</v>
+        <v>1097.235558960292</v>
       </c>
       <c r="E69">
-        <v>-112.5119999999998</v>
+        <v>-100.4479999999999</v>
       </c>
       <c r="F69">
-        <v>808.2880000000001</v>
+        <v>820.3520000000001</v>
       </c>
       <c r="G69">
         <v>6.52</v>
@@ -6939,28 +6939,28 @@
         <v>188.11</v>
       </c>
       <c r="M69">
-        <v>78.86271576606333</v>
+        <v>80.03977122525829</v>
       </c>
       <c r="N69">
-        <v>109.2472842339367</v>
+        <v>108.0702287747417</v>
       </c>
       <c r="O69">
-        <v>26.2193482161448</v>
+        <v>25.93685490593801</v>
       </c>
       <c r="P69">
-        <v>83.02793601779189</v>
+        <v>82.13337386880372</v>
       </c>
       <c r="Q69">
-        <v>85.41793601779189</v>
+        <v>84.52337386880372</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1564767566689567</v>
+        <v>0.1596089932882223</v>
       </c>
       <c r="T69">
-        <v>1.523507214830879</v>
+        <v>1.566623630884542</v>
       </c>
       <c r="U69">
         <v>0.09756759442929168</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.385284328249683</v>
+        <v>2.350206617540128</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1014978106532891</v>
+        <v>0.1016768725224271</v>
       </c>
       <c r="C70">
-        <v>283.4035589602915</v>
+        <v>268.1751176165003</v>
       </c>
       <c r="D70">
-        <v>1097.235558960292</v>
+        <v>1094.0711176165</v>
       </c>
       <c r="E70">
-        <v>-100.4479999999999</v>
+        <v>-88.38399999999979</v>
       </c>
       <c r="F70">
-        <v>820.3520000000001</v>
+        <v>832.4160000000002</v>
       </c>
       <c r="G70">
         <v>6.52</v>
@@ -7021,28 +7021,28 @@
         <v>188.11</v>
       </c>
       <c r="M70">
-        <v>80.03977122525829</v>
+        <v>81.21682668445328</v>
       </c>
       <c r="N70">
-        <v>108.0702287747417</v>
+        <v>106.8931733155467</v>
       </c>
       <c r="O70">
-        <v>25.93685490593801</v>
+        <v>25.65436159573121</v>
       </c>
       <c r="P70">
-        <v>82.13337386880372</v>
+        <v>81.23881171981552</v>
       </c>
       <c r="Q70">
-        <v>84.52337386880372</v>
+        <v>83.62881171981552</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1596089932882223</v>
+        <v>0.1629433096893761</v>
       </c>
       <c r="T70">
-        <v>1.566623630884542</v>
+        <v>1.612521751199731</v>
       </c>
       <c r="U70">
         <v>0.09756759442929168</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.350206617540128</v>
+        <v>2.316145652068532</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1016768725224271</v>
+        <v>0.1018559343915652</v>
       </c>
       <c r="C71">
-        <v>268.1751176165003</v>
+        <v>252.9648763617962</v>
       </c>
       <c r="D71">
-        <v>1094.0711176165</v>
+        <v>1090.924876361796</v>
       </c>
       <c r="E71">
-        <v>-88.38399999999979</v>
+        <v>-76.31999999999982</v>
       </c>
       <c r="F71">
-        <v>832.4160000000002</v>
+        <v>844.4800000000001</v>
       </c>
       <c r="G71">
         <v>6.52</v>
@@ -7103,28 +7103,28 @@
         <v>188.11</v>
       </c>
       <c r="M71">
-        <v>81.21682668445328</v>
+        <v>82.39388214364826</v>
       </c>
       <c r="N71">
-        <v>106.8931733155467</v>
+        <v>105.7161178563518</v>
       </c>
       <c r="O71">
-        <v>25.65436159573121</v>
+        <v>25.37186828552442</v>
       </c>
       <c r="P71">
-        <v>81.23881171981552</v>
+        <v>80.34424957082734</v>
       </c>
       <c r="Q71">
-        <v>83.62881171981552</v>
+        <v>82.73424957082734</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1629433096893761</v>
+        <v>0.1664999138506067</v>
       </c>
       <c r="T71">
-        <v>1.612521751199731</v>
+        <v>1.661479746202599</v>
       </c>
       <c r="U71">
         <v>0.09756759442929168</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.316145652068532</v>
+        <v>2.283057857038982</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1018559343915652</v>
+        <v>0.1020349962607032</v>
       </c>
       <c r="C72">
-        <v>252.9648763617962</v>
+        <v>237.7726786313812</v>
       </c>
       <c r="D72">
-        <v>1090.924876361796</v>
+        <v>1087.796678631381</v>
       </c>
       <c r="E72">
-        <v>-76.31999999999982</v>
+        <v>-64.25599999999974</v>
       </c>
       <c r="F72">
-        <v>844.4800000000001</v>
+        <v>856.5440000000002</v>
       </c>
       <c r="G72">
         <v>6.52</v>
@@ -7185,28 +7185,28 @@
         <v>188.11</v>
       </c>
       <c r="M72">
-        <v>82.39388214364826</v>
+        <v>83.57093760284323</v>
       </c>
       <c r="N72">
-        <v>105.7161178563518</v>
+        <v>104.5390623971568</v>
       </c>
       <c r="O72">
-        <v>25.37186828552442</v>
+        <v>25.08937497531763</v>
       </c>
       <c r="P72">
-        <v>80.34424957082734</v>
+        <v>79.44968742183916</v>
       </c>
       <c r="Q72">
-        <v>82.73424957082734</v>
+        <v>81.83968742183916</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1664999138506067</v>
+        <v>0.1703018010574395</v>
       </c>
       <c r="T72">
-        <v>1.661479746202599</v>
+        <v>1.713814154653941</v>
       </c>
       <c r="U72">
         <v>0.09756759442929168</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.283057857038982</v>
+        <v>2.250902112573644</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1020349962607032</v>
+        <v>0.1022140581298413</v>
       </c>
       <c r="C73">
-        <v>237.7726786313816</v>
+        <v>222.5983696511058</v>
       </c>
       <c r="D73">
-        <v>1087.796678631382</v>
+        <v>1084.686369651106</v>
       </c>
       <c r="E73">
-        <v>-64.25599999999997</v>
+        <v>-52.19199999999989</v>
       </c>
       <c r="F73">
-        <v>856.544</v>
+        <v>868.6080000000001</v>
       </c>
       <c r="G73">
         <v>6.52</v>
@@ -7267,28 +7267,28 @@
         <v>188.11</v>
       </c>
       <c r="M73">
-        <v>83.57093760284322</v>
+        <v>84.74799306203819</v>
       </c>
       <c r="N73">
-        <v>104.5390623971568</v>
+        <v>103.3620069379618</v>
       </c>
       <c r="O73">
-        <v>25.08937497531763</v>
+        <v>24.80688166511084</v>
       </c>
       <c r="P73">
-        <v>79.44968742183917</v>
+        <v>78.55512527285099</v>
       </c>
       <c r="Q73">
-        <v>81.83968742183917</v>
+        <v>80.94512527285099</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1703018010574394</v>
+        <v>0.1743752516361888</v>
       </c>
       <c r="T73">
-        <v>1.71381415465394</v>
+        <v>1.769886735137521</v>
       </c>
       <c r="U73">
         <v>0.09756759442929168</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.250902112573645</v>
+        <v>2.219639583232344</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1022140581298413</v>
+        <v>0.1023931199989793</v>
       </c>
       <c r="C74">
-        <v>222.5983696511058</v>
+        <v>207.4417964119384</v>
       </c>
       <c r="D74">
-        <v>1084.686369651106</v>
+        <v>1081.593796411938</v>
       </c>
       <c r="E74">
-        <v>-52.19199999999989</v>
+        <v>-40.12799999999993</v>
       </c>
       <c r="F74">
-        <v>868.6080000000001</v>
+        <v>880.672</v>
       </c>
       <c r="G74">
         <v>6.52</v>
@@ -7349,28 +7349,28 @@
         <v>188.11</v>
       </c>
       <c r="M74">
-        <v>84.74799306203819</v>
+        <v>85.92504852123317</v>
       </c>
       <c r="N74">
-        <v>103.3620069379618</v>
+        <v>102.1849514787668</v>
       </c>
       <c r="O74">
-        <v>24.80688166511084</v>
+        <v>24.52438835490404</v>
       </c>
       <c r="P74">
-        <v>78.55512527285099</v>
+        <v>77.6605631238628</v>
       </c>
       <c r="Q74">
-        <v>80.94512527285099</v>
+        <v>80.0505631238628</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1743752516361888</v>
+        <v>0.1787504392948456</v>
       </c>
       <c r="T74">
-        <v>1.769886735137521</v>
+        <v>1.830112840101366</v>
       </c>
       <c r="U74">
         <v>0.09756759442929168</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.219639583232344</v>
+        <v>2.18923356154423</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1023931199989793</v>
+        <v>0.1025721818681174</v>
       </c>
       <c r="C75">
-        <v>207.4417964119384</v>
+        <v>192.3028076448775</v>
       </c>
       <c r="D75">
-        <v>1081.593796411938</v>
+        <v>1078.518807644878</v>
       </c>
       <c r="E75">
-        <v>-40.12799999999993</v>
+        <v>-28.06399999999985</v>
       </c>
       <c r="F75">
-        <v>880.672</v>
+        <v>892.7360000000001</v>
       </c>
       <c r="G75">
         <v>6.52</v>
@@ -7431,28 +7431,28 @@
         <v>188.11</v>
       </c>
       <c r="M75">
-        <v>85.92504852123317</v>
+        <v>87.10210398042814</v>
       </c>
       <c r="N75">
-        <v>102.1849514787668</v>
+        <v>101.0078960195719</v>
       </c>
       <c r="O75">
-        <v>24.52438835490404</v>
+        <v>24.24189504469725</v>
       </c>
       <c r="P75">
-        <v>77.6605631238628</v>
+        <v>76.76600097487463</v>
       </c>
       <c r="Q75">
-        <v>80.0505631238628</v>
+        <v>79.15600097487463</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1787504392948456</v>
+        <v>0.1834621798503221</v>
       </c>
       <c r="T75">
-        <v>1.830112840101366</v>
+        <v>1.894971722370123</v>
       </c>
       <c r="U75">
         <v>0.09756759442929168</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.18923356154423</v>
+        <v>2.159649324226064</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1025721818681174</v>
+        <v>0.1027512437372554</v>
       </c>
       <c r="C76">
-        <v>192.3028076448775</v>
+        <v>177.181253796285</v>
       </c>
       <c r="D76">
-        <v>1078.518807644878</v>
+        <v>1075.461253796285</v>
       </c>
       <c r="E76">
-        <v>-28.06399999999985</v>
+        <v>-15.99999999999989</v>
       </c>
       <c r="F76">
-        <v>892.7360000000001</v>
+        <v>904.8000000000001</v>
       </c>
       <c r="G76">
         <v>6.52</v>
@@ -7513,28 +7513,28 @@
         <v>188.11</v>
       </c>
       <c r="M76">
-        <v>87.10210398042814</v>
+        <v>88.27915943962311</v>
       </c>
       <c r="N76">
-        <v>101.0078960195719</v>
+        <v>99.8308405603769</v>
       </c>
       <c r="O76">
-        <v>24.24189504469725</v>
+        <v>23.95940173449046</v>
       </c>
       <c r="P76">
-        <v>76.76600097487463</v>
+        <v>75.87143882588644</v>
       </c>
       <c r="Q76">
-        <v>79.15600097487463</v>
+        <v>78.26143882588644</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1834621798503221</v>
+        <v>0.1885508596502368</v>
       </c>
       <c r="T76">
-        <v>1.894971722370123</v>
+        <v>1.965019315220381</v>
       </c>
       <c r="U76">
         <v>0.09756759442929168</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.159649324226064</v>
+        <v>2.13085399990305</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1027512437372554</v>
+        <v>0.1029303056063935</v>
       </c>
       <c r="C77">
-        <v>177.181253796285</v>
+        <v>162.0769870036415</v>
       </c>
       <c r="D77">
-        <v>1075.461253796285</v>
+        <v>1072.420987003642</v>
       </c>
       <c r="E77">
-        <v>-15.99999999999989</v>
+        <v>-3.935999999999922</v>
       </c>
       <c r="F77">
-        <v>904.8000000000001</v>
+        <v>916.864</v>
       </c>
       <c r="G77">
         <v>6.52</v>
@@ -7595,28 +7595,28 @@
         <v>188.11</v>
       </c>
       <c r="M77">
-        <v>88.27915943962311</v>
+        <v>89.45621489881809</v>
       </c>
       <c r="N77">
-        <v>99.8308405603769</v>
+        <v>98.65378510118192</v>
       </c>
       <c r="O77">
-        <v>23.95940173449046</v>
+        <v>23.67690842428366</v>
       </c>
       <c r="P77">
-        <v>75.87143882588644</v>
+        <v>74.97687667689826</v>
       </c>
       <c r="Q77">
-        <v>78.26143882588644</v>
+        <v>77.36687667689826</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1885508596502368</v>
+        <v>0.1940635961001443</v>
       </c>
       <c r="T77">
-        <v>1.965019315220381</v>
+        <v>2.040904207474826</v>
       </c>
       <c r="U77">
         <v>0.09756759442929168</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.13085399990305</v>
+        <v>2.102816447272747</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1029303056063935</v>
+        <v>0.1031093674755315</v>
       </c>
       <c r="C78">
-        <v>162.0769870036415</v>
+        <v>146.9898610717089</v>
       </c>
       <c r="D78">
-        <v>1072.420987003642</v>
+        <v>1069.397861071709</v>
       </c>
       <c r="E78">
-        <v>-3.935999999999922</v>
+        <v>8.128000000000156</v>
       </c>
       <c r="F78">
-        <v>916.864</v>
+        <v>928.9280000000001</v>
       </c>
       <c r="G78">
         <v>6.52</v>
@@ -7677,28 +7677,28 @@
         <v>188.11</v>
       </c>
       <c r="M78">
-        <v>89.45621489881809</v>
+        <v>90.63327035801308</v>
       </c>
       <c r="N78">
-        <v>98.65378510118192</v>
+        <v>97.47672964198694</v>
       </c>
       <c r="O78">
-        <v>23.67690842428366</v>
+        <v>23.39441511407686</v>
       </c>
       <c r="P78">
-        <v>74.97687667689826</v>
+        <v>74.08231452791007</v>
       </c>
       <c r="Q78">
-        <v>77.36687667689826</v>
+        <v>76.47231452791007</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1940635961001443</v>
+        <v>0.2000557009370003</v>
       </c>
       <c r="T78">
-        <v>2.040904207474826</v>
+        <v>2.123387786012267</v>
       </c>
       <c r="U78">
         <v>0.09756759442929168</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.102816447272747</v>
+        <v>2.075507142762711</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1031093674755315</v>
+        <v>0.1032884293446696</v>
       </c>
       <c r="C79">
-        <v>146.9898610717089</v>
+        <v>131.919731449097</v>
       </c>
       <c r="D79">
-        <v>1069.397861071709</v>
+        <v>1066.391731449097</v>
       </c>
       <c r="E79">
-        <v>8.128000000000156</v>
+        <v>20.19200000000012</v>
       </c>
       <c r="F79">
-        <v>928.9280000000001</v>
+        <v>940.9920000000001</v>
       </c>
       <c r="G79">
         <v>6.52</v>
@@ -7759,28 +7759,28 @@
         <v>188.11</v>
       </c>
       <c r="M79">
-        <v>90.63327035801308</v>
+        <v>91.81032581720804</v>
       </c>
       <c r="N79">
-        <v>97.47672964198694</v>
+        <v>96.29967418279197</v>
       </c>
       <c r="O79">
-        <v>23.39441511407686</v>
+        <v>23.11192180387007</v>
       </c>
       <c r="P79">
-        <v>74.08231452791007</v>
+        <v>73.1877523789219</v>
       </c>
       <c r="Q79">
-        <v>76.47231452791007</v>
+        <v>75.5777523789219</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2000557009370003</v>
+        <v>0.2065925425772068</v>
       </c>
       <c r="T79">
-        <v>2.123387786012267</v>
+        <v>2.213369871689476</v>
       </c>
       <c r="U79">
         <v>0.09756759442929168</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.075507142762711</v>
+        <v>2.048898076829856</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1032884293446696</v>
+        <v>0.1034674912138077</v>
       </c>
       <c r="C80">
-        <v>131.919731449097</v>
+        <v>116.8664552052234</v>
       </c>
       <c r="D80">
-        <v>1066.391731449097</v>
+        <v>1063.402455205224</v>
       </c>
       <c r="E80">
-        <v>20.19200000000012</v>
+        <v>32.2560000000002</v>
       </c>
       <c r="F80">
-        <v>940.9920000000001</v>
+        <v>953.0560000000002</v>
       </c>
       <c r="G80">
         <v>6.52</v>
@@ -7841,28 +7841,28 @@
         <v>188.11</v>
       </c>
       <c r="M80">
-        <v>91.81032581720804</v>
+        <v>92.98738127640303</v>
       </c>
       <c r="N80">
-        <v>96.29967418279197</v>
+        <v>95.12261872359699</v>
       </c>
       <c r="O80">
-        <v>23.11192180387007</v>
+        <v>22.82942849366328</v>
       </c>
       <c r="P80">
-        <v>73.1877523789219</v>
+        <v>72.29319022993371</v>
       </c>
       <c r="Q80">
-        <v>75.5777523789219</v>
+        <v>74.68319022993371</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2065925425772068</v>
+        <v>0.2137519405640997</v>
       </c>
       <c r="T80">
-        <v>2.213369871689476</v>
+        <v>2.311921679812133</v>
       </c>
       <c r="U80">
         <v>0.09756759442929168</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.048898076829856</v>
+        <v>2.022962658135807</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1034674912138077</v>
+        <v>0.1122801530829457</v>
       </c>
       <c r="C81">
-        <v>116.8664552052234</v>
+        <v>-24.11862226332016</v>
       </c>
       <c r="D81">
-        <v>1063.402455205224</v>
+        <v>934.48137773668</v>
       </c>
       <c r="E81">
-        <v>32.2560000000002</v>
+        <v>44.32000000000016</v>
       </c>
       <c r="F81">
-        <v>953.0560000000002</v>
+        <v>965.1200000000001</v>
       </c>
       <c r="G81">
         <v>6.52</v>
@@ -7923,45 +7923,45 @@
         <v>188.11</v>
       </c>
       <c r="M81">
-        <v>92.98738127640303</v>
+        <v>107.869140735598</v>
       </c>
       <c r="N81">
-        <v>95.12261872359699</v>
+        <v>80.240859264402</v>
       </c>
       <c r="O81">
-        <v>22.82942849366328</v>
+        <v>19.25780622345648</v>
       </c>
       <c r="P81">
-        <v>72.29319022993371</v>
+        <v>60.98305304094552</v>
       </c>
       <c r="Q81">
-        <v>74.68319022993371</v>
+        <v>63.37305304094552</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2137519405640997</v>
+        <v>0.2216272783496819</v>
       </c>
       <c r="T81">
-        <v>2.311921679812133</v>
+        <v>2.420328668747055</v>
       </c>
       <c r="U81">
-        <v>0.09756759442929168</v>
+        <v>0.1117675944292917</v>
       </c>
       <c r="V81">
         <v>0.24</v>
       </c>
       <c r="W81">
-        <v>0.07415137176626167</v>
+        <v>0.08494337176626168</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y81">
-        <v>2.022962658135807</v>
+        <v>1.743872239244802</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1122801530829457</v>
+        <v>0.1125671349520838</v>
       </c>
       <c r="C82">
-        <v>-24.11862226332016</v>
+        <v>-39.85741684001823</v>
       </c>
       <c r="D82">
-        <v>934.48137773668</v>
+        <v>930.8065831599819</v>
       </c>
       <c r="E82">
-        <v>44.32000000000016</v>
+        <v>56.38400000000013</v>
       </c>
       <c r="F82">
-        <v>965.1200000000001</v>
+        <v>977.1840000000001</v>
       </c>
       <c r="G82">
         <v>6.52</v>
@@ -8005,28 +8005,28 @@
         <v>188.11</v>
       </c>
       <c r="M82">
-        <v>107.869140735598</v>
+        <v>109.217504994793</v>
       </c>
       <c r="N82">
-        <v>80.240859264402</v>
+        <v>78.89249500520704</v>
       </c>
       <c r="O82">
-        <v>19.25780622345648</v>
+        <v>18.93419880124969</v>
       </c>
       <c r="P82">
-        <v>60.98305304094552</v>
+        <v>59.95829620395735</v>
       </c>
       <c r="Q82">
-        <v>63.37305304094552</v>
+        <v>62.34829620395735</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2216272783496819</v>
+        <v>0.2303315990600622</v>
       </c>
       <c r="T82">
-        <v>2.420328668747055</v>
+        <v>2.540146919675127</v>
       </c>
       <c r="U82">
         <v>0.1117675944292917</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.743872239244802</v>
+        <v>1.722342952340546</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1125671349520838</v>
+        <v>0.1128541168212218</v>
       </c>
       <c r="C83">
-        <v>-39.85741684001823</v>
+        <v>-55.56742278731883</v>
       </c>
       <c r="D83">
-        <v>930.8065831599819</v>
+        <v>927.1605772126813</v>
       </c>
       <c r="E83">
-        <v>56.38400000000013</v>
+        <v>68.44800000000021</v>
       </c>
       <c r="F83">
-        <v>977.1840000000001</v>
+        <v>989.2480000000002</v>
       </c>
       <c r="G83">
         <v>6.52</v>
@@ -8087,28 +8087,28 @@
         <v>188.11</v>
       </c>
       <c r="M83">
-        <v>109.217504994793</v>
+        <v>110.565869253988</v>
       </c>
       <c r="N83">
-        <v>78.89249500520704</v>
+        <v>77.54413074601206</v>
       </c>
       <c r="O83">
-        <v>18.93419880124969</v>
+        <v>18.61059137904289</v>
       </c>
       <c r="P83">
-        <v>59.95829620395735</v>
+        <v>58.93353936696916</v>
       </c>
       <c r="Q83">
-        <v>62.34829620395735</v>
+        <v>61.32353936696916</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2303315990600622</v>
+        <v>0.2400030665160403</v>
       </c>
       <c r="T83">
-        <v>2.540146919675127</v>
+        <v>2.673278309595208</v>
       </c>
       <c r="U83">
         <v>0.1117675944292917</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.722342952340546</v>
+        <v>1.701338769994929</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1128541168212218</v>
+        <v>0.1131410986903599</v>
       </c>
       <c r="C84">
-        <v>-55.56742278731883</v>
+        <v>-71.24897708383958</v>
       </c>
       <c r="D84">
-        <v>927.1605772126813</v>
+        <v>923.5430229161606</v>
       </c>
       <c r="E84">
-        <v>68.44800000000021</v>
+        <v>80.51200000000017</v>
       </c>
       <c r="F84">
-        <v>989.2480000000002</v>
+        <v>1001.312</v>
       </c>
       <c r="G84">
         <v>6.52</v>
@@ -8169,28 +8169,28 @@
         <v>188.11</v>
       </c>
       <c r="M84">
-        <v>110.565869253988</v>
+        <v>111.9142335131829</v>
       </c>
       <c r="N84">
-        <v>77.54413074601206</v>
+        <v>76.19576648681709</v>
       </c>
       <c r="O84">
-        <v>18.61059137904289</v>
+        <v>18.2869839568361</v>
       </c>
       <c r="P84">
-        <v>58.93353936696916</v>
+        <v>57.90878252998099</v>
       </c>
       <c r="Q84">
-        <v>61.32353936696916</v>
+        <v>60.29878252998099</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2400030665160403</v>
+        <v>0.2508123536727218</v>
       </c>
       <c r="T84">
-        <v>2.673278309595208</v>
+        <v>2.822072215976474</v>
       </c>
       <c r="U84">
         <v>0.1117675944292917</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.701338769994929</v>
+        <v>1.680840712525111</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1131410986903599</v>
+        <v>0.1134280805594979</v>
       </c>
       <c r="C85">
-        <v>-71.24897708383958</v>
+        <v>-86.90241146940582</v>
       </c>
       <c r="D85">
-        <v>923.5430229161606</v>
+        <v>919.9535885305944</v>
       </c>
       <c r="E85">
-        <v>80.51200000000017</v>
+        <v>92.57600000000025</v>
       </c>
       <c r="F85">
-        <v>1001.312</v>
+        <v>1013.376</v>
       </c>
       <c r="G85">
         <v>6.52</v>
@@ -8251,28 +8251,28 @@
         <v>188.11</v>
       </c>
       <c r="M85">
-        <v>111.9142335131829</v>
+        <v>113.2625977723779</v>
       </c>
       <c r="N85">
-        <v>76.19576648681709</v>
+        <v>74.8474022276221</v>
       </c>
       <c r="O85">
-        <v>18.2869839568361</v>
+        <v>17.9633765346293</v>
       </c>
       <c r="P85">
-        <v>57.90878252998099</v>
+        <v>56.88402569299279</v>
       </c>
       <c r="Q85">
-        <v>60.29878252998099</v>
+        <v>59.27402569299279</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2508123536727218</v>
+        <v>0.2629728017239883</v>
       </c>
       <c r="T85">
-        <v>2.822072215976474</v>
+        <v>2.989465360655398</v>
       </c>
       <c r="U85">
         <v>0.1117675944292917</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.680840712525111</v>
+        <v>1.660830704042669</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1134280805594979</v>
+        <v>0.113715062428636</v>
       </c>
       <c r="C86">
-        <v>-86.90241146940571</v>
+        <v>-102.5280525464607</v>
       </c>
       <c r="D86">
-        <v>919.9535885305944</v>
+        <v>916.3919474535394</v>
       </c>
       <c r="E86">
-        <v>92.57600000000014</v>
+        <v>104.6400000000001</v>
       </c>
       <c r="F86">
-        <v>1013.376</v>
+        <v>1025.44</v>
       </c>
       <c r="G86">
         <v>6.52</v>
@@ -8333,28 +8333,28 @@
         <v>188.11</v>
       </c>
       <c r="M86">
-        <v>113.2625977723779</v>
+        <v>114.6109620315729</v>
       </c>
       <c r="N86">
-        <v>74.84740222762211</v>
+        <v>73.49903796842715</v>
       </c>
       <c r="O86">
-        <v>17.9633765346293</v>
+        <v>17.63976911242251</v>
       </c>
       <c r="P86">
-        <v>56.88402569299281</v>
+        <v>55.85926885600463</v>
       </c>
       <c r="Q86">
-        <v>59.27402569299281</v>
+        <v>58.24926885600463</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2629728017239882</v>
+        <v>0.276754642848757</v>
       </c>
       <c r="T86">
-        <v>2.989465360655396</v>
+        <v>3.179177591291511</v>
       </c>
       <c r="U86">
         <v>0.1117675944292917</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.660830704042669</v>
+        <v>1.641291519289226</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.113715062428636</v>
+        <v>0.114002044297774</v>
       </c>
       <c r="C87">
-        <v>-102.5280525464607</v>
+        <v>-118.1262218791305</v>
       </c>
       <c r="D87">
-        <v>916.3919474535394</v>
+        <v>912.8577781208696</v>
       </c>
       <c r="E87">
-        <v>104.6400000000001</v>
+        <v>116.7040000000002</v>
       </c>
       <c r="F87">
-        <v>1025.44</v>
+        <v>1037.504</v>
       </c>
       <c r="G87">
         <v>6.52</v>
@@ -8415,28 +8415,28 @@
         <v>188.11</v>
       </c>
       <c r="M87">
-        <v>114.6109620315729</v>
+        <v>115.9593262907678</v>
       </c>
       <c r="N87">
-        <v>73.49903796842715</v>
+        <v>72.15067370923217</v>
       </c>
       <c r="O87">
-        <v>17.63976911242251</v>
+        <v>17.31616169021572</v>
       </c>
       <c r="P87">
-        <v>55.85926885600463</v>
+        <v>54.83451201901644</v>
       </c>
       <c r="Q87">
-        <v>58.24926885600463</v>
+        <v>57.22451201901644</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.276754642848757</v>
+        <v>0.2925053184199213</v>
       </c>
       <c r="T87">
-        <v>3.179177591291511</v>
+        <v>3.395991569161355</v>
       </c>
       <c r="U87">
         <v>0.1117675944292917</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.641291519289226</v>
+        <v>1.622206734181212</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.114002044297774</v>
+        <v>0.1142890261669121</v>
       </c>
       <c r="C88">
-        <v>-118.1262218791305</v>
+        <v>-133.6972360900046</v>
       </c>
       <c r="D88">
-        <v>912.8577781208696</v>
+        <v>909.3507639099954</v>
       </c>
       <c r="E88">
-        <v>116.7040000000002</v>
+        <v>128.768</v>
       </c>
       <c r="F88">
-        <v>1037.504</v>
+        <v>1049.568</v>
       </c>
       <c r="G88">
         <v>6.52</v>
@@ -8497,28 +8497,28 @@
         <v>188.11</v>
       </c>
       <c r="M88">
-        <v>115.9593262907678</v>
+        <v>117.3076905499628</v>
       </c>
       <c r="N88">
-        <v>72.15067370923217</v>
+        <v>70.8023094500372</v>
       </c>
       <c r="O88">
-        <v>17.31616169021572</v>
+        <v>16.99255426800893</v>
       </c>
       <c r="P88">
-        <v>54.83451201901644</v>
+        <v>53.80975518202827</v>
       </c>
       <c r="Q88">
-        <v>57.22451201901644</v>
+        <v>56.19975518202827</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2925053184199213</v>
+        <v>0.3106791748481879</v>
       </c>
       <c r="T88">
-        <v>3.395991569161355</v>
+        <v>3.64616154362656</v>
       </c>
       <c r="U88">
         <v>0.1117675944292917</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.622206734181212</v>
+        <v>1.603560679765336</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1142890261669121</v>
+        <v>0.1145760080360501</v>
       </c>
       <c r="C89">
-        <v>-133.6972360900046</v>
+        <v>-149.2414069546961</v>
       </c>
       <c r="D89">
-        <v>909.3507639099954</v>
+        <v>905.870593045304</v>
       </c>
       <c r="E89">
-        <v>128.768</v>
+        <v>140.8320000000001</v>
       </c>
       <c r="F89">
-        <v>1049.568</v>
+        <v>1061.632</v>
       </c>
       <c r="G89">
         <v>6.52</v>
@@ -8579,28 +8579,28 @@
         <v>188.11</v>
       </c>
       <c r="M89">
-        <v>117.3076905499628</v>
+        <v>118.6560548091578</v>
       </c>
       <c r="N89">
-        <v>70.8023094500372</v>
+        <v>69.45394519084222</v>
       </c>
       <c r="O89">
-        <v>16.99255426800893</v>
+        <v>16.66894684580213</v>
       </c>
       <c r="P89">
-        <v>53.80975518202827</v>
+        <v>52.78499834504009</v>
       </c>
       <c r="Q89">
-        <v>56.19975518202827</v>
+        <v>55.17499834504009</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3106791748481879</v>
+        <v>0.3318820073478322</v>
       </c>
       <c r="T89">
-        <v>3.64616154362656</v>
+        <v>3.938026513835967</v>
       </c>
       <c r="U89">
         <v>0.1117675944292917</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.603560679765336</v>
+        <v>1.585338399313457</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1145760080360501</v>
+        <v>0.1148629899051882</v>
       </c>
       <c r="C90">
-        <v>-149.2414069546961</v>
+        <v>-164.7590414942347</v>
       </c>
       <c r="D90">
-        <v>905.870593045304</v>
+        <v>902.4169585057655</v>
       </c>
       <c r="E90">
-        <v>140.8320000000001</v>
+        <v>152.8960000000002</v>
       </c>
       <c r="F90">
-        <v>1061.632</v>
+        <v>1073.696</v>
       </c>
       <c r="G90">
         <v>6.52</v>
@@ -8661,28 +8661,28 @@
         <v>188.11</v>
       </c>
       <c r="M90">
-        <v>118.6560548091578</v>
+        <v>120.0044190683528</v>
       </c>
       <c r="N90">
-        <v>69.45394519084222</v>
+        <v>68.10558093164724</v>
       </c>
       <c r="O90">
-        <v>16.66894684580213</v>
+        <v>16.34533942359534</v>
       </c>
       <c r="P90">
-        <v>52.78499834504009</v>
+        <v>51.76024150805191</v>
       </c>
       <c r="Q90">
-        <v>55.17499834504009</v>
+        <v>54.15024150805191</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3318820073478322</v>
+        <v>0.3569399003019573</v>
       </c>
       <c r="T90">
-        <v>3.938026513835967</v>
+        <v>4.282957842265265</v>
       </c>
       <c r="U90">
         <v>0.1117675944292917</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.585338399313457</v>
+        <v>1.567525608309935</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1148629899051882</v>
+        <v>0.1151499717743263</v>
       </c>
       <c r="C91">
-        <v>-164.7590414942347</v>
+        <v>-180.2504420653585</v>
       </c>
       <c r="D91">
-        <v>902.4169585057655</v>
+        <v>898.9895579346418</v>
       </c>
       <c r="E91">
-        <v>152.8960000000002</v>
+        <v>164.9600000000003</v>
       </c>
       <c r="F91">
-        <v>1073.696</v>
+        <v>1085.76</v>
       </c>
       <c r="G91">
         <v>6.52</v>
@@ -8743,28 +8743,28 @@
         <v>188.11</v>
       </c>
       <c r="M91">
-        <v>120.0044190683528</v>
+        <v>121.3527833275478</v>
       </c>
       <c r="N91">
-        <v>68.10558093164724</v>
+        <v>66.75721667245224</v>
       </c>
       <c r="O91">
-        <v>16.34533942359534</v>
+        <v>16.02173200138854</v>
       </c>
       <c r="P91">
-        <v>51.76024150805191</v>
+        <v>50.7354846710637</v>
       </c>
       <c r="Q91">
-        <v>54.15024150805191</v>
+        <v>53.1254846710637</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3569399003019573</v>
+        <v>0.3870093718469074</v>
       </c>
       <c r="T91">
-        <v>4.282957842265265</v>
+        <v>4.696875436380424</v>
       </c>
       <c r="U91">
         <v>0.1117675944292917</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.567525608309935</v>
+        <v>1.550108657106491</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1151499717743263</v>
+        <v>0.1154369536434643</v>
       </c>
       <c r="C92">
-        <v>-180.2504420653585</v>
+        <v>-195.7159064487532</v>
       </c>
       <c r="D92">
-        <v>898.9895579346418</v>
+        <v>895.5880935512469</v>
       </c>
       <c r="E92">
-        <v>164.9600000000003</v>
+        <v>177.0240000000001</v>
       </c>
       <c r="F92">
-        <v>1085.76</v>
+        <v>1097.824</v>
       </c>
       <c r="G92">
         <v>6.52</v>
@@ -8825,28 +8825,28 @@
         <v>188.11</v>
       </c>
       <c r="M92">
-        <v>121.3527833275478</v>
+        <v>122.7011475867427</v>
       </c>
       <c r="N92">
-        <v>66.75721667245224</v>
+        <v>65.40885241325729</v>
       </c>
       <c r="O92">
-        <v>16.02173200138854</v>
+        <v>15.69812457918175</v>
       </c>
       <c r="P92">
-        <v>50.7354846710637</v>
+        <v>49.71072783407554</v>
       </c>
       <c r="Q92">
-        <v>53.1254846710637</v>
+        <v>52.10072783407554</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3870093718469074</v>
+        <v>0.4237609481796242</v>
       </c>
       <c r="T92">
-        <v>4.696875436380424</v>
+        <v>5.202774718076729</v>
       </c>
       <c r="U92">
         <v>0.1117675944292917</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.550108657106491</v>
+        <v>1.533074496039387</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1154369536434643</v>
+        <v>0.1157239355126023</v>
       </c>
       <c r="C93">
-        <v>-195.7159064487532</v>
+        <v>-211.1557279352988</v>
       </c>
       <c r="D93">
-        <v>895.5880935512469</v>
+        <v>892.2122720647013</v>
       </c>
       <c r="E93">
-        <v>177.0240000000001</v>
+        <v>189.0880000000002</v>
       </c>
       <c r="F93">
-        <v>1097.824</v>
+        <v>1109.888</v>
       </c>
       <c r="G93">
         <v>6.52</v>
@@ -8907,28 +8907,28 @@
         <v>188.11</v>
       </c>
       <c r="M93">
-        <v>122.7011475867427</v>
+        <v>124.0495118459377</v>
       </c>
       <c r="N93">
-        <v>65.40885241325729</v>
+        <v>64.06048815406231</v>
       </c>
       <c r="O93">
-        <v>15.69812457918175</v>
+        <v>15.37451715697495</v>
       </c>
       <c r="P93">
-        <v>49.71072783407554</v>
+        <v>48.68597099708736</v>
       </c>
       <c r="Q93">
-        <v>52.10072783407554</v>
+        <v>51.07597099708736</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4237609481796242</v>
+        <v>0.4697004185955204</v>
       </c>
       <c r="T93">
-        <v>5.202774718076729</v>
+        <v>5.83514882019711</v>
       </c>
       <c r="U93">
         <v>0.1117675944292917</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.533074496039387</v>
+        <v>1.516410642821567</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1157239355126023</v>
+        <v>0.1160109173817404</v>
       </c>
       <c r="C94">
-        <v>-211.1557279352988</v>
+        <v>-226.5701954103688</v>
       </c>
       <c r="D94">
-        <v>892.2122720647013</v>
+        <v>888.8618045896314</v>
       </c>
       <c r="E94">
-        <v>189.0880000000002</v>
+        <v>201.1520000000003</v>
       </c>
       <c r="F94">
-        <v>1109.888</v>
+        <v>1121.952</v>
       </c>
       <c r="G94">
         <v>6.52</v>
@@ -8989,28 +8989,28 @@
         <v>188.11</v>
       </c>
       <c r="M94">
-        <v>124.0495118459377</v>
+        <v>125.3978761051327</v>
       </c>
       <c r="N94">
-        <v>64.06048815406231</v>
+        <v>62.71212389486733</v>
       </c>
       <c r="O94">
-        <v>15.37451715697495</v>
+        <v>15.05090973476816</v>
       </c>
       <c r="P94">
-        <v>48.68597099708736</v>
+        <v>47.66121416009917</v>
       </c>
       <c r="Q94">
-        <v>51.07597099708736</v>
+        <v>50.05121416009917</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4697004185955204</v>
+        <v>0.5287654519873867</v>
       </c>
       <c r="T94">
-        <v>5.83514882019711</v>
+        <v>6.648201237209029</v>
       </c>
       <c r="U94">
         <v>0.1117675944292917</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.516410642821567</v>
+        <v>1.50010515203854</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1160109173817404</v>
+        <v>0.1576388272383233</v>
       </c>
       <c r="C95">
-        <v>-226.5701954103688</v>
+        <v>-552.0738475401126</v>
       </c>
       <c r="D95">
-        <v>888.8618045896314</v>
+        <v>575.4221524598875</v>
       </c>
       <c r="E95">
-        <v>201.1520000000003</v>
+        <v>213.2160000000001</v>
       </c>
       <c r="F95">
-        <v>1121.952</v>
+        <v>1134.016</v>
       </c>
       <c r="G95">
         <v>6.52</v>
@@ -9071,45 +9071,45 @@
         <v>188.11</v>
       </c>
       <c r="M95">
-        <v>125.3978761051327</v>
+        <v>191.1583491643277</v>
       </c>
       <c r="N95">
-        <v>62.71212389486733</v>
+        <v>-3.048349164327647</v>
       </c>
       <c r="O95">
-        <v>15.05090973476816</v>
+        <v>-0.7316037994386352</v>
       </c>
       <c r="P95">
-        <v>47.66121416009917</v>
+        <v>-2.316745364889012</v>
       </c>
       <c r="Q95">
-        <v>50.05121416009917</v>
+        <v>0.07325463511098862</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5287654519873867</v>
+        <v>0.6101283711315436</v>
       </c>
       <c r="T95">
-        <v>6.648201237209029</v>
+        <v>7.768192444636532</v>
       </c>
       <c r="U95">
-        <v>0.1117675944292917</v>
+        <v>0.1685675944292917</v>
       </c>
       <c r="V95">
-        <v>0.24</v>
+        <v>0.2361727865791009</v>
       </c>
       <c r="W95">
-        <v>0.08494337176626168</v>
+        <v>0.1287565159259902</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y95">
-        <v>1.50010515203854</v>
+        <v>0.9840532774129204</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1576388272383233</v>
+        <v>0.1588665031826163</v>
       </c>
       <c r="C96">
-        <v>-552.0738475401126</v>
+        <v>-570.0604450797492</v>
       </c>
       <c r="D96">
-        <v>575.4221524598875</v>
+        <v>569.4995549202509</v>
       </c>
       <c r="E96">
-        <v>213.2160000000001</v>
+        <v>225.2800000000002</v>
       </c>
       <c r="F96">
-        <v>1134.016</v>
+        <v>1146.08</v>
       </c>
       <c r="G96">
         <v>6.52</v>
@@ -9153,37 +9153,37 @@
         <v>188.11</v>
       </c>
       <c r="M96">
-        <v>191.1583491643277</v>
+        <v>193.1919486235226</v>
       </c>
       <c r="N96">
-        <v>-3.048349164327647</v>
+        <v>-5.081948623522635</v>
       </c>
       <c r="O96">
-        <v>-0.7316037994386352</v>
+        <v>-1.219667669645432</v>
       </c>
       <c r="P96">
-        <v>-2.316745364889012</v>
+        <v>-3.862280953877203</v>
       </c>
       <c r="Q96">
-        <v>0.07325463511098862</v>
+        <v>-1.472280953877203</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6101283711315436</v>
+        <v>0.7229940453578529</v>
       </c>
       <c r="T96">
-        <v>7.768192444636532</v>
+        <v>9.321830933563845</v>
       </c>
       <c r="U96">
         <v>0.1685675944292917</v>
       </c>
       <c r="V96">
-        <v>0.2361727865791009</v>
+        <v>0.2336867572466892</v>
       </c>
       <c r="W96">
-        <v>0.1287565159259902</v>
+        <v>0.1291755799102355</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.9840532774129204</v>
+        <v>0.9736948218612053</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1588665031826163</v>
+        <v>0.1600941791269092</v>
       </c>
       <c r="C97">
-        <v>-570.0604450797492</v>
+        <v>-587.9263666809981</v>
       </c>
       <c r="D97">
-        <v>569.4995549202509</v>
+        <v>563.6976333190022</v>
       </c>
       <c r="E97">
-        <v>225.2800000000002</v>
+        <v>237.3440000000003</v>
       </c>
       <c r="F97">
-        <v>1146.08</v>
+        <v>1158.144</v>
       </c>
       <c r="G97">
         <v>6.52</v>
@@ -9235,37 +9235,37 @@
         <v>188.11</v>
       </c>
       <c r="M97">
-        <v>193.1919486235226</v>
+        <v>195.2255480827176</v>
       </c>
       <c r="N97">
-        <v>-5.081948623522635</v>
+        <v>-7.115548082717623</v>
       </c>
       <c r="O97">
-        <v>-1.219667669645432</v>
+        <v>-1.707731539852229</v>
       </c>
       <c r="P97">
-        <v>-3.862280953877203</v>
+        <v>-5.407816542865394</v>
       </c>
       <c r="Q97">
-        <v>-1.472280953877203</v>
+        <v>-3.017816542865394</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7229940453578529</v>
+        <v>0.8922925566973163</v>
       </c>
       <c r="T97">
-        <v>9.321830933563845</v>
+        <v>11.65228866695481</v>
       </c>
       <c r="U97">
         <v>0.1685675944292917</v>
       </c>
       <c r="V97">
-        <v>0.2336867572466892</v>
+        <v>0.2312525201920362</v>
       </c>
       <c r="W97">
-        <v>0.1291755799102355</v>
+        <v>0.129585913394809</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.9736948218612053</v>
+        <v>0.9635521674668177</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1600941791269092</v>
+        <v>0.1613218550712021</v>
       </c>
       <c r="C98">
-        <v>-587.9263666809978</v>
+        <v>-605.6752633982827</v>
       </c>
       <c r="D98">
-        <v>563.6976333190022</v>
+        <v>558.0127366017174</v>
       </c>
       <c r="E98">
-        <v>237.3440000000001</v>
+        <v>249.4080000000001</v>
       </c>
       <c r="F98">
-        <v>1158.144</v>
+        <v>1170.208</v>
       </c>
       <c r="G98">
         <v>6.52</v>
@@ -9317,37 +9317,37 @@
         <v>188.11</v>
       </c>
       <c r="M98">
-        <v>195.2255480827176</v>
+        <v>197.2591475419126</v>
       </c>
       <c r="N98">
-        <v>-7.115548082717595</v>
+        <v>-9.149147541912583</v>
       </c>
       <c r="O98">
-        <v>-1.707731539852223</v>
+        <v>-2.19579541005902</v>
       </c>
       <c r="P98">
-        <v>-5.407816542865373</v>
+        <v>-6.953352131853563</v>
       </c>
       <c r="Q98">
-        <v>-3.017816542865372</v>
+        <v>-4.563352131853563</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8922925566973142</v>
+        <v>1.174456742263086</v>
       </c>
       <c r="T98">
-        <v>11.65228866695478</v>
+        <v>15.53638488927304</v>
       </c>
       <c r="U98">
         <v>0.1685675944292917</v>
       </c>
       <c r="V98">
-        <v>0.2312525201920363</v>
+        <v>0.2288684735921184</v>
       </c>
       <c r="W98">
-        <v>0.129585913394809</v>
+        <v>0.1299877863951644</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.9635521674668178</v>
+        <v>0.9536186399671599</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1613218550712021</v>
+        <v>0.162549531015495</v>
       </c>
       <c r="C99">
-        <v>-605.6752633982827</v>
+        <v>-623.3106404728624</v>
       </c>
       <c r="D99">
-        <v>558.0127366017174</v>
+        <v>552.4413595271378</v>
       </c>
       <c r="E99">
-        <v>249.4080000000001</v>
+        <v>261.4720000000002</v>
       </c>
       <c r="F99">
-        <v>1170.208</v>
+        <v>1182.272</v>
       </c>
       <c r="G99">
         <v>6.52</v>
@@ -9399,37 +9399,37 @@
         <v>188.11</v>
       </c>
       <c r="M99">
-        <v>197.2591475419126</v>
+        <v>199.2927470011076</v>
       </c>
       <c r="N99">
-        <v>-9.149147541912583</v>
+        <v>-11.18274700110757</v>
       </c>
       <c r="O99">
-        <v>-2.19579541005902</v>
+        <v>-2.683859280265817</v>
       </c>
       <c r="P99">
-        <v>-6.953352131853563</v>
+        <v>-8.498887720841754</v>
       </c>
       <c r="Q99">
-        <v>-4.563352131853563</v>
+        <v>-6.108887720841754</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.174456742263086</v>
+        <v>1.738785113394628</v>
       </c>
       <c r="T99">
-        <v>15.53638488927304</v>
+        <v>23.30457733390956</v>
       </c>
       <c r="U99">
         <v>0.1685675944292917</v>
       </c>
       <c r="V99">
-        <v>0.2288684735921184</v>
+        <v>0.2265330810044437</v>
       </c>
       <c r="W99">
-        <v>0.1299877863951644</v>
+        <v>0.1303814579057168</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.9536186399671599</v>
+        <v>0.9438878375185153</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.162549531015495</v>
+        <v>0.163777206959788</v>
       </c>
       <c r="C100">
-        <v>-623.3106404728624</v>
+        <v>-640.8358645400951</v>
       </c>
       <c r="D100">
-        <v>552.4413595271378</v>
+        <v>546.9801354599049</v>
       </c>
       <c r="E100">
-        <v>261.4720000000002</v>
+        <v>273.5360000000001</v>
       </c>
       <c r="F100">
-        <v>1182.272</v>
+        <v>1194.336</v>
       </c>
       <c r="G100">
         <v>6.52</v>
@@ -9481,37 +9481,37 @@
         <v>188.11</v>
       </c>
       <c r="M100">
-        <v>199.2927470011076</v>
+        <v>201.3263464603025</v>
       </c>
       <c r="N100">
-        <v>-11.18274700110757</v>
+        <v>-13.21634646030253</v>
       </c>
       <c r="O100">
-        <v>-2.683859280265817</v>
+        <v>-3.171923150472607</v>
       </c>
       <c r="P100">
-        <v>-8.498887720841754</v>
+        <v>-10.04442330982992</v>
       </c>
       <c r="Q100">
-        <v>-6.108887720841754</v>
+        <v>-7.654423309829923</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.738785113394628</v>
+        <v>3.431770226789256</v>
       </c>
       <c r="T100">
-        <v>23.30457733390956</v>
+        <v>46.60915466781911</v>
       </c>
       <c r="U100">
         <v>0.1685675944292917</v>
       </c>
       <c r="V100">
-        <v>0.2265330810044437</v>
+        <v>0.2242448680650048</v>
       </c>
       <c r="W100">
-        <v>0.1303814579057168</v>
+        <v>0.1307671764564599</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.9438878375185153</v>
+        <v>0.9343536169375203</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.163777206959788</v>
-      </c>
-      <c r="C101">
-        <v>-640.8358645400951</v>
-      </c>
-      <c r="D101">
-        <v>546.9801354599049</v>
-      </c>
-      <c r="E101">
-        <v>273.5360000000001</v>
-      </c>
-      <c r="F101">
-        <v>1194.336</v>
-      </c>
-      <c r="G101">
-        <v>6.52</v>
-      </c>
-      <c r="H101">
-        <v>285.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>190.5</v>
-      </c>
-      <c r="K101">
-        <v>2.39</v>
-      </c>
-      <c r="L101">
-        <v>188.11</v>
-      </c>
-      <c r="M101">
-        <v>201.3263464603025</v>
-      </c>
-      <c r="N101">
-        <v>-13.21634646030253</v>
-      </c>
-      <c r="O101">
-        <v>-3.171923150472607</v>
-      </c>
-      <c r="P101">
-        <v>-10.04442330982992</v>
-      </c>
-      <c r="Q101">
-        <v>-7.654423309829923</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.431770226789256</v>
-      </c>
-      <c r="T101">
-        <v>46.60915466781911</v>
-      </c>
-      <c r="U101">
-        <v>0.1685675944292917</v>
-      </c>
-      <c r="V101">
-        <v>0.2242448680650048</v>
-      </c>
-      <c r="W101">
-        <v>0.1307671764564599</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.9343536169375203</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
